--- a/Financial Statement Model Online Walk Through.xlsx
+++ b/Financial Statement Model Online Walk Through.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eipny-my.sharepoint.com/personal/isiaka_energyimpactpartners_com/Documents/Training/Financial Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="491" documentId="13_ncr:1_{DD486496-2B70-447A-98D9-F2E49C8F2BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47DEB86C-30B6-45FF-95A3-E420938A7885}"/>
+  <xr:revisionPtr revIDLastSave="603" documentId="13_ncr:1_{DD486496-2B70-447A-98D9-F2E49C8F2BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0CFE351-5DE7-4165-8C60-4C5D3FA154DB}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="11370" tabRatio="736" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="736" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FSM Data Input_Empty" sheetId="66" r:id="rId1"/>
@@ -83,7 +83,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="12">'Rev Build Complete'!$C$2:$R$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'Rev Build Fill '!$C$2:$Q$41</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029" calcMode="autoNoTable"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -2499,7 +2499,7 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-Increse common stock by stock bsed compenstation
+common stock increases because ever year we get + are prev yr
 </t>
         </r>
       </text>
@@ -3401,7 +3401,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3415" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3419" uniqueCount="335">
   <si>
     <t>Tax rate</t>
   </si>
@@ -4458,6 +4458,15 @@
   <si>
     <t>Repurchases of common stock</t>
   </si>
+  <si>
+    <t>outflow</t>
+  </si>
+  <si>
+    <t>Inflow</t>
+  </si>
+  <si>
+    <t>Rev</t>
+  </si>
 </sst>
 </file>
 
@@ -5168,7 +5177,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="44">
+  <fills count="46">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5398,6 +5407,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD2F2FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -6316,7 +6337,7 @@
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyAlignment="0"/>
     <xf numFmtId="233" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="302">
+  <cellXfs count="305">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -6749,6 +6770,9 @@
     <xf numFmtId="10" fontId="2" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="63" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="60" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="37" fontId="2" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="209">
     <cellStyle name="$" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -53525,11 +53549,26 @@
       <c r="F30" s="3">
         <v>10903</v>
       </c>
-      <c r="G30" s="96"/>
-      <c r="H30" s="96"/>
-      <c r="I30" s="96"/>
-      <c r="J30" s="96"/>
-      <c r="K30" s="96"/>
+      <c r="G30" s="304">
+        <f>G106</f>
+        <v>10722.489599999999</v>
+      </c>
+      <c r="H30" s="304">
+        <f t="shared" ref="H30:K30" si="10">H106</f>
+        <v>11636.785152</v>
+      </c>
+      <c r="I30" s="304">
+        <f t="shared" si="10"/>
+        <v>12729.364789632</v>
+      </c>
+      <c r="J30" s="304">
+        <f t="shared" si="10"/>
+        <v>13917.317683148543</v>
+      </c>
+      <c r="K30" s="304">
+        <f t="shared" si="10"/>
+        <v>15208.603570206933</v>
+      </c>
       <c r="M30" t="s">
         <v>158</v>
       </c>
@@ -53552,23 +53591,23 @@
       </c>
       <c r="G31" s="300">
         <f>G22+G30</f>
-        <v>61703.030399999989</v>
+        <v>72425.51999999999</v>
       </c>
       <c r="H31" s="300">
-        <f t="shared" ref="H31:K31" si="10">H22+H30</f>
-        <v>67297.098528000002</v>
+        <f t="shared" ref="H31:K31" si="11">H22+H30</f>
+        <v>78933.883679999999</v>
       </c>
       <c r="I31" s="300">
-        <f t="shared" si="10"/>
-        <v>72229.51639199999</v>
+        <f t="shared" si="11"/>
+        <v>84958.881181631994</v>
       </c>
       <c r="J31" s="300">
-        <f t="shared" si="10"/>
-        <v>77213.353023047996</v>
+        <f t="shared" si="11"/>
+        <v>91130.670706196543</v>
       </c>
       <c r="K31" s="300">
-        <f t="shared" si="10"/>
-        <v>82541.074381638289</v>
+        <f t="shared" si="11"/>
+        <v>97749.677951845224</v>
       </c>
       <c r="M31" s="16" t="s">
         <v>97</v>
@@ -53592,19 +53631,19 @@
         <v>5126.3999999999996</v>
       </c>
       <c r="H32" s="59">
-        <f t="shared" ref="H32:K32" si="11">G32 *(1+H36)</f>
+        <f t="shared" ref="H32:K32" si="12">G32 *(1+H36)</f>
         <v>5433.9839999999995</v>
       </c>
       <c r="I32" s="59">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5808.9288959999994</v>
       </c>
       <c r="J32" s="59">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6209.7449898239993</v>
       </c>
       <c r="K32" s="59">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>6638.2173941218552</v>
       </c>
       <c r="M32" t="s">
@@ -53629,23 +53668,23 @@
       </c>
       <c r="G33" s="300">
         <f>G31+G32</f>
-        <v>66829.430399999983</v>
+        <v>77551.919999999984</v>
       </c>
       <c r="H33" s="300">
-        <f t="shared" ref="H33:K33" si="12">H31+H32</f>
-        <v>72731.082527999999</v>
+        <f t="shared" ref="H33:K33" si="13">H31+H32</f>
+        <v>84367.867679999996</v>
       </c>
       <c r="I33" s="300">
-        <f t="shared" si="12"/>
-        <v>78038.445287999988</v>
+        <f t="shared" si="13"/>
+        <v>90767.810077631992</v>
       </c>
       <c r="J33" s="300">
-        <f t="shared" si="12"/>
-        <v>83423.098012871997</v>
+        <f t="shared" si="13"/>
+        <v>97340.415696020544</v>
       </c>
       <c r="K33" s="300">
-        <f t="shared" si="12"/>
-        <v>89179.291775760139</v>
+        <f t="shared" si="13"/>
+        <v>104387.89534596707</v>
       </c>
       <c r="M33" s="16" t="s">
         <v>98</v>
@@ -53725,11 +53764,11 @@
         <v>0.38200000000000001</v>
       </c>
       <c r="J37" s="299">
-        <f t="shared" ref="J37:K40" si="13">I37</f>
+        <f t="shared" ref="J37:K40" si="14">I37</f>
         <v>0.38200000000000001</v>
       </c>
       <c r="K37" s="299">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.38200000000000001</v>
       </c>
       <c r="M37" t="s">
@@ -53768,11 +53807,11 @@
         <v>6.3E-2</v>
       </c>
       <c r="J38" s="299">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.3E-2</v>
       </c>
       <c r="K38" s="299">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.3E-2</v>
       </c>
       <c r="M38" t="s">
@@ -53811,11 +53850,11 @@
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="J39" s="299">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="K39" s="299">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="M39" t="s">
@@ -53854,11 +53893,11 @@
         <v>0.16900000000000001</v>
       </c>
       <c r="J40" s="299">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.16900000000000001</v>
       </c>
       <c r="K40" s="299">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.16900000000000001</v>
       </c>
       <c r="M40" t="s">
@@ -53898,31 +53937,31 @@
       </c>
       <c r="D43" s="23"/>
       <c r="E43" s="23">
-        <f t="shared" ref="E43:K44" si="14">E14</f>
+        <f t="shared" ref="E43:K44" si="15">E14</f>
         <v>2017</v>
       </c>
       <c r="F43" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2018</v>
       </c>
       <c r="G43" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2019</v>
       </c>
       <c r="H43" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2020</v>
       </c>
       <c r="I43" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2021</v>
       </c>
       <c r="J43" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2022</v>
       </c>
       <c r="K43" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2023</v>
       </c>
     </row>
@@ -53933,31 +53972,31 @@
       </c>
       <c r="D44" s="25"/>
       <c r="E44" s="25">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>43008</v>
       </c>
       <c r="F44" s="25">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>43372</v>
       </c>
       <c r="G44" s="25">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>43738</v>
       </c>
       <c r="H44" s="25">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>44104</v>
       </c>
       <c r="I44" s="25">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>44469</v>
       </c>
       <c r="J44" s="25">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>44834</v>
       </c>
       <c r="K44" s="25">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>45199</v>
       </c>
     </row>
@@ -53974,11 +54013,26 @@
         <f>25913+40388+170799</f>
         <v>237100</v>
       </c>
-      <c r="G45" s="101"/>
-      <c r="H45" s="101"/>
-      <c r="I45" s="101"/>
-      <c r="J45" s="101"/>
-      <c r="K45" s="101"/>
+      <c r="G45" s="298">
+        <f>G90+F45</f>
+        <v>300609.96712000988</v>
+      </c>
+      <c r="H45" s="298">
+        <f t="shared" ref="H45:K45" si="16">H90+G45</f>
+        <v>374579.51445339958</v>
+      </c>
+      <c r="I45" s="298">
+        <f t="shared" si="16"/>
+        <v>454939.44004868198</v>
+      </c>
+      <c r="J45" s="298">
+        <f t="shared" si="16"/>
+        <v>541270.73842356959</v>
+      </c>
+      <c r="K45" s="298">
+        <f t="shared" si="16"/>
+        <v>633915.17385224556</v>
+      </c>
       <c r="M45" t="s">
         <v>118</v>
       </c>
@@ -53995,24 +54049,24 @@
         <v>23186</v>
       </c>
       <c r="G46" s="59">
-        <f>F46+ (1+G36)</f>
-        <v>23186.959999999999</v>
+        <f>F46* (1+G36)</f>
+        <v>22258.559999999998</v>
       </c>
       <c r="H46" s="59">
-        <f t="shared" ref="H46:K46" si="15">G46+ (1+H36)</f>
-        <v>23188.02</v>
+        <f t="shared" ref="H46:K46" si="17">G46* (1+H36)</f>
+        <v>23594.0736</v>
       </c>
       <c r="I46" s="59">
-        <f t="shared" si="15"/>
-        <v>23189.089</v>
+        <f t="shared" si="17"/>
+        <v>25222.064678399998</v>
       </c>
       <c r="J46" s="59">
-        <f t="shared" si="15"/>
-        <v>23190.157999999999</v>
+        <f t="shared" si="17"/>
+        <v>26962.387141209598</v>
       </c>
       <c r="K46" s="59">
-        <f t="shared" si="15"/>
-        <v>23191.226999999999</v>
+        <f t="shared" si="17"/>
+        <v>28822.791853953058</v>
       </c>
       <c r="M46" t="s">
         <v>103</v>
@@ -54034,19 +54088,19 @@
         <v>3831.2507254598308</v>
       </c>
       <c r="H47" s="59">
-        <f t="shared" ref="H47:K47" si="16">G47*(((H18/G18)))</f>
+        <f t="shared" ref="H47:K47" si="18">G47*(((H18/G18)))</f>
         <v>4041.5383456643308</v>
       </c>
       <c r="I47" s="59">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>4313.4248396710418</v>
       </c>
       <c r="J47" s="59">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>4611.0511536083422</v>
       </c>
       <c r="K47" s="59">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>4929.2136832073174</v>
       </c>
       <c r="M47" t="s">
@@ -54067,24 +54121,24 @@
         <v>37896</v>
       </c>
       <c r="G48" s="59">
-        <f>F48+(1+G36)</f>
-        <v>37896.959999999999</v>
+        <f>F48*(1+G36)</f>
+        <v>36380.159999999996</v>
       </c>
       <c r="H48" s="59">
-        <f t="shared" ref="H48:K48" si="17">G48+(1+H36)</f>
-        <v>37898.019999999997</v>
+        <f t="shared" ref="H48:K48" si="19">G48*(1+H36)</f>
+        <v>38562.969599999997</v>
       </c>
       <c r="I48" s="59">
-        <f t="shared" si="17"/>
-        <v>37899.089</v>
+        <f t="shared" si="19"/>
+        <v>41223.814502399997</v>
       </c>
       <c r="J48" s="59">
-        <f t="shared" si="17"/>
-        <v>37900.158000000003</v>
+        <f t="shared" si="19"/>
+        <v>44068.257703065596</v>
       </c>
       <c r="K48" s="59">
-        <f t="shared" si="17"/>
-        <v>37901.227000000006</v>
+        <f t="shared" si="19"/>
+        <v>47108.967484577122</v>
       </c>
       <c r="M48" t="s">
         <v>103</v>
@@ -54122,24 +54176,24 @@
         <v>22283</v>
       </c>
       <c r="G50" s="59">
-        <f>F50+(1+G36)</f>
-        <v>22283.96</v>
+        <f>F50*(1+G36)</f>
+        <v>21391.68</v>
       </c>
       <c r="H50" s="59">
-        <f t="shared" ref="H50:K50" si="18">G50+(1+H36)</f>
-        <v>22285.02</v>
+        <f t="shared" ref="H50:K50" si="20">G50*(1+H36)</f>
+        <v>22675.180800000002</v>
       </c>
       <c r="I50" s="59">
-        <f t="shared" si="18"/>
-        <v>22286.089</v>
+        <f t="shared" si="20"/>
+        <v>24239.7682752</v>
       </c>
       <c r="J50" s="59">
-        <f t="shared" si="18"/>
-        <v>22287.157999999999</v>
+        <f t="shared" si="20"/>
+        <v>25912.3122861888</v>
       </c>
       <c r="K50" s="59">
-        <f t="shared" si="18"/>
-        <v>22288.226999999999</v>
+        <f t="shared" si="20"/>
+        <v>27700.261833935827</v>
       </c>
       <c r="M50" t="s">
         <v>103</v>
@@ -54160,23 +54214,23 @@
       </c>
       <c r="G51" s="300">
         <f>SUM(G45:G50)</f>
-        <v>87199.130725459836</v>
+        <v>384471.61784546968</v>
       </c>
       <c r="H51" s="300">
-        <f t="shared" ref="H51:K51" si="19">SUM(H45:H50)</f>
-        <v>87412.59834566433</v>
+        <f t="shared" ref="H51:K51" si="21">SUM(H45:H50)</f>
+        <v>463453.2767990639</v>
       </c>
       <c r="I51" s="300">
-        <f t="shared" si="19"/>
-        <v>87687.691839671053</v>
+        <f t="shared" si="21"/>
+        <v>549938.51234435302</v>
       </c>
       <c r="J51" s="300">
-        <f t="shared" si="19"/>
-        <v>87988.525153608338</v>
+        <f t="shared" si="21"/>
+        <v>642824.74670764199</v>
       </c>
       <c r="K51" s="300">
-        <f t="shared" si="19"/>
-        <v>88309.894683207312</v>
+        <f t="shared" si="21"/>
+        <v>742476.40870791883</v>
       </c>
     </row>
     <row r="52" spans="3:13">
@@ -54201,19 +54255,19 @@
         <v>54125.616922269721</v>
       </c>
       <c r="H53" s="59">
-        <f t="shared" ref="H53:K53" si="20">G53*(H18/G18)</f>
+        <f t="shared" ref="H53:K53" si="22">G53*(H18/G18)</f>
         <v>57096.434545623888</v>
       </c>
       <c r="I53" s="59">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>60937.48418592901</v>
       </c>
       <c r="J53" s="59">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>65142.170594758092</v>
       </c>
       <c r="K53" s="59">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>69636.980365796393</v>
       </c>
       <c r="M53" t="s">
@@ -54236,19 +54290,19 @@
         <v>31379.52</v>
       </c>
       <c r="H54" s="59">
-        <f t="shared" ref="H54:K54" si="21">G54*(1+H36)</f>
+        <f t="shared" ref="H54:K54" si="23">G54*(1+H36)</f>
         <v>33262.2912</v>
       </c>
       <c r="I54" s="59">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>35557.389292799999</v>
       </c>
       <c r="J54" s="59">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>38010.849154003197</v>
       </c>
       <c r="K54" s="59">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>40633.597745629413</v>
       </c>
       <c r="M54" t="s">
@@ -54273,19 +54327,19 @@
         <v>9926.4</v>
       </c>
       <c r="H55" s="59">
-        <f t="shared" ref="H55:K55" si="22">G55*(1+H36)</f>
+        <f t="shared" ref="H55:K55" si="24">G55*(1+H36)</f>
         <v>10521.984</v>
       </c>
       <c r="I55" s="59">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>11248.000896</v>
       </c>
       <c r="J55" s="59">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>12024.112957824</v>
       </c>
       <c r="K55" s="59">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>12853.776751913854</v>
       </c>
       <c r="M55" t="s">
@@ -54330,19 +54384,19 @@
         <v>102519</v>
       </c>
       <c r="H57" s="59">
-        <f t="shared" ref="H57:K57" si="23">$F$57</f>
+        <f t="shared" ref="H57:K57" si="25">$F$57</f>
         <v>102519</v>
       </c>
       <c r="I57" s="59">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>102519</v>
       </c>
       <c r="J57" s="59">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>102519</v>
       </c>
       <c r="K57" s="59">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>102519</v>
       </c>
       <c r="M57" t="s">
@@ -54361,24 +54415,24 @@
         <v>45180</v>
       </c>
       <c r="G58" s="59">
-        <f>F58+(1+G36)</f>
-        <v>45180.959999999999</v>
+        <f>F58*(1+G36)</f>
+        <v>43372.799999999996</v>
       </c>
       <c r="H58" s="59">
-        <f t="shared" ref="H58:K58" si="24">G58+(1+H36)</f>
-        <v>45182.02</v>
+        <f t="shared" ref="H58:K58" si="26">G58*(1+H36)</f>
+        <v>45975.167999999998</v>
       </c>
       <c r="I58" s="59">
-        <f t="shared" si="24"/>
-        <v>45183.089</v>
+        <f t="shared" si="26"/>
+        <v>49147.454591999995</v>
       </c>
       <c r="J58" s="59">
-        <f t="shared" si="24"/>
-        <v>45184.158000000003</v>
+        <f t="shared" si="26"/>
+        <v>52538.628958847992</v>
       </c>
       <c r="K58" s="59">
-        <f t="shared" si="24"/>
-        <v>45185.227000000006</v>
+        <f t="shared" si="26"/>
+        <v>56163.794357008504</v>
       </c>
       <c r="M58" t="s">
         <v>103</v>
@@ -54399,23 +54453,23 @@
       </c>
       <c r="G59" s="59">
         <f>SUM(G53:G58)</f>
-        <v>243131.49692226973</v>
+        <v>241323.33692226972</v>
       </c>
       <c r="H59" s="59">
-        <f t="shared" ref="H59:K59" si="25">SUM(H53:H58)</f>
-        <v>248581.72974562386</v>
+        <f t="shared" ref="H59:K59" si="27">SUM(H53:H58)</f>
+        <v>249374.87774562387</v>
       </c>
       <c r="I59" s="59">
-        <f t="shared" si="25"/>
-        <v>255444.96337472901</v>
+        <f t="shared" si="27"/>
+        <v>259409.32896672899</v>
       </c>
       <c r="J59" s="59">
-        <f t="shared" si="25"/>
-        <v>262880.29070658528</v>
+        <f t="shared" si="27"/>
+        <v>270234.7616654333</v>
       </c>
       <c r="K59" s="59">
-        <f t="shared" si="25"/>
-        <v>270828.58186333964</v>
+        <f t="shared" si="27"/>
+        <v>281807.14922034816</v>
       </c>
     </row>
     <row r="60" spans="3:13">
@@ -54435,11 +54489,26 @@
       <c r="F61" s="3">
         <v>40201</v>
       </c>
-      <c r="G61" s="101"/>
-      <c r="H61" s="101"/>
-      <c r="I61" s="101"/>
-      <c r="J61" s="101"/>
-      <c r="K61" s="101"/>
+      <c r="G61" s="59">
+        <f>F61+G32</f>
+        <v>45327.4</v>
+      </c>
+      <c r="H61" s="59">
+        <f t="shared" ref="H61:K61" si="28">G61+H32</f>
+        <v>50761.383999999998</v>
+      </c>
+      <c r="I61" s="59">
+        <f t="shared" si="28"/>
+        <v>56570.312895999996</v>
+      </c>
+      <c r="J61" s="59">
+        <f t="shared" si="28"/>
+        <v>62780.057885823997</v>
+      </c>
+      <c r="K61" s="59">
+        <f t="shared" si="28"/>
+        <v>69418.275279945854</v>
+      </c>
       <c r="M61" t="s">
         <v>154</v>
       </c>
@@ -54475,11 +54544,26 @@
       <c r="F63" s="3">
         <v>-3454</v>
       </c>
-      <c r="G63" s="101"/>
-      <c r="H63" s="101"/>
-      <c r="I63" s="101"/>
-      <c r="J63" s="101"/>
-      <c r="K63" s="101"/>
+      <c r="G63" s="59">
+        <f>$F$63</f>
+        <v>-3454</v>
+      </c>
+      <c r="H63" s="59">
+        <f t="shared" ref="H63:K63" si="29">$F$63</f>
+        <v>-3454</v>
+      </c>
+      <c r="I63" s="59">
+        <f t="shared" si="29"/>
+        <v>-3454</v>
+      </c>
+      <c r="J63" s="59">
+        <f t="shared" si="29"/>
+        <v>-3454</v>
+      </c>
+      <c r="K63" s="59">
+        <f t="shared" si="29"/>
+        <v>-3454</v>
+      </c>
       <c r="M63" t="s">
         <v>100</v>
       </c>
@@ -54497,52 +54581,67 @@
         <f>SUM(F61:F63)</f>
         <v>107147</v>
       </c>
-      <c r="G64" s="228"/>
-      <c r="H64" s="228"/>
-      <c r="I64" s="228"/>
-      <c r="J64" s="228"/>
-      <c r="K64" s="228"/>
-    </row>
-    <row r="65" spans="2:13">
+      <c r="G64" s="102">
+        <f>SUM(G61:G63)</f>
+        <v>41873.4</v>
+      </c>
+      <c r="H64" s="102">
+        <f t="shared" ref="H64:K64" si="30">SUM(H61:H63)</f>
+        <v>47307.383999999998</v>
+      </c>
+      <c r="I64" s="102">
+        <f t="shared" si="30"/>
+        <v>53116.312895999996</v>
+      </c>
+      <c r="J64" s="102">
+        <f t="shared" si="30"/>
+        <v>59326.057885823997</v>
+      </c>
+      <c r="K64" s="102">
+        <f t="shared" si="30"/>
+        <v>65964.275279945854</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14">
       <c r="D65" s="18"/>
       <c r="E65" s="18"/>
       <c r="F65" s="18"/>
     </row>
-    <row r="66" spans="2:13">
+    <row r="66" spans="2:14">
       <c r="C66" s="12" t="s">
         <v>26</v>
       </c>
       <c r="D66" s="30"/>
       <c r="E66" s="30">
-        <f t="shared" ref="E66:K66" si="26">ROUND(E51-E59-E64,3)</f>
+        <f t="shared" ref="E66:G66" si="31">ROUND(E51-E59-E64,3)</f>
         <v>0</v>
       </c>
       <c r="F66" s="30">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="G66" s="30">
-        <f t="shared" si="26"/>
-        <v>-155932.36600000001</v>
+        <f t="shared" si="31"/>
+        <v>101274.88099999999</v>
       </c>
       <c r="H66" s="30">
-        <f t="shared" si="26"/>
-        <v>-161169.13099999999</v>
+        <f t="shared" ref="H66:K66" si="32">ROUND(H51-H59-H64,3)</f>
+        <v>166771.01500000001</v>
       </c>
       <c r="I66" s="30">
-        <f t="shared" si="26"/>
-        <v>-167757.272</v>
+        <f t="shared" si="32"/>
+        <v>237412.87</v>
       </c>
       <c r="J66" s="30">
-        <f t="shared" si="26"/>
-        <v>-174891.766</v>
+        <f t="shared" si="32"/>
+        <v>313263.92700000003</v>
       </c>
       <c r="K66" s="30">
-        <f t="shared" si="26"/>
-        <v>-182518.68700000001</v>
-      </c>
-    </row>
-    <row r="67" spans="2:13">
+        <f t="shared" si="32"/>
+        <v>394704.984</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14">
       <c r="E67" s="18"/>
       <c r="F67" s="18"/>
       <c r="H67" s="18"/>
@@ -54550,7 +54649,7 @@
       <c r="J67" s="18"/>
       <c r="K67" s="18"/>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:14">
       <c r="B68" t="s">
         <v>316</v>
       </c>
@@ -54566,7 +54665,7 @@
       <c r="J68" s="11"/>
       <c r="K68" s="11"/>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:14">
       <c r="C69" s="26" t="str">
         <f>C14</f>
         <v xml:space="preserve">Fiscal year  </v>
@@ -54575,27 +54674,27 @@
       <c r="E69" s="23"/>
       <c r="F69" s="23"/>
       <c r="G69" s="24">
-        <f t="shared" ref="G69:K70" si="27">G14</f>
+        <f t="shared" ref="G69:K70" si="33">G14</f>
         <v>2019</v>
       </c>
       <c r="H69" s="24">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>2020</v>
       </c>
       <c r="I69" s="24">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>2021</v>
       </c>
       <c r="J69" s="24">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>2022</v>
       </c>
       <c r="K69" s="24">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>2023</v>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:14">
       <c r="C70" s="7" t="str">
         <f>C15</f>
         <v>Fiscal year end date</v>
@@ -54604,27 +54703,27 @@
       <c r="E70" s="25"/>
       <c r="F70" s="25"/>
       <c r="G70" s="25">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>43738</v>
       </c>
       <c r="H70" s="25">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>44104</v>
       </c>
       <c r="I70" s="25">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>44469</v>
       </c>
       <c r="J70" s="25">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>44834</v>
       </c>
       <c r="K70" s="25">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>45199</v>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:14">
       <c r="C72" t="s">
         <v>2</v>
       </c>
@@ -54636,52 +54735,52 @@
         <v>51031.271323199988</v>
       </c>
       <c r="H72" s="298">
-        <f t="shared" ref="H72:K72" si="28">H28</f>
+        <f t="shared" ref="H72:K72" si="34">H28</f>
         <v>55490.56177824</v>
       </c>
       <c r="I72" s="298">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>59656.257121751987</v>
       </c>
       <c r="J72" s="298">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>63797.825362152886</v>
       </c>
       <c r="K72" s="298">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>68225.161811141414</v>
       </c>
       <c r="M72" s="16"/>
     </row>
-    <row r="73" spans="2:13">
+    <row r="73" spans="2:14">
       <c r="C73" t="s">
         <v>33</v>
       </c>
       <c r="D73" s="34"/>
       <c r="E73" s="34"/>
       <c r="F73" s="34"/>
-      <c r="G73" s="105">
-        <f>G30</f>
-        <v>0</v>
-      </c>
-      <c r="H73" s="105">
-        <f t="shared" ref="H73:K73" si="29">H30</f>
-        <v>0</v>
-      </c>
-      <c r="I73" s="105">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="J73" s="105">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="K73" s="105">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="2:13">
+      <c r="G73" s="304">
+        <f>G106</f>
+        <v>10722.489599999999</v>
+      </c>
+      <c r="H73" s="304">
+        <f t="shared" ref="H73:K73" si="35">H106</f>
+        <v>11636.785152</v>
+      </c>
+      <c r="I73" s="304">
+        <f t="shared" si="35"/>
+        <v>12729.364789632</v>
+      </c>
+      <c r="J73" s="304">
+        <f t="shared" si="35"/>
+        <v>13917.317683148543</v>
+      </c>
+      <c r="K73" s="304">
+        <f t="shared" si="35"/>
+        <v>15208.603570206933</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14">
       <c r="C74" t="s">
         <v>74</v>
       </c>
@@ -54693,83 +54792,163 @@
         <v>5126.3999999999996</v>
       </c>
       <c r="H74" s="59">
-        <f t="shared" ref="H74:K74" si="30">H32</f>
+        <f t="shared" ref="H74:K74" si="36">H32</f>
         <v>5433.9839999999995</v>
       </c>
       <c r="I74" s="59">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>5808.9288959999994</v>
       </c>
       <c r="J74" s="59">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>6209.7449898239993</v>
       </c>
       <c r="K74" s="59">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>6638.2173941218552</v>
       </c>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:14">
       <c r="C75" t="s">
         <v>65</v>
       </c>
       <c r="D75" s="18"/>
       <c r="E75" s="18"/>
       <c r="F75" s="18"/>
-      <c r="G75" s="101"/>
-      <c r="H75" s="101"/>
-      <c r="I75" s="101"/>
-      <c r="J75" s="101"/>
-      <c r="K75" s="101"/>
-    </row>
-    <row r="76" spans="2:13">
+      <c r="G75" s="59">
+        <f>SUM(F46:F48) - SUM(G46:G48)</f>
+        <v>2568.0292745401748</v>
+      </c>
+      <c r="H75" s="59">
+        <f>SUM(G46:G48) - SUM(H46:H48)</f>
+        <v>-3728.610820204507</v>
+      </c>
+      <c r="I75" s="59">
+        <f t="shared" ref="I75:K75" si="37">SUM(H46:H48) - SUM(I46:I48)</f>
+        <v>-4560.7224748067092</v>
+      </c>
+      <c r="J75" s="59">
+        <f t="shared" si="37"/>
+        <v>-4882.3919774124952</v>
+      </c>
+      <c r="K75" s="59">
+        <f t="shared" si="37"/>
+        <v>-5219.277023853967</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14">
       <c r="C76" t="s">
         <v>66</v>
       </c>
       <c r="D76" s="18"/>
       <c r="E76" s="18"/>
       <c r="F76" s="18"/>
-      <c r="G76" s="101"/>
-      <c r="H76" s="101"/>
-      <c r="I76" s="101"/>
-      <c r="J76" s="101"/>
-      <c r="K76" s="101"/>
-    </row>
-    <row r="77" spans="2:13">
+      <c r="G76" s="59">
+        <f>-(SUM(F53:F55) - SUM(G53:G55))</f>
+        <v>-3483.4630777302809</v>
+      </c>
+      <c r="H76" s="59">
+        <f t="shared" ref="H76:K76" si="38">-(SUM(G53:G55) - SUM(H53:H55))</f>
+        <v>5449.1728233541653</v>
+      </c>
+      <c r="I76" s="59">
+        <f t="shared" si="38"/>
+        <v>6862.1646291051293</v>
+      </c>
+      <c r="J76" s="59">
+        <f t="shared" si="38"/>
+        <v>7434.2583318562683</v>
+      </c>
+      <c r="K76" s="59">
+        <f t="shared" si="38"/>
+        <v>7947.2221567543747</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14">
       <c r="C77" t="s">
         <v>56</v>
       </c>
-      <c r="G77" s="96"/>
-      <c r="H77" s="96"/>
-      <c r="I77" s="96"/>
-      <c r="J77" s="96"/>
-      <c r="K77" s="96"/>
-      <c r="M77" t="s">
+      <c r="G77" s="304">
+        <f>G111</f>
+        <v>-647.56000000000131</v>
+      </c>
+      <c r="H77" s="304">
+        <f t="shared" ref="H77:K77" si="39">H111</f>
+        <v>-2914.7136000000028</v>
+      </c>
+      <c r="I77" s="304">
+        <f t="shared" si="39"/>
+        <v>-3308.3539583999991</v>
+      </c>
+      <c r="J77" s="304">
+        <f t="shared" si="39"/>
+        <v>-3536.6303815296014</v>
+      </c>
+      <c r="K77" s="304">
+        <f t="shared" si="39"/>
+        <v>-3780.6578778551411</v>
+      </c>
+      <c r="M77" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="N77" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:14">
       <c r="C78" t="s">
         <v>59</v>
       </c>
-      <c r="G78" s="101"/>
-      <c r="H78" s="101"/>
-      <c r="I78" s="101"/>
-      <c r="J78" s="101"/>
-      <c r="K78" s="101"/>
-      <c r="M78" s="16"/>
-    </row>
-    <row r="79" spans="2:13">
+      <c r="G78" s="59">
+        <f>G58-F58</f>
+        <v>-1807.2000000000044</v>
+      </c>
+      <c r="H78" s="59">
+        <f t="shared" ref="H78:K78" si="40">H58-G58</f>
+        <v>2602.3680000000022</v>
+      </c>
+      <c r="I78" s="59">
+        <f t="shared" si="40"/>
+        <v>3172.2865919999967</v>
+      </c>
+      <c r="J78" s="59">
+        <f t="shared" si="40"/>
+        <v>3391.1743668479976</v>
+      </c>
+      <c r="K78" s="59">
+        <f t="shared" si="40"/>
+        <v>3625.1653981605123</v>
+      </c>
+      <c r="M78" s="16" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14">
       <c r="C79" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="G79" s="228"/>
-      <c r="H79" s="228"/>
-      <c r="I79" s="228"/>
-      <c r="J79" s="228"/>
-      <c r="K79" s="228"/>
-    </row>
-    <row r="81" spans="3:13">
+      <c r="G79" s="300">
+        <f>SUM(G72:G78)</f>
+        <v>63509.967120009875</v>
+      </c>
+      <c r="H79" s="300">
+        <f t="shared" ref="H79:K79" si="41">SUM(H72:H78)</f>
+        <v>73969.547333389666</v>
+      </c>
+      <c r="I79" s="300">
+        <f t="shared" si="41"/>
+        <v>80359.925595282402</v>
+      </c>
+      <c r="J79" s="300">
+        <f t="shared" si="41"/>
+        <v>86331.298374887614</v>
+      </c>
+      <c r="K79" s="300">
+        <f t="shared" si="41"/>
+        <v>92644.435428675992</v>
+      </c>
+    </row>
+    <row r="81" spans="2:13">
       <c r="C81" t="s">
         <v>35</v>
       </c>
@@ -54779,17 +54958,32 @@
       <c r="J81" s="96"/>
       <c r="K81" s="96"/>
     </row>
-    <row r="82" spans="3:13">
+    <row r="82" spans="2:13">
       <c r="C82" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="G82" s="228"/>
-      <c r="H82" s="228"/>
-      <c r="I82" s="228"/>
-      <c r="J82" s="228"/>
-      <c r="K82" s="228"/>
-    </row>
-    <row r="84" spans="3:13">
+      <c r="G82" s="228">
+        <f>SUM(G81)</f>
+        <v>0</v>
+      </c>
+      <c r="H82" s="228">
+        <f t="shared" ref="H82:K82" si="42">SUM(H81)</f>
+        <v>0</v>
+      </c>
+      <c r="I82" s="228">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="J82" s="228">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="K82" s="228">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="2:13">
       <c r="C84" t="s">
         <v>67</v>
       </c>
@@ -54799,57 +54993,90 @@
       <c r="J84" s="97"/>
       <c r="K84" s="97"/>
     </row>
-    <row r="85" spans="3:13">
+    <row r="85" spans="2:13">
       <c r="C85" t="s">
         <v>23</v>
       </c>
-      <c r="G85" s="96"/>
-      <c r="H85" s="96"/>
-      <c r="I85" s="96"/>
-      <c r="J85" s="96"/>
-      <c r="K85" s="96"/>
-    </row>
-    <row r="86" spans="3:13">
+      <c r="G85" s="302"/>
+      <c r="H85" s="302"/>
+      <c r="I85" s="302"/>
+      <c r="J85" s="302"/>
+      <c r="K85" s="302"/>
+    </row>
+    <row r="86" spans="2:13">
       <c r="C86" t="s">
         <v>70</v>
       </c>
-      <c r="G86" s="96"/>
-      <c r="H86" s="96"/>
-      <c r="I86" s="96"/>
-      <c r="J86" s="96"/>
-      <c r="K86" s="96"/>
-    </row>
-    <row r="87" spans="3:13">
+      <c r="G86" s="302"/>
+      <c r="H86" s="302"/>
+      <c r="I86" s="302"/>
+      <c r="J86" s="302"/>
+      <c r="K86" s="302"/>
+    </row>
+    <row r="87" spans="2:13">
       <c r="C87" t="s">
         <v>71</v>
       </c>
-      <c r="G87" s="96"/>
-      <c r="H87" s="96"/>
-      <c r="I87" s="96"/>
-      <c r="J87" s="96"/>
-      <c r="K87" s="96"/>
-    </row>
-    <row r="88" spans="3:13">
+      <c r="G87" s="302"/>
+      <c r="H87" s="302"/>
+      <c r="I87" s="302"/>
+      <c r="J87" s="302"/>
+      <c r="K87" s="302"/>
+    </row>
+    <row r="88" spans="2:13">
       <c r="C88" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="G88" s="228"/>
-      <c r="H88" s="228"/>
-      <c r="I88" s="228"/>
-      <c r="J88" s="228"/>
-      <c r="K88" s="228"/>
-    </row>
-    <row r="90" spans="3:13">
+      <c r="G88" s="228">
+        <f>SUM(G84:G87)</f>
+        <v>0</v>
+      </c>
+      <c r="H88" s="228">
+        <f t="shared" ref="H88:K88" si="43">SUM(H84:H87)</f>
+        <v>0</v>
+      </c>
+      <c r="I88" s="228">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="J88" s="228">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="K88" s="228">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="2:13">
       <c r="C90" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="G90" s="228"/>
-      <c r="H90" s="228"/>
-      <c r="I90" s="228"/>
-      <c r="J90" s="228"/>
-      <c r="K90" s="228"/>
-    </row>
-    <row r="92" spans="3:13">
+      <c r="G90" s="300">
+        <f>G88+G82+G79</f>
+        <v>63509.967120009875</v>
+      </c>
+      <c r="H90" s="300">
+        <f t="shared" ref="H90:K90" si="44">H88+H82+H79</f>
+        <v>73969.547333389666</v>
+      </c>
+      <c r="I90" s="300">
+        <f t="shared" si="44"/>
+        <v>80359.925595282402</v>
+      </c>
+      <c r="J90" s="300">
+        <f t="shared" si="44"/>
+        <v>86331.298374887614</v>
+      </c>
+      <c r="K90" s="300">
+        <f t="shared" si="44"/>
+        <v>92644.435428675992</v>
+      </c>
+    </row>
+    <row r="92" spans="2:13">
+      <c r="B92" t="s">
+        <v>316</v>
+      </c>
       <c r="C92" s="5" t="s">
         <v>29</v>
       </c>
@@ -54862,83 +55089,83 @@
       <c r="J92" s="7"/>
       <c r="K92" s="7"/>
     </row>
-    <row r="93" spans="3:13">
+    <row r="93" spans="2:13">
       <c r="C93" s="26" t="str">
-        <f t="shared" ref="C93:K93" si="31">C14</f>
+        <f t="shared" ref="C93:K93" si="45">C14</f>
         <v xml:space="preserve">Fiscal year  </v>
       </c>
       <c r="D93" s="23">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>2016</v>
       </c>
       <c r="E93" s="23">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>2017</v>
       </c>
       <c r="F93" s="23">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>2018</v>
       </c>
       <c r="G93" s="24">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>2019</v>
       </c>
       <c r="H93" s="24">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>2020</v>
       </c>
       <c r="I93" s="24">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>2021</v>
       </c>
       <c r="J93" s="24">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>2022</v>
       </c>
       <c r="K93" s="24">
-        <f t="shared" si="31"/>
+        <f t="shared" si="45"/>
         <v>2023</v>
       </c>
     </row>
-    <row r="94" spans="3:13">
+    <row r="94" spans="2:13">
       <c r="C94" s="7" t="str">
-        <f t="shared" ref="C94:K94" si="32">C15</f>
+        <f t="shared" ref="C94:K94" si="46">C15</f>
         <v>Fiscal year end date</v>
       </c>
       <c r="D94" s="25">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>42643</v>
       </c>
       <c r="E94" s="25">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>43008</v>
       </c>
       <c r="F94" s="25">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>43372</v>
       </c>
       <c r="G94" s="25">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>43738</v>
       </c>
       <c r="H94" s="25">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>44104</v>
       </c>
       <c r="I94" s="25">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>44469</v>
       </c>
       <c r="J94" s="25">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>44834</v>
       </c>
       <c r="K94" s="25">
-        <f t="shared" si="32"/>
+        <f t="shared" si="46"/>
         <v>45199</v>
       </c>
     </row>
-    <row r="95" spans="3:13">
+    <row r="95" spans="2:13">
       <c r="C95" s="16"/>
       <c r="G95" s="76" t="s">
         <v>116</v>
@@ -54948,15 +55175,30 @@
       <c r="J95" s="76"/>
       <c r="K95" s="76"/>
     </row>
-    <row r="96" spans="3:13">
+    <row r="96" spans="2:13">
       <c r="C96" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="G96" s="59"/>
-      <c r="H96" s="59"/>
-      <c r="I96" s="59"/>
-      <c r="J96" s="59"/>
-      <c r="K96" s="59"/>
+      <c r="G96" s="59">
+        <f>F99</f>
+        <v>41304</v>
+      </c>
+      <c r="H96" s="59">
+        <f t="shared" ref="H96:K96" si="47">G99</f>
+        <v>44900.8704</v>
+      </c>
+      <c r="I96" s="59">
+        <f t="shared" si="47"/>
+        <v>48442.606847999996</v>
+      </c>
+      <c r="J96" s="59">
+        <f t="shared" si="47"/>
+        <v>51939.081648767991</v>
+      </c>
+      <c r="K96" s="59">
+        <f t="shared" si="47"/>
+        <v>55367.186487757041</v>
+      </c>
       <c r="M96" t="s">
         <v>166</v>
       </c>
@@ -54975,19 +55217,27 @@
         <v>13313</v>
       </c>
       <c r="G97" s="3">
-        <v>13285</v>
+        <f>F97*(1+G36)</f>
+        <v>12780.48</v>
       </c>
       <c r="H97" s="3">
-        <v>13649</v>
+        <f t="shared" ref="H97:K97" si="48">G97*(1+H36)</f>
+        <v>13547.308800000001</v>
       </c>
       <c r="I97" s="3">
-        <v>13819</v>
+        <f t="shared" si="48"/>
+        <v>14482.0731072</v>
       </c>
       <c r="J97" s="3">
-        <v>14000</v>
+        <f t="shared" si="48"/>
+        <v>15481.336151596799</v>
       </c>
       <c r="K97" s="3">
-        <v>14200</v>
+        <f t="shared" si="48"/>
+        <v>16549.548346056978</v>
+      </c>
+      <c r="L97" s="303" t="s">
+        <v>334</v>
       </c>
       <c r="M97" t="s">
         <v>153</v>
@@ -55006,11 +55256,26 @@
       <c r="F98" s="62">
         <v>-9300</v>
       </c>
-      <c r="G98" s="103"/>
-      <c r="H98" s="103"/>
-      <c r="I98" s="103"/>
-      <c r="J98" s="103"/>
-      <c r="K98" s="103"/>
+      <c r="G98" s="103">
+        <f>(G101*G97) *-1</f>
+        <v>-9183.6095999999998</v>
+      </c>
+      <c r="H98" s="103">
+        <f t="shared" ref="H98:K98" si="49">(H101*H97) *-1</f>
+        <v>-10005.572352000001</v>
+      </c>
+      <c r="I98" s="103">
+        <f t="shared" si="49"/>
+        <v>-10985.598306432001</v>
+      </c>
+      <c r="J98" s="103">
+        <f t="shared" si="49"/>
+        <v>-12053.231312607744</v>
+      </c>
+      <c r="K98" s="103">
+        <f t="shared" si="49"/>
+        <v>-13215.895240098818</v>
+      </c>
       <c r="M98" t="s">
         <v>165</v>
       </c>
@@ -55028,11 +55293,26 @@
         <f>F49</f>
         <v>41304</v>
       </c>
-      <c r="G99" s="102"/>
-      <c r="H99" s="102"/>
-      <c r="I99" s="102"/>
-      <c r="J99" s="102"/>
-      <c r="K99" s="102"/>
+      <c r="G99" s="102">
+        <f>SUM(G96:G98)</f>
+        <v>44900.8704</v>
+      </c>
+      <c r="H99" s="102">
+        <f t="shared" ref="H99:K99" si="50">SUM(H96:H98)</f>
+        <v>48442.606847999996</v>
+      </c>
+      <c r="I99" s="102">
+        <f t="shared" si="50"/>
+        <v>51939.081648767991</v>
+      </c>
+      <c r="J99" s="102">
+        <f t="shared" si="50"/>
+        <v>55367.186487757041</v>
+      </c>
+      <c r="K99" s="102">
+        <f t="shared" si="50"/>
+        <v>58700.839593715194</v>
+      </c>
       <c r="M99" t="s">
         <v>164</v>
       </c>
@@ -55059,11 +55339,26 @@
         <f>-(F98/F97)</f>
         <v>0.69856531210095396</v>
       </c>
-      <c r="G101" s="95"/>
-      <c r="H101" s="95"/>
-      <c r="I101" s="95"/>
-      <c r="J101" s="95"/>
-      <c r="K101" s="95"/>
+      <c r="G101" s="95">
+        <f>F101+$M$101</f>
+        <v>0.71856531210095398</v>
+      </c>
+      <c r="H101" s="95">
+        <f t="shared" ref="H101:K101" si="51">G101+$M$101</f>
+        <v>0.738565312100954</v>
+      </c>
+      <c r="I101" s="95">
+        <f t="shared" si="51"/>
+        <v>0.75856531210095401</v>
+      </c>
+      <c r="J101" s="95">
+        <f>I101+$M$101</f>
+        <v>0.77856531210095403</v>
+      </c>
+      <c r="K101" s="95">
+        <f t="shared" si="51"/>
+        <v>0.79856531210095405</v>
+      </c>
       <c r="M101" s="55">
         <v>0.02</v>
       </c>
@@ -55114,11 +55409,26 @@
         <f>F106+F98</f>
         <v>1603</v>
       </c>
-      <c r="G104" s="99"/>
-      <c r="H104" s="99"/>
-      <c r="I104" s="99"/>
-      <c r="J104" s="99"/>
-      <c r="K104" s="99"/>
+      <c r="G104" s="99">
+        <f>G105*G17</f>
+        <v>1538.8799999999999</v>
+      </c>
+      <c r="H104" s="99">
+        <f t="shared" ref="H104:K104" si="52">H105*H17</f>
+        <v>1631.2128</v>
+      </c>
+      <c r="I104" s="99">
+        <f t="shared" si="52"/>
+        <v>1743.7664832</v>
+      </c>
+      <c r="J104" s="99">
+        <f t="shared" si="52"/>
+        <v>1864.0863705407999</v>
+      </c>
+      <c r="K104" s="99">
+        <f t="shared" si="52"/>
+        <v>1992.708330108115</v>
+      </c>
       <c r="M104" t="s">
         <v>237</v>
       </c>
@@ -55142,11 +55452,26 @@
         <f>F104/F17</f>
         <v>6.0355051864681188E-3</v>
       </c>
-      <c r="G105" s="95"/>
-      <c r="H105" s="95"/>
-      <c r="I105" s="95"/>
-      <c r="J105" s="95"/>
-      <c r="K105" s="95"/>
+      <c r="G105" s="95">
+        <f>$F$105</f>
+        <v>6.0355051864681188E-3</v>
+      </c>
+      <c r="H105" s="95">
+        <f t="shared" ref="H105:K105" si="53">$F$105</f>
+        <v>6.0355051864681188E-3</v>
+      </c>
+      <c r="I105" s="95">
+        <f t="shared" si="53"/>
+        <v>6.0355051864681188E-3</v>
+      </c>
+      <c r="J105" s="95">
+        <f t="shared" si="53"/>
+        <v>6.0355051864681188E-3</v>
+      </c>
+      <c r="K105" s="95">
+        <f t="shared" si="53"/>
+        <v>6.0355051864681188E-3</v>
+      </c>
       <c r="M105" t="s">
         <v>157</v>
       </c>
@@ -55170,11 +55495,26 @@
         <f>F30</f>
         <v>10903</v>
       </c>
-      <c r="G106" s="100"/>
-      <c r="H106" s="100"/>
-      <c r="I106" s="100"/>
-      <c r="J106" s="100"/>
-      <c r="K106" s="100"/>
+      <c r="G106" s="100">
+        <f>G104-G98</f>
+        <v>10722.489599999999</v>
+      </c>
+      <c r="H106" s="100">
+        <f t="shared" ref="H106:K106" si="54">H104-H98</f>
+        <v>11636.785152</v>
+      </c>
+      <c r="I106" s="100">
+        <f t="shared" si="54"/>
+        <v>12729.364789632</v>
+      </c>
+      <c r="J106" s="100">
+        <f t="shared" si="54"/>
+        <v>13917.317683148543</v>
+      </c>
+      <c r="K106" s="100">
+        <f t="shared" si="54"/>
+        <v>15208.603570206933</v>
+      </c>
       <c r="M106" t="s">
         <v>159</v>
       </c>
@@ -55205,11 +55545,26 @@
         <v>27</v>
       </c>
       <c r="D109" s="18"/>
-      <c r="G109" s="108"/>
-      <c r="H109" s="108"/>
-      <c r="I109" s="108"/>
-      <c r="J109" s="108"/>
-      <c r="K109" s="108"/>
+      <c r="G109" s="108">
+        <f>F112</f>
+        <v>22283</v>
+      </c>
+      <c r="H109" s="108">
+        <f t="shared" ref="H109:K109" si="55">G112</f>
+        <v>21391.68</v>
+      </c>
+      <c r="I109" s="108">
+        <f t="shared" si="55"/>
+        <v>22675.180800000002</v>
+      </c>
+      <c r="J109" s="108">
+        <f t="shared" si="55"/>
+        <v>24239.7682752</v>
+      </c>
+      <c r="K109" s="108">
+        <f t="shared" si="55"/>
+        <v>25912.3122861888</v>
+      </c>
       <c r="M109" t="s">
         <v>166</v>
       </c>
@@ -55220,23 +55575,23 @@
       </c>
       <c r="G110" s="18">
         <f>-(G104)</f>
-        <v>0</v>
+        <v>-1538.8799999999999</v>
       </c>
       <c r="H110" s="18">
         <f>-(H104)</f>
-        <v>0</v>
+        <v>-1631.2128</v>
       </c>
       <c r="I110" s="18">
         <f>-(I104)</f>
-        <v>0</v>
+        <v>-1743.7664832</v>
       </c>
       <c r="J110" s="18">
         <f>-(J104)</f>
-        <v>0</v>
+        <v>-1864.0863705407999</v>
       </c>
       <c r="K110" s="18">
         <f>-(K104)</f>
-        <v>0</v>
+        <v>-1992.708330108115</v>
       </c>
       <c r="M110" t="s">
         <v>161</v>
@@ -55249,11 +55604,26 @@
       <c r="D111" s="67"/>
       <c r="E111" s="67"/>
       <c r="F111" s="67"/>
-      <c r="G111" s="107"/>
-      <c r="H111" s="107"/>
-      <c r="I111" s="107"/>
-      <c r="J111" s="107"/>
-      <c r="K111" s="107"/>
+      <c r="G111" s="107">
+        <f>(-G109-G110+G112)/-1</f>
+        <v>-647.56000000000131</v>
+      </c>
+      <c r="H111" s="107">
+        <f t="shared" ref="H111:K111" si="56">(-H109-H110+H112)/-1</f>
+        <v>-2914.7136000000028</v>
+      </c>
+      <c r="I111" s="107">
+        <f t="shared" si="56"/>
+        <v>-3308.3539583999991</v>
+      </c>
+      <c r="J111" s="107">
+        <f t="shared" si="56"/>
+        <v>-3536.6303815296014</v>
+      </c>
+      <c r="K111" s="107">
+        <f t="shared" si="56"/>
+        <v>-3780.6578778551411</v>
+      </c>
       <c r="M111" t="s">
         <v>167</v>
       </c>
@@ -55263,32 +55633,32 @@
         <v>28</v>
       </c>
       <c r="E112" s="29">
-        <f t="shared" ref="E112:K112" si="33">E50</f>
+        <f t="shared" ref="E112:K112" si="57">E50</f>
         <v>18177</v>
       </c>
       <c r="F112" s="29">
-        <f t="shared" si="33"/>
+        <f t="shared" si="57"/>
         <v>22283</v>
       </c>
       <c r="G112" s="29">
-        <f t="shared" si="33"/>
-        <v>22283.96</v>
+        <f t="shared" si="57"/>
+        <v>21391.68</v>
       </c>
       <c r="H112" s="29">
-        <f t="shared" si="33"/>
-        <v>22285.02</v>
+        <f t="shared" si="57"/>
+        <v>22675.180800000002</v>
       </c>
       <c r="I112" s="29">
-        <f t="shared" si="33"/>
-        <v>22286.089</v>
+        <f t="shared" si="57"/>
+        <v>24239.7682752</v>
       </c>
       <c r="J112" s="29">
-        <f t="shared" si="33"/>
-        <v>22287.157999999999</v>
+        <f t="shared" si="57"/>
+        <v>25912.3122861888</v>
       </c>
       <c r="K112" s="29">
-        <f t="shared" si="33"/>
-        <v>22288.226999999999</v>
+        <f t="shared" si="57"/>
+        <v>27700.261833935827</v>
       </c>
       <c r="M112" t="s">
         <v>168</v>

--- a/Financial Statement Model Online Walk Through.xlsx
+++ b/Financial Statement Model Online Walk Through.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="0" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eipny-my.sharepoint.com/personal/isiaka_energyimpactpartners_com/Documents/Training/Financial Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="729" documentId="13_ncr:1_{DD486496-2B70-447A-98D9-F2E49C8F2BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7308BD00-2584-4386-AF05-C3B1F553024B}"/>
+  <xr:revisionPtr revIDLastSave="907" documentId="13_ncr:1_{DD486496-2B70-447A-98D9-F2E49C8F2BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C03CCFA5-9A1E-41A8-B5A9-36DE499F7131}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="736" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="11260" tabRatio="736" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FSM Data Input_Empty" sheetId="66" r:id="rId1"/>
@@ -83,7 +83,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="12">'Rev Build Complete'!$C$2:$R$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'Rev Build Fill '!$C$2:$Q$41</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcMode="autoNoTable" calcCompleted="0"/>
+  <calcPr calcId="191029" calcMode="autoNoTable"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -3400,8 +3400,30 @@
 </comments>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3432" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3483" uniqueCount="340">
   <si>
     <t>Tax rate</t>
   </si>
@@ -4475,6 +4497,12 @@
   </si>
   <si>
     <t>cashflow free to be distributed</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -6360,7 +6388,7 @@
     <xf numFmtId="233" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="9" fontId="97" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="305">
+  <cellXfs count="304">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -6792,9 +6820,6 @@
     <xf numFmtId="3" fontId="60" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="44" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="37" fontId="2" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
     <xf numFmtId="194" fontId="0" fillId="0" borderId="0" xfId="209" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="194" fontId="1" fillId="0" borderId="0" xfId="209" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="0" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -8931,7 +8956,7 @@
   <sheetPr codeName="Sheet10">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="C1:T219"/>
+  <dimension ref="B1:T219"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="2" width="1.7265625" customWidth="1"/>
@@ -8945,8 +8970,11 @@
     <col min="18" max="19" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:19" ht="15" thickBot="1"/>
-    <row r="2" spans="3:19" ht="15" thickBot="1">
+    <row r="1" spans="2:19" ht="15" thickBot="1"/>
+    <row r="2" spans="2:19" ht="15" thickBot="1">
+      <c r="B2" t="s">
+        <v>338</v>
+      </c>
       <c r="C2" s="63" t="str">
         <f>"Financial Statement Model for "&amp;D5</f>
         <v>Financial Statement Model for Apple</v>
@@ -8960,7 +8988,7 @@
       <c r="J2" s="48"/>
       <c r="K2" s="48"/>
     </row>
-    <row r="3" spans="3:19">
+    <row r="3" spans="2:19">
       <c r="C3" s="2" t="s">
         <v>46</v>
       </c>
@@ -8970,7 +8998,7 @@
       <c r="G3" s="40"/>
       <c r="H3" s="40"/>
     </row>
-    <row r="5" spans="3:19">
+    <row r="5" spans="2:19">
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
@@ -8978,7 +9006,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="3:19">
+    <row r="6" spans="2:19">
       <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
@@ -8986,15 +9014,15 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="3:19">
+    <row r="7" spans="2:19">
       <c r="C7" t="s">
         <v>109</v>
       </c>
       <c r="D7" s="78">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="3:19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19">
       <c r="C8" t="s">
         <v>73</v>
       </c>
@@ -9002,7 +9030,7 @@
         <v>171.25</v>
       </c>
     </row>
-    <row r="9" spans="3:19">
+    <row r="9" spans="2:19">
       <c r="C9" t="s">
         <v>9</v>
       </c>
@@ -9010,7 +9038,7 @@
         <v>43500</v>
       </c>
     </row>
-    <row r="10" spans="3:19">
+    <row r="10" spans="2:19">
       <c r="C10" s="1" t="s">
         <v>8</v>
       </c>
@@ -9018,7 +9046,7 @@
         <v>43372</v>
       </c>
     </row>
-    <row r="11" spans="3:19" ht="15" customHeight="1">
+    <row r="11" spans="2:19" ht="15" customHeight="1">
       <c r="C11" t="s">
         <v>291</v>
       </c>
@@ -9026,7 +9054,7 @@
         <v>4745.3980000000001</v>
       </c>
     </row>
-    <row r="12" spans="3:19">
+    <row r="12" spans="2:19">
       <c r="C12" t="s">
         <v>82</v>
       </c>
@@ -9034,11 +9062,14 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="3:19">
+    <row r="13" spans="2:19">
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
     </row>
-    <row r="14" spans="3:19">
+    <row r="14" spans="2:19">
+      <c r="B14" t="s">
+        <v>338</v>
+      </c>
       <c r="C14" s="5" t="s">
         <v>19</v>
       </c>
@@ -9051,7 +9082,7 @@
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
     </row>
-    <row r="15" spans="3:19">
+    <row r="15" spans="2:19">
       <c r="C15" t="s">
         <v>10</v>
       </c>
@@ -9088,7 +9119,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="16" spans="3:19">
+    <row r="16" spans="2:19">
       <c r="C16" s="10" t="s">
         <v>7</v>
       </c>
@@ -9201,7 +9232,7 @@
       </c>
       <c r="H19" s="15">
         <f>H20-H18</f>
-        <v>-167296.80316800001</v>
+        <v>-167567.07264</v>
       </c>
       <c r="I19" s="15">
         <f>I20-I18</f>
@@ -9241,7 +9272,7 @@
       </c>
       <c r="H20" s="17">
         <f>H18*H38</f>
-        <v>102972.66883200001</v>
+        <v>102702.39936000001</v>
       </c>
       <c r="I20" s="17">
         <f>I18*I38</f>
@@ -9355,7 +9386,7 @@
       </c>
       <c r="H23" s="17">
         <f t="shared" si="0"/>
-        <v>67297.098528000002</v>
+        <v>67026.829056000017</v>
       </c>
       <c r="I23" s="17">
         <f t="shared" si="0"/>
@@ -9387,24 +9418,24 @@
         <v>5686</v>
       </c>
       <c r="G24" s="18">
-        <f ca="1">G157</f>
-        <v>4744.4371106301642</v>
+        <f>G157</f>
+        <v>0</v>
       </c>
       <c r="H24" s="18">
-        <f ca="1">H157</f>
-        <v>4090.2133392642463</v>
+        <f>H157</f>
+        <v>0</v>
       </c>
       <c r="I24" s="18">
-        <f ca="1">I157</f>
-        <v>3592.0870665129901</v>
+        <f>I157</f>
+        <v>0</v>
       </c>
       <c r="J24" s="18">
-        <f ca="1">J157</f>
-        <v>3200.5876330043361</v>
+        <f>J157</f>
+        <v>0</v>
       </c>
       <c r="K24" s="18">
-        <f ca="1">K157</f>
-        <v>2913.259316698618</v>
+        <f>K157</f>
+        <v>0</v>
       </c>
       <c r="M24" t="s">
         <v>95</v>
@@ -9424,24 +9455,24 @@
         <v>-3240</v>
       </c>
       <c r="G25" s="18">
-        <f ca="1">-G143</f>
-        <v>-3223.1468651501777</v>
+        <f>-G143</f>
+        <v>-2961.9392651501776</v>
       </c>
       <c r="H25" s="18">
-        <f ca="1">-H143</f>
-        <v>-3223.5392651501775</v>
+        <f>-H143</f>
+        <v>-2961.9392651501776</v>
       </c>
       <c r="I25" s="18">
-        <f ca="1">-I143</f>
-        <v>-3223.5392651501775</v>
+        <f>-I143</f>
+        <v>-2961.9392651501776</v>
       </c>
       <c r="J25" s="18">
-        <f ca="1">-J143</f>
-        <v>-3223.5392651501775</v>
+        <f>-J143</f>
+        <v>-2961.9392651501776</v>
       </c>
       <c r="K25" s="18">
-        <f ca="1">-K143</f>
-        <v>-3223.5392651501775</v>
+        <f>-K143</f>
+        <v>-2961.9392651501776</v>
       </c>
       <c r="M25" t="s">
         <v>94</v>
@@ -9501,24 +9532,24 @@
         <v>72903</v>
       </c>
       <c r="G27" s="17">
-        <f ca="1">SUM(G23:G26)</f>
-        <v>62783.320645479995</v>
+        <f>SUM(G23:G26)</f>
+        <v>58300.091134849827</v>
       </c>
       <c r="H27" s="17">
-        <f t="shared" ca="1" si="1"/>
-        <v>67722.77260211407</v>
+        <f t="shared" si="1"/>
+        <v>63623.88979084984</v>
       </c>
       <c r="I27" s="17">
-        <f t="shared" ca="1" si="1"/>
-        <v>72157.064193362821</v>
+        <f t="shared" si="1"/>
+        <v>68826.577126849821</v>
       </c>
       <c r="J27" s="17">
-        <f t="shared" ca="1" si="1"/>
-        <v>76749.40139090216</v>
+        <f t="shared" si="1"/>
+        <v>73810.413757897812</v>
       </c>
       <c r="K27" s="17">
-        <f t="shared" ca="1" si="1"/>
-        <v>81789.794433186747</v>
+        <f t="shared" si="1"/>
+        <v>79138.13511648812</v>
       </c>
       <c r="M27" s="16" t="s">
         <v>96</v>
@@ -9539,24 +9570,24 @@
         <v>-13372</v>
       </c>
       <c r="G28" s="15">
-        <f ca="1">-G41*G27</f>
-        <v>-10484.81454779516</v>
+        <f>-G41*G27</f>
+        <v>-9736.1152195199211</v>
       </c>
       <c r="H28" s="15">
-        <f ca="1">-H41*H27</f>
-        <v>-11512.871342359393</v>
+        <f>-H41*H27</f>
+        <v>-10816.061264444474</v>
       </c>
       <c r="I28" s="15">
-        <f ca="1">-I41*I27</f>
-        <v>-12194.543848678317</v>
+        <f>-I41*I27</f>
+        <v>-11631.691534437621</v>
       </c>
       <c r="J28" s="15">
-        <f ca="1">-J41*J27</f>
-        <v>-12970.648835062466</v>
+        <f>-J41*J27</f>
+        <v>-12473.959925084731</v>
       </c>
       <c r="K28" s="15">
-        <f ca="1">-K41*K27</f>
-        <v>-13822.475259208561</v>
+        <f>-K41*K27</f>
+        <v>-13374.344834686493</v>
       </c>
       <c r="M28" t="s">
         <v>92</v>
@@ -9579,24 +9610,24 @@
         <v>59531</v>
       </c>
       <c r="G29" s="17">
-        <f ca="1">SUM(G27:G28)</f>
-        <v>52298.506097684833</v>
+        <f>SUM(G27:G28)</f>
+        <v>48563.975915329909</v>
       </c>
       <c r="H29" s="17">
-        <f t="shared" ca="1" si="2"/>
-        <v>56209.901259754675</v>
+        <f t="shared" si="2"/>
+        <v>52807.82852640537</v>
       </c>
       <c r="I29" s="17">
-        <f t="shared" ca="1" si="2"/>
-        <v>59962.520344684504</v>
+        <f t="shared" si="2"/>
+        <v>57194.885592412204</v>
       </c>
       <c r="J29" s="17">
-        <f t="shared" ca="1" si="2"/>
-        <v>63778.752555839696</v>
+        <f t="shared" si="2"/>
+        <v>61336.45383281308</v>
       </c>
       <c r="K29" s="17">
-        <f t="shared" ca="1" si="2"/>
-        <v>67967.319173978191</v>
+        <f t="shared" si="2"/>
+        <v>65763.79028180163</v>
       </c>
       <c r="M29" s="16" t="s">
         <v>93</v>
@@ -9672,7 +9703,7 @@
       </c>
       <c r="H32" s="17">
         <f t="shared" si="3"/>
-        <v>79008.989272865918</v>
+        <v>78738.719800865932</v>
       </c>
       <c r="I32" s="17">
         <f t="shared" si="3"/>
@@ -9690,7 +9721,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="33" spans="3:20">
+    <row r="33" spans="2:20">
       <c r="C33" s="28" t="s">
         <v>74</v>
       </c>
@@ -9727,7 +9758,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="34" spans="3:20">
+    <row r="34" spans="2:20">
       <c r="C34" s="27" t="s">
         <v>72</v>
       </c>
@@ -9749,7 +9780,7 @@
       </c>
       <c r="H34" s="17">
         <f t="shared" si="4"/>
-        <v>84442.973272865915</v>
+        <v>84172.703800865929</v>
       </c>
       <c r="I34" s="17">
         <f t="shared" si="4"/>
@@ -9767,16 +9798,16 @@
         <v>98</v>
       </c>
     </row>
-    <row r="35" spans="3:20">
+    <row r="35" spans="2:20">
       <c r="C35" s="20"/>
       <c r="G35" s="38"/>
     </row>
-    <row r="36" spans="3:20">
+    <row r="36" spans="2:20">
       <c r="C36" s="19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="3:20">
+    <row r="37" spans="2:20">
       <c r="C37" s="20" t="s">
         <v>1</v>
       </c>
@@ -9790,20 +9821,23 @@
         <v>0.15861957650261305</v>
       </c>
       <c r="G37" s="159">
+        <f>G175</f>
         <v>-0.04</v>
       </c>
       <c r="H37" s="159">
+        <f t="shared" ref="H37:K37" si="5">H175</f>
         <v>0.06</v>
       </c>
       <c r="I37" s="159">
+        <f t="shared" si="5"/>
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="J37" s="95">
-        <f>I37</f>
+        <f t="shared" si="5"/>
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="K37" s="95">
-        <f t="shared" ref="K37:K41" si="5">J37</f>
+        <f t="shared" si="5"/>
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="M37" t="s">
@@ -9816,7 +9850,7 @@
       <c r="S37" s="22"/>
       <c r="T37" s="22"/>
     </row>
-    <row r="38" spans="3:20">
+    <row r="38" spans="2:20">
       <c r="C38" s="20" t="s">
         <v>230</v>
       </c>
@@ -9833,20 +9867,23 @@
         <v>0.38343718820007905</v>
       </c>
       <c r="G38" s="159">
+        <f t="shared" ref="G38:K41" si="6">G176</f>
         <v>0.378</v>
       </c>
       <c r="H38" s="159">
-        <v>0.38100000000000001</v>
+        <f t="shared" si="6"/>
+        <v>0.38</v>
       </c>
       <c r="I38" s="159">
+        <f t="shared" si="6"/>
         <v>0.38200000000000001</v>
       </c>
       <c r="J38" s="95">
-        <f t="shared" ref="J38" si="6">I38</f>
+        <f t="shared" si="6"/>
         <v>0.38200000000000001</v>
       </c>
       <c r="K38" s="95">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.38200000000000001</v>
       </c>
       <c r="M38" t="s">
@@ -9859,7 +9896,7 @@
       <c r="S38" s="22"/>
       <c r="T38" s="22"/>
     </row>
-    <row r="39" spans="3:20">
+    <row r="39" spans="2:20">
       <c r="C39" s="20" t="s">
         <v>231</v>
       </c>
@@ -9876,20 +9913,23 @@
         <v>5.3600406634161032E-2</v>
       </c>
       <c r="G39" s="159">
+        <f t="shared" si="6"/>
         <v>6.2E-2</v>
       </c>
       <c r="H39" s="159">
+        <f t="shared" si="6"/>
         <v>6.3E-2</v>
       </c>
       <c r="I39" s="159">
+        <f t="shared" si="6"/>
         <v>6.3E-2</v>
       </c>
       <c r="J39" s="95">
-        <f t="shared" ref="J39" si="7">I39</f>
+        <f t="shared" si="6"/>
         <v>6.3E-2</v>
       </c>
       <c r="K39" s="95">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6.3E-2</v>
       </c>
       <c r="M39" t="s">
@@ -9902,7 +9942,7 @@
       <c r="S39" s="22"/>
       <c r="T39" s="22"/>
     </row>
-    <row r="40" spans="3:20">
+    <row r="40" spans="2:20">
       <c r="C40" s="20" t="s">
         <v>233</v>
       </c>
@@ -9919,20 +9959,23 @@
         <v>6.2896515371147807E-2</v>
       </c>
       <c r="G40" s="159">
+        <f t="shared" si="6"/>
         <v>7.3999999999999996E-2</v>
       </c>
       <c r="H40" s="159">
+        <f t="shared" si="6"/>
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="I40" s="159">
+        <f t="shared" si="6"/>
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="J40" s="95">
-        <f t="shared" ref="J40" si="8">I40</f>
+        <f t="shared" si="6"/>
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="K40" s="95">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="M40" t="s">
@@ -9945,7 +9988,7 @@
       <c r="S40" s="22"/>
       <c r="T40" s="22"/>
     </row>
-    <row r="41" spans="3:20">
+    <row r="41" spans="2:20">
       <c r="C41" s="20" t="s">
         <v>0</v>
       </c>
@@ -9971,11 +10014,10 @@
         <v>0.16900000000000001</v>
       </c>
       <c r="J41" s="95">
-        <f t="shared" ref="J41" si="9">I41</f>
+        <f>$I41</f>
         <v>0.16900000000000001</v>
       </c>
       <c r="K41" s="95">
-        <f t="shared" si="5"/>
         <v>0.16900000000000001</v>
       </c>
       <c r="M41" t="s">
@@ -9988,11 +10030,14 @@
       <c r="S41" s="22"/>
       <c r="T41" s="22"/>
     </row>
-    <row r="42" spans="3:20">
+    <row r="42" spans="2:20">
       <c r="C42" s="20"/>
       <c r="G42" s="38"/>
     </row>
-    <row r="43" spans="3:20">
+    <row r="43" spans="2:20">
+      <c r="B43" t="s">
+        <v>338</v>
+      </c>
       <c r="C43" s="5" t="s">
         <v>20</v>
       </c>
@@ -10005,77 +10050,77 @@
       <c r="J43" s="7"/>
       <c r="K43" s="7"/>
     </row>
-    <row r="44" spans="3:20">
+    <row r="44" spans="2:20">
       <c r="C44" s="26" t="str">
         <f>C15</f>
         <v xml:space="preserve">Fiscal year  </v>
       </c>
       <c r="D44" s="23"/>
       <c r="E44" s="23">
-        <f t="shared" ref="E44:K45" si="10">E15</f>
+        <f t="shared" ref="E44:K45" si="7">E15</f>
         <v>2017</v>
       </c>
       <c r="F44" s="23">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>2018</v>
       </c>
       <c r="G44" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>2019</v>
       </c>
       <c r="H44" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>2020</v>
       </c>
       <c r="I44" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>2021</v>
       </c>
       <c r="J44" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>2022</v>
       </c>
       <c r="K44" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>2023</v>
       </c>
     </row>
-    <row r="45" spans="3:20">
+    <row r="45" spans="2:20">
       <c r="C45" s="7" t="str">
         <f>C16</f>
         <v>Fiscal year end date</v>
       </c>
       <c r="D45" s="25"/>
       <c r="E45" s="25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>43008</v>
       </c>
       <c r="F45" s="25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>43372</v>
       </c>
       <c r="G45" s="25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>43738</v>
       </c>
       <c r="H45" s="25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>44104</v>
       </c>
       <c r="I45" s="25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>44469</v>
       </c>
       <c r="J45" s="25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>44834</v>
       </c>
       <c r="K45" s="25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>45199</v>
       </c>
     </row>
-    <row r="46" spans="3:20">
+    <row r="46" spans="2:20">
       <c r="C46" t="s">
         <v>138</v>
       </c>
@@ -10089,30 +10134,30 @@
         <v>237100</v>
       </c>
       <c r="G46" s="18">
-        <f ca="1">G91+F46</f>
-        <v>202199.73246575586</v>
+        <f>G91+F46</f>
+        <v>198465.20228340095</v>
       </c>
       <c r="H46" s="18">
-        <f ca="1">H91+G46</f>
-        <v>176523.72487352614</v>
+        <f>H91+G46</f>
+        <v>169472.83261404157</v>
       </c>
       <c r="I46" s="18">
-        <f ca="1">I91+H46</f>
-        <v>156076.92943323214</v>
+        <f>I91+H46</f>
+        <v>146172.69176525564</v>
       </c>
       <c r="J46" s="18">
-        <f ca="1">J91+I46</f>
-        <v>140273.77732642859</v>
+        <f>J91+I46</f>
+        <v>127927.24093542548</v>
       </c>
       <c r="K46" s="18">
-        <f ca="1">K91+J46</f>
-        <v>129472.4557012212</v>
+        <f>K91+J46</f>
+        <v>114922.39041804151</v>
       </c>
       <c r="M46" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="47" spans="3:20">
+    <row r="47" spans="2:20">
       <c r="C47" t="s">
         <v>54</v>
       </c>
@@ -10147,7 +10192,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="48" spans="3:20">
+    <row r="48" spans="2:20">
       <c r="C48" t="s">
         <v>55</v>
       </c>
@@ -10164,7 +10209,7 @@
       </c>
       <c r="H48" s="18">
         <f>G48*H19/G19</f>
-        <v>4041.5383456643303</v>
+        <v>4048.0674867720268</v>
       </c>
       <c r="I48" s="18">
         <f>H48*I19/H19</f>
@@ -10182,7 +10227,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="49" spans="3:13">
+    <row r="49" spans="2:13">
       <c r="C49" t="s">
         <v>108</v>
       </c>
@@ -10219,7 +10264,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="50" spans="3:13">
+    <row r="50" spans="2:13">
       <c r="C50" t="s">
         <v>21</v>
       </c>
@@ -10254,7 +10299,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="51" spans="3:13">
+    <row r="51" spans="2:13">
       <c r="C51" t="s">
         <v>56</v>
       </c>
@@ -10289,41 +10334,44 @@
         <v>103</v>
       </c>
     </row>
-    <row r="52" spans="3:13">
+    <row r="52" spans="2:13">
+      <c r="B52" t="s">
+        <v>316</v>
+      </c>
       <c r="C52" s="27" t="s">
         <v>22</v>
       </c>
       <c r="D52" s="17"/>
       <c r="E52" s="17">
-        <f t="shared" ref="E52:K52" si="11">SUM(E46:E51)</f>
+        <f t="shared" ref="E52:K52" si="8">SUM(E46:E51)</f>
         <v>375319</v>
       </c>
       <c r="F52" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>365725</v>
       </c>
       <c r="G52" s="29">
-        <f t="shared" ca="1" si="11"/>
-        <v>331104.24301995453</v>
+        <f t="shared" si="8"/>
+        <v>327369.71283759963</v>
       </c>
       <c r="H52" s="29">
-        <f t="shared" ca="1" si="11"/>
-        <v>314008.66910306341</v>
+        <f t="shared" si="8"/>
+        <v>306964.30598468648</v>
       </c>
       <c r="I52" s="29">
-        <f t="shared" ca="1" si="11"/>
-        <v>303023.56956485298</v>
+        <f t="shared" si="8"/>
+        <v>293119.33189687651</v>
       </c>
       <c r="J52" s="29">
-        <f t="shared" ca="1" si="11"/>
-        <v>297046.49980922102</v>
+        <f t="shared" si="8"/>
+        <v>284699.9634182179</v>
       </c>
       <c r="K52" s="29">
-        <f t="shared" ca="1" si="11"/>
-        <v>296433.42393223592</v>
-      </c>
-    </row>
-    <row r="53" spans="3:13">
+        <f t="shared" si="8"/>
+        <v>281883.35864905623</v>
+      </c>
+    </row>
+    <row r="53" spans="2:13">
       <c r="C53" s="28"/>
       <c r="D53" s="18"/>
       <c r="E53" s="18"/>
@@ -10334,7 +10382,7 @@
       <c r="J53" s="18"/>
       <c r="K53" s="18"/>
     </row>
-    <row r="54" spans="3:13">
+    <row r="54" spans="2:13">
       <c r="C54" s="28" t="s">
         <v>57</v>
       </c>
@@ -10351,11 +10399,11 @@
       </c>
       <c r="H54" s="18">
         <f>G54*H19/G19</f>
-        <v>57096.434545623881</v>
+        <v>57188.674342951221</v>
       </c>
       <c r="I54" s="18">
         <f>H54*I19/H19</f>
-        <v>60937.484185928995</v>
+        <v>60937.484185929003</v>
       </c>
       <c r="J54" s="18">
         <f>I54*J19/I19</f>
@@ -10369,7 +10417,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="55" spans="3:13">
+    <row r="55" spans="2:13">
       <c r="C55" s="28" t="s">
         <v>117</v>
       </c>
@@ -10404,7 +10452,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="56" spans="3:13">
+    <row r="56" spans="2:13">
       <c r="C56" s="28" t="s">
         <v>58</v>
       </c>
@@ -10441,7 +10489,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="57" spans="3:13">
+    <row r="57" spans="2:13">
       <c r="C57" s="28" t="s">
         <v>60</v>
       </c>
@@ -10453,30 +10501,30 @@
         <v>11964</v>
       </c>
       <c r="G57" s="18">
-        <f ca="1">G136</f>
+        <f>G136</f>
         <v>12000</v>
       </c>
       <c r="H57" s="18">
-        <f ca="1">H136</f>
+        <f>H136</f>
         <v>12000</v>
       </c>
       <c r="I57" s="18">
-        <f ca="1">I136</f>
+        <f>I136</f>
         <v>12000</v>
       </c>
       <c r="J57" s="18">
-        <f ca="1">J136</f>
+        <f>J136</f>
         <v>12000</v>
       </c>
       <c r="K57" s="18">
-        <f ca="1">K136</f>
+        <f>K136</f>
         <v>12000</v>
       </c>
       <c r="M57" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="58" spans="3:13">
+    <row r="58" spans="2:13">
       <c r="C58" s="28" t="s">
         <v>122</v>
       </c>
@@ -10494,26 +10542,26 @@
         <v>102519</v>
       </c>
       <c r="H58" s="18">
-        <f t="shared" ref="H58:K58" si="12">G58</f>
+        <f t="shared" ref="H58:K58" si="9">G58</f>
         <v>102519</v>
       </c>
       <c r="I58" s="18">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>102519</v>
       </c>
       <c r="J58" s="18">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>102519</v>
       </c>
       <c r="K58" s="18">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>102519</v>
       </c>
       <c r="M58" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="3:13" ht="15.75" customHeight="1">
+    <row r="59" spans="2:13" ht="15.75" customHeight="1">
       <c r="C59" s="28" t="s">
         <v>59</v>
       </c>
@@ -10529,60 +10577,63 @@
         <v>43372.799999999996</v>
       </c>
       <c r="H59" s="18">
-        <f t="shared" ref="H59:K59" si="13">G59*(1+H37)</f>
+        <f t="shared" ref="H59:K59" si="10">G59*(1+H37)</f>
         <v>45975.167999999998</v>
       </c>
       <c r="I59" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>49147.454591999995</v>
       </c>
       <c r="J59" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>52538.628958847992</v>
       </c>
       <c r="K59" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>56163.794357008504</v>
       </c>
       <c r="M59" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="60" spans="3:13">
+    <row r="60" spans="2:13">
+      <c r="B60" t="s">
+        <v>316</v>
+      </c>
       <c r="C60" s="27" t="s">
         <v>24</v>
       </c>
       <c r="D60" s="17"/>
       <c r="E60" s="17">
-        <f t="shared" ref="E60:K60" si="14">SUM(E54:E59)</f>
+        <f t="shared" ref="E60:K60" si="11">SUM(E54:E59)</f>
         <v>241272</v>
       </c>
       <c r="F60" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>258578</v>
       </c>
       <c r="G60" s="29">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" si="11"/>
         <v>253323.33692226969</v>
       </c>
       <c r="H60" s="29">
-        <f t="shared" ca="1" si="14"/>
-        <v>261374.87774562387</v>
+        <f t="shared" si="11"/>
+        <v>261467.11754295122</v>
       </c>
       <c r="I60" s="29">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" si="11"/>
         <v>271409.32896672899</v>
       </c>
       <c r="J60" s="29">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" si="11"/>
         <v>282234.7616654333</v>
       </c>
       <c r="K60" s="29">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" si="11"/>
         <v>293807.14922034822</v>
       </c>
     </row>
-    <row r="61" spans="3:13">
+    <row r="61" spans="2:13">
       <c r="C61" s="27"/>
       <c r="D61" s="17"/>
       <c r="E61" s="17"/>
@@ -10593,7 +10644,7 @@
       <c r="J61" s="18"/>
       <c r="K61" s="18"/>
     </row>
-    <row r="62" spans="3:13">
+    <row r="62" spans="2:13">
       <c r="C62" s="28" t="s">
         <v>61</v>
       </c>
@@ -10628,7 +10679,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="63" spans="3:13" ht="15.75" customHeight="1">
+    <row r="63" spans="2:13" ht="15.75" customHeight="1">
       <c r="C63" s="28" t="s">
         <v>44</v>
       </c>
@@ -10641,30 +10692,30 @@
         <v>70400</v>
       </c>
       <c r="G63" s="18">
-        <f ca="1">G120</f>
-        <v>35907.506097684833</v>
+        <f>G120</f>
+        <v>32172.975915329909</v>
       </c>
       <c r="H63" s="18">
-        <f ca="1">H120</f>
-        <v>5326.4073574395152</v>
+        <f>H120</f>
+        <v>-1810.1955582647206</v>
       </c>
       <c r="I63" s="18">
-        <f ca="1">I120</f>
-        <v>-21502.07229787598</v>
+        <f>I120</f>
+        <v>-31406.309965852517</v>
       </c>
       <c r="J63" s="18">
-        <f ca="1">J120</f>
-        <v>-44514.319742036285</v>
+        <f>J120</f>
+        <v>-56860.856133039437</v>
       </c>
       <c r="K63" s="18">
-        <f ca="1">K120</f>
-        <v>-63338.000568058094</v>
+        <f>K120</f>
+        <v>-77888.0658512378</v>
       </c>
       <c r="M63" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="64" spans="3:13" ht="15.75" customHeight="1">
+    <row r="64" spans="2:13" ht="15.75" customHeight="1">
       <c r="C64" s="28" t="s">
         <v>121</v>
       </c>
@@ -10699,80 +10750,83 @@
         <v>100</v>
       </c>
     </row>
-    <row r="65" spans="3:13">
+    <row r="65" spans="2:13">
+      <c r="B65" t="s">
+        <v>316</v>
+      </c>
       <c r="C65" s="27" t="s">
         <v>25</v>
       </c>
       <c r="D65" s="29"/>
       <c r="E65" s="29">
-        <f t="shared" ref="E65:K65" si="15">SUM(E62:E64)</f>
+        <f t="shared" ref="E65:K65" si="12">SUM(E62:E64)</f>
         <v>134047</v>
       </c>
       <c r="F65" s="29">
-        <f t="shared" si="15"/>
+        <f t="shared" si="12"/>
         <v>107147</v>
       </c>
       <c r="G65" s="29">
-        <f t="shared" ca="1" si="15"/>
-        <v>77780.906097684841</v>
+        <f t="shared" si="12"/>
+        <v>74046.375915329903</v>
       </c>
       <c r="H65" s="29">
-        <f t="shared" ca="1" si="15"/>
-        <v>52633.791357439513</v>
+        <f t="shared" si="12"/>
+        <v>45497.188441735278</v>
       </c>
       <c r="I65" s="29">
-        <f t="shared" ca="1" si="15"/>
-        <v>31614.240598124015</v>
+        <f t="shared" si="12"/>
+        <v>21710.002930147479</v>
       </c>
       <c r="J65" s="29">
-        <f t="shared" ca="1" si="15"/>
-        <v>14811.738143787712</v>
+        <f t="shared" si="12"/>
+        <v>2465.2017527845601</v>
       </c>
       <c r="K65" s="29">
-        <f t="shared" ca="1" si="15"/>
-        <v>2626.2747118877596</v>
-      </c>
-    </row>
-    <row r="66" spans="3:13">
+        <f t="shared" si="12"/>
+        <v>-11923.790571291946</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13">
       <c r="D66" s="18"/>
       <c r="E66" s="18"/>
       <c r="F66" s="18"/>
     </row>
-    <row r="67" spans="3:13">
+    <row r="67" spans="2:13">
       <c r="C67" s="12" t="s">
         <v>26</v>
       </c>
       <c r="D67" s="30"/>
       <c r="E67" s="30">
-        <f t="shared" ref="E67:K67" si="16">ROUND(E52-E60-E65,3)</f>
+        <f t="shared" ref="E67:K67" si="13">ROUND(E52-E60-E65,3)</f>
         <v>0</v>
       </c>
       <c r="F67" s="30">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G67" s="30">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H67" s="30">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I67" s="30">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J67" s="30">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="K67" s="30">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="3:13">
+    <row r="68" spans="2:13">
       <c r="E68" s="18"/>
       <c r="F68" s="18"/>
       <c r="H68" s="18"/>
@@ -10780,7 +10834,10 @@
       <c r="J68" s="18"/>
       <c r="K68" s="18"/>
     </row>
-    <row r="69" spans="3:13">
+    <row r="69" spans="2:13">
+      <c r="B69" t="s">
+        <v>338</v>
+      </c>
       <c r="C69" s="5" t="s">
         <v>32</v>
       </c>
@@ -10793,7 +10850,7 @@
       <c r="J69" s="11"/>
       <c r="K69" s="11"/>
     </row>
-    <row r="70" spans="3:13">
+    <row r="70" spans="2:13">
       <c r="C70" s="26" t="str">
         <f>C15</f>
         <v xml:space="preserve">Fiscal year  </v>
@@ -10802,27 +10859,27 @@
       <c r="E70" s="23"/>
       <c r="F70" s="23"/>
       <c r="G70" s="24">
-        <f t="shared" ref="G70:K71" si="17">G15</f>
+        <f t="shared" ref="G70:K71" si="14">G15</f>
         <v>2019</v>
       </c>
       <c r="H70" s="24">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>2020</v>
       </c>
       <c r="I70" s="24">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>2021</v>
       </c>
       <c r="J70" s="24">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>2022</v>
       </c>
       <c r="K70" s="24">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>2023</v>
       </c>
     </row>
-    <row r="71" spans="3:13">
+    <row r="71" spans="2:13">
       <c r="C71" s="7" t="str">
         <f>C16</f>
         <v>Fiscal year end date</v>
@@ -10831,27 +10888,27 @@
       <c r="E71" s="25"/>
       <c r="F71" s="25"/>
       <c r="G71" s="25">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>43738</v>
       </c>
       <c r="H71" s="25">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>44104</v>
       </c>
       <c r="I71" s="25">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>44469</v>
       </c>
       <c r="J71" s="25">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>44834</v>
       </c>
       <c r="K71" s="25">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v>45199</v>
       </c>
     </row>
-    <row r="73" spans="3:13">
+    <row r="73" spans="2:13">
       <c r="C73" t="s">
         <v>2</v>
       </c>
@@ -10859,28 +10916,28 @@
       <c r="E73" s="34"/>
       <c r="F73" s="34"/>
       <c r="G73" s="18">
-        <f ca="1">G29</f>
-        <v>52298.506097684833</v>
+        <f>G29</f>
+        <v>48563.975915329909</v>
       </c>
       <c r="H73" s="18">
-        <f ca="1">H29</f>
-        <v>56209.901259754675</v>
+        <f>H29</f>
+        <v>52807.82852640537</v>
       </c>
       <c r="I73" s="18">
-        <f ca="1">I29</f>
-        <v>59962.520344684504</v>
+        <f>I29</f>
+        <v>57194.885592412204</v>
       </c>
       <c r="J73" s="18">
-        <f ca="1">J29</f>
-        <v>63778.752555839696</v>
+        <f>J29</f>
+        <v>61336.45383281308</v>
       </c>
       <c r="K73" s="18">
-        <f ca="1">K29</f>
-        <v>67967.319173978191</v>
+        <f>K29</f>
+        <v>65763.79028180163</v>
       </c>
       <c r="M73" s="16"/>
     </row>
-    <row r="74" spans="3:13">
+    <row r="74" spans="2:13">
       <c r="C74" t="s">
         <v>33</v>
       </c>
@@ -10911,7 +10968,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="75" spans="3:13">
+    <row r="75" spans="2:13">
       <c r="C75" t="s">
         <v>74</v>
       </c>
@@ -10939,7 +10996,7 @@
         <v>6638.2173941218552</v>
       </c>
     </row>
-    <row r="76" spans="3:13">
+    <row r="76" spans="2:13">
       <c r="C76" t="s">
         <v>65</v>
       </c>
@@ -10952,11 +11009,11 @@
       </c>
       <c r="H76" s="18">
         <f>-1*(SUM(H47:H49)-SUM(G47:G49))</f>
-        <v>-3728.6108202044925</v>
+        <v>-3735.1399613121976</v>
       </c>
       <c r="I76" s="18">
         <f>-1*(SUM(I47:I49)-SUM(H47:H49))</f>
-        <v>-4560.7224748067092</v>
+        <v>-4554.1933336990041</v>
       </c>
       <c r="J76" s="18">
         <f>-1*(SUM(J47:J49)-SUM(I47:I49))</f>
@@ -10967,7 +11024,7 @@
         <v>-5219.277023853967</v>
       </c>
     </row>
-    <row r="77" spans="3:13">
+    <row r="77" spans="2:13">
       <c r="C77" t="s">
         <v>66</v>
       </c>
@@ -10980,22 +11037,22 @@
       </c>
       <c r="H77" s="18">
         <f>SUM(H54:H56)-SUM(G54:G56)</f>
-        <v>5449.1728233541653</v>
+        <v>5541.4126206815126</v>
       </c>
       <c r="I77" s="18">
         <f>SUM(I54:I56)-SUM(H54:H56)</f>
-        <v>6862.1646291051147</v>
+        <v>6769.9248317777819</v>
       </c>
       <c r="J77" s="18">
         <f>SUM(J54:J56)-SUM(I54:I56)</f>
-        <v>7434.2583318562974</v>
+        <v>7434.2583318562829</v>
       </c>
       <c r="K77" s="18">
         <f>SUM(K54:K56)-SUM(J54:J56)</f>
         <v>7947.2221567544038</v>
       </c>
     </row>
-    <row r="78" spans="3:13">
+    <row r="78" spans="2:13">
       <c r="C78" t="s">
         <v>56</v>
       </c>
@@ -11023,7 +11080,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="79" spans="3:13">
+    <row r="79" spans="2:13">
       <c r="C79" t="s">
         <v>59</v>
       </c>
@@ -11049,39 +11106,39 @@
       </c>
       <c r="M79" s="16"/>
     </row>
-    <row r="80" spans="3:13">
+    <row r="80" spans="2:13">
       <c r="C80" s="16" t="s">
         <v>34</v>
       </c>
       <c r="G80" s="29">
-        <f ca="1">SUM(G73:G79)</f>
-        <v>65139.732465755871</v>
+        <f>SUM(G73:G79)</f>
+        <v>61405.202283400962</v>
       </c>
       <c r="H80" s="29">
-        <f ca="1">SUM(H73:H79)</f>
-        <v>74763.992407770274</v>
+        <f>SUM(H73:H79)</f>
+        <v>71447.630330640619</v>
       </c>
       <c r="I80" s="29">
-        <f ca="1">SUM(I73:I79)</f>
-        <v>80163.204559706006</v>
+        <f>SUM(I73:I79)</f>
+        <v>77309.85915121407</v>
       </c>
       <c r="J80" s="29">
-        <f ca="1">SUM(J73:J79)</f>
-        <v>85760.358893196448</v>
+        <f>SUM(J73:J79)</f>
+        <v>83318.060170169832</v>
       </c>
       <c r="K80" s="29">
-        <f ca="1">SUM(K73:K79)</f>
-        <v>91781.492633792601</v>
-      </c>
-    </row>
-    <row r="81" spans="3:13">
+        <f>SUM(K73:K79)</f>
+        <v>89577.963741616026</v>
+      </c>
+    </row>
+    <row r="81" spans="2:13">
       <c r="G81" s="18"/>
       <c r="H81" s="18"/>
       <c r="I81" s="18"/>
       <c r="J81" s="18"/>
       <c r="K81" s="18"/>
     </row>
-    <row r="82" spans="3:13">
+    <row r="82" spans="2:13">
       <c r="C82" t="s">
         <v>35</v>
       </c>
@@ -11109,7 +11166,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="83" spans="3:13">
+    <row r="83" spans="2:13">
       <c r="C83" s="16" t="s">
         <v>36</v>
       </c>
@@ -11134,14 +11191,14 @@
         <v>-15791.814258999997</v>
       </c>
     </row>
-    <row r="84" spans="3:13">
+    <row r="84" spans="2:13">
       <c r="G84" s="18"/>
       <c r="H84" s="18"/>
       <c r="I84" s="18"/>
       <c r="J84" s="18"/>
       <c r="K84" s="18"/>
     </row>
-    <row r="85" spans="3:13">
+    <row r="85" spans="2:13">
       <c r="C85" t="s">
         <v>67</v>
       </c>
@@ -11166,35 +11223,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="3:13">
+    <row r="86" spans="2:13">
       <c r="C86" t="s">
         <v>23</v>
       </c>
       <c r="G86" s="18">
-        <f ca="1">G57-F57</f>
+        <f>G57-F57</f>
         <v>36</v>
       </c>
       <c r="H86" s="18">
-        <f ca="1">H57-G57</f>
+        <f>H57-G57</f>
         <v>0</v>
       </c>
       <c r="I86" s="18">
-        <f ca="1">I57-H57</f>
+        <f>I57-H57</f>
         <v>0</v>
       </c>
       <c r="J86" s="18">
-        <f ca="1">J57-I57</f>
+        <f>J57-I57</f>
         <v>0</v>
       </c>
       <c r="K86" s="18">
-        <f ca="1">K57-J57</f>
+        <f>K57-J57</f>
         <v>0</v>
       </c>
       <c r="M86" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="87" spans="3:13">
+    <row r="87" spans="2:13">
       <c r="C87" t="s">
         <v>70</v>
       </c>
@@ -11222,7 +11279,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="88" spans="3:13">
+    <row r="88" spans="2:13">
       <c r="C88" t="s">
         <v>71</v>
       </c>
@@ -11250,64 +11307,67 @@
         <v>107</v>
       </c>
     </row>
-    <row r="89" spans="3:13">
+    <row r="89" spans="2:13">
       <c r="C89" s="16" t="s">
         <v>37</v>
       </c>
       <c r="G89" s="29">
-        <f ca="1">SUM(G85:G88)</f>
+        <f>SUM(G85:G88)</f>
         <v>-86755</v>
       </c>
       <c r="H89" s="29">
-        <f ca="1">SUM(H85:H88)</f>
+        <f>SUM(H85:H88)</f>
         <v>-86791</v>
       </c>
       <c r="I89" s="29">
-        <f ca="1">SUM(I85:I88)</f>
+        <f>SUM(I85:I88)</f>
         <v>-86791</v>
       </c>
       <c r="J89" s="29">
-        <f ca="1">SUM(J85:J88)</f>
+        <f>SUM(J85:J88)</f>
         <v>-86791</v>
       </c>
       <c r="K89" s="29">
-        <f ca="1">SUM(K85:K88)</f>
+        <f>SUM(K85:K88)</f>
         <v>-86791</v>
       </c>
     </row>
-    <row r="90" spans="3:13">
+    <row r="90" spans="2:13">
       <c r="G90" s="18"/>
       <c r="H90" s="18"/>
       <c r="I90" s="18"/>
       <c r="J90" s="18"/>
       <c r="K90" s="18"/>
     </row>
-    <row r="91" spans="3:13">
+    <row r="91" spans="2:13">
       <c r="C91" s="16" t="s">
         <v>38</v>
       </c>
       <c r="G91" s="29">
-        <f ca="1">G80+G83+G89</f>
-        <v>-34900.267534244129</v>
+        <f>G80+G83+G89</f>
+        <v>-38634.797716599038</v>
       </c>
       <c r="H91" s="29">
-        <f ca="1">H80+H83+H89</f>
-        <v>-25676.007592229726</v>
+        <f>H80+H83+H89</f>
+        <v>-28992.369669359381</v>
       </c>
       <c r="I91" s="29">
-        <f ca="1">I80+I83+I89</f>
-        <v>-20446.795440293994</v>
+        <f>I80+I83+I89</f>
+        <v>-23300.14084878593</v>
       </c>
       <c r="J91" s="29">
-        <f ca="1">J80+J83+J89</f>
-        <v>-15803.152106803551</v>
+        <f>J80+J83+J89</f>
+        <v>-18245.450829830166</v>
       </c>
       <c r="K91" s="29">
-        <f ca="1">K80+K83+K89</f>
-        <v>-10801.321625207391</v>
-      </c>
-    </row>
-    <row r="93" spans="3:13">
+        <f>K80+K83+K89</f>
+        <v>-13004.850517383966</v>
+      </c>
+    </row>
+    <row r="93" spans="2:13">
+      <c r="B93" t="s">
+        <v>338</v>
+      </c>
       <c r="C93" s="5" t="s">
         <v>29</v>
       </c>
@@ -11320,83 +11380,83 @@
       <c r="J93" s="7"/>
       <c r="K93" s="7"/>
     </row>
-    <row r="94" spans="3:13">
+    <row r="94" spans="2:13">
       <c r="C94" s="26" t="str">
-        <f t="shared" ref="C94:K94" si="18">C15</f>
+        <f t="shared" ref="C94:K94" si="15">C15</f>
         <v xml:space="preserve">Fiscal year  </v>
       </c>
       <c r="D94" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>2016</v>
       </c>
       <c r="E94" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>2017</v>
       </c>
       <c r="F94" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>2018</v>
       </c>
       <c r="G94" s="24">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>2019</v>
       </c>
       <c r="H94" s="24">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>2020</v>
       </c>
       <c r="I94" s="24">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>2021</v>
       </c>
       <c r="J94" s="24">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>2022</v>
       </c>
       <c r="K94" s="24">
-        <f t="shared" si="18"/>
+        <f t="shared" si="15"/>
         <v>2023</v>
       </c>
     </row>
-    <row r="95" spans="3:13">
+    <row r="95" spans="2:13">
       <c r="C95" s="7" t="str">
-        <f t="shared" ref="C95:K95" si="19">C16</f>
+        <f t="shared" ref="C95:K95" si="16">C16</f>
         <v>Fiscal year end date</v>
       </c>
       <c r="D95" s="25">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>42643</v>
       </c>
       <c r="E95" s="25">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>43008</v>
       </c>
       <c r="F95" s="25">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>43372</v>
       </c>
       <c r="G95" s="25">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>43738</v>
       </c>
       <c r="H95" s="25">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>44104</v>
       </c>
       <c r="I95" s="25">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>44469</v>
       </c>
       <c r="J95" s="25">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>44834</v>
       </c>
       <c r="K95" s="25">
-        <f t="shared" si="19"/>
+        <f t="shared" si="16"/>
         <v>45199</v>
       </c>
     </row>
-    <row r="96" spans="3:13">
+    <row r="96" spans="2:13">
       <c r="C96" s="16"/>
       <c r="G96" s="76" t="s">
         <v>116</v>
@@ -11406,7 +11466,7 @@
       <c r="J96" s="76"/>
       <c r="K96" s="76"/>
     </row>
-    <row r="97" spans="3:17">
+    <row r="97" spans="2:17">
       <c r="C97" s="28" t="s">
         <v>27</v>
       </c>
@@ -11434,7 +11494,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="98" spans="3:17">
+    <row r="98" spans="2:17">
       <c r="C98" s="31" t="s">
         <v>30</v>
       </c>
@@ -11461,14 +11521,14 @@
         <v>14772.510999999999</v>
       </c>
       <c r="K98" s="3">
-        <f t="shared" ref="K98" si="20">J98*(1+K37)</f>
+        <f t="shared" ref="K98" si="17">J98*(1+K37)</f>
         <v>15791.814258999997</v>
       </c>
       <c r="M98" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="99" spans="3:17">
+    <row r="99" spans="2:17">
       <c r="C99" s="69" t="s">
         <v>31</v>
       </c>
@@ -11505,7 +11565,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="100" spans="3:17">
+    <row r="100" spans="2:17">
       <c r="C100" s="35" t="s">
         <v>28</v>
       </c>
@@ -11542,13 +11602,13 @@
         <v>164</v>
       </c>
     </row>
-    <row r="101" spans="3:17">
+    <row r="101" spans="2:17">
       <c r="C101" s="28"/>
       <c r="M101" s="19" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="102" spans="3:17">
+    <row r="102" spans="2:17">
       <c r="C102" s="28" t="s">
         <v>123</v>
       </c>
@@ -11591,7 +11651,7 @@
       <c r="P102" s="65"/>
       <c r="Q102" s="65"/>
     </row>
-    <row r="103" spans="3:17">
+    <row r="103" spans="2:17">
       <c r="C103" s="28"/>
       <c r="D103" s="4"/>
       <c r="E103" s="4"/>
@@ -11605,7 +11665,10 @@
       <c r="P103" s="65"/>
       <c r="Q103" s="65"/>
     </row>
-    <row r="104" spans="3:17">
+    <row r="104" spans="2:17">
+      <c r="B104" t="s">
+        <v>338</v>
+      </c>
       <c r="C104" s="90" t="s">
         <v>130</v>
       </c>
@@ -11621,7 +11684,7 @@
       <c r="P104" s="65"/>
       <c r="Q104" s="65"/>
     </row>
-    <row r="105" spans="3:17">
+    <row r="105" spans="2:17">
       <c r="C105" s="28" t="s">
         <v>155</v>
       </c>
@@ -11664,7 +11727,7 @@
       <c r="P105" s="65"/>
       <c r="Q105" s="65"/>
     </row>
-    <row r="106" spans="3:17">
+    <row r="106" spans="2:17">
       <c r="C106" s="20" t="s">
         <v>156</v>
       </c>
@@ -11704,7 +11767,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="107" spans="3:17">
+    <row r="107" spans="2:17">
       <c r="C107" s="27" t="s">
         <v>110</v>
       </c>
@@ -11744,7 +11807,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="108" spans="3:17">
+    <row r="108" spans="2:17">
       <c r="C108" s="28"/>
       <c r="D108" s="18"/>
       <c r="E108" s="18"/>
@@ -11754,7 +11817,10 @@
       <c r="J108" s="18"/>
       <c r="K108" s="18"/>
     </row>
-    <row r="109" spans="3:17">
+    <row r="109" spans="2:17">
+      <c r="B109" t="s">
+        <v>338</v>
+      </c>
       <c r="C109" s="42" t="s">
         <v>129</v>
       </c>
@@ -11766,7 +11832,7 @@
       <c r="J109" s="18"/>
       <c r="K109" s="18"/>
     </row>
-    <row r="110" spans="3:17">
+    <row r="110" spans="2:17">
       <c r="C110" s="28" t="s">
         <v>27</v>
       </c>
@@ -11795,7 +11861,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="111" spans="3:17">
+    <row r="111" spans="2:17">
       <c r="C111" s="20" t="s">
         <v>124</v>
       </c>
@@ -11823,7 +11889,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="112" spans="3:17" ht="15" customHeight="1">
+    <row r="112" spans="2:17" ht="15" customHeight="1">
       <c r="C112" s="70" t="s">
         <v>125</v>
       </c>
@@ -11854,43 +11920,43 @@
         <v>167</v>
       </c>
     </row>
-    <row r="113" spans="3:17">
+    <row r="113" spans="2:17">
       <c r="C113" s="35" t="s">
         <v>28</v>
       </c>
       <c r="E113" s="29">
-        <f t="shared" ref="E113:K113" si="21">E51</f>
+        <f t="shared" ref="E113:K113" si="18">E51</f>
         <v>18177</v>
       </c>
       <c r="F113" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>22283</v>
       </c>
       <c r="G113" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>21391.68</v>
       </c>
       <c r="H113" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>22675.180800000002</v>
       </c>
       <c r="I113" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>24239.7682752</v>
       </c>
       <c r="J113" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>25912.3122861888</v>
       </c>
       <c r="K113" s="29">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>27700.261833935827</v>
       </c>
       <c r="M113" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="114" spans="3:17">
+    <row r="114" spans="2:17">
       <c r="C114" s="20"/>
       <c r="E114" s="18"/>
       <c r="F114" s="18"/>
@@ -11899,7 +11965,10 @@
       <c r="J114" s="18"/>
       <c r="K114" s="18"/>
     </row>
-    <row r="115" spans="3:17">
+    <row r="115" spans="2:17">
+      <c r="B115" t="s">
+        <v>338</v>
+      </c>
       <c r="C115" s="43" t="s">
         <v>75</v>
       </c>
@@ -11912,7 +11981,7 @@
       <c r="J115" s="7"/>
       <c r="K115" s="7"/>
     </row>
-    <row r="116" spans="3:17">
+    <row r="116" spans="2:17">
       <c r="C116" s="28" t="s">
         <v>27</v>
       </c>
@@ -11921,66 +11990,66 @@
         <v>70400</v>
       </c>
       <c r="H116" s="18">
-        <f ca="1">G120</f>
-        <v>35907.506097684833</v>
+        <f>G120</f>
+        <v>32172.975915329909</v>
       </c>
       <c r="I116" s="18">
-        <f ca="1">H120</f>
-        <v>5326.4073574395152</v>
+        <f>H120</f>
+        <v>-1810.1955582647206</v>
       </c>
       <c r="J116" s="18">
-        <f ca="1">I120</f>
-        <v>-21502.07229787598</v>
+        <f>I120</f>
+        <v>-31406.309965852517</v>
       </c>
       <c r="K116" s="18">
-        <f ca="1">J120</f>
-        <v>-44514.319742036285</v>
+        <f>J120</f>
+        <v>-56860.856133039437</v>
       </c>
       <c r="M116" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="117" spans="3:17">
+    <row r="117" spans="2:17">
       <c r="C117" s="20" t="s">
         <v>62</v>
       </c>
       <c r="D117" s="15">
-        <f t="shared" ref="D117:K117" si="22">D29</f>
+        <f t="shared" ref="D117:K117" si="19">D29</f>
         <v>45687</v>
       </c>
       <c r="E117" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>48351</v>
       </c>
       <c r="F117" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>59531</v>
       </c>
       <c r="G117" s="18">
-        <f t="shared" ca="1" si="22"/>
-        <v>52298.506097684833</v>
+        <f t="shared" si="19"/>
+        <v>48563.975915329909</v>
       </c>
       <c r="H117" s="18">
-        <f t="shared" ca="1" si="22"/>
-        <v>56209.901259754675</v>
+        <f t="shared" si="19"/>
+        <v>52807.82852640537</v>
       </c>
       <c r="I117" s="18">
-        <f t="shared" ca="1" si="22"/>
-        <v>59962.520344684504</v>
+        <f t="shared" si="19"/>
+        <v>57194.885592412204</v>
       </c>
       <c r="J117" s="18">
-        <f t="shared" ca="1" si="22"/>
-        <v>63778.752555839696</v>
+        <f t="shared" si="19"/>
+        <v>61336.45383281308</v>
       </c>
       <c r="K117" s="18">
-        <f t="shared" ca="1" si="22"/>
-        <v>67967.319173978191</v>
+        <f t="shared" si="19"/>
+        <v>65763.79028180163</v>
       </c>
       <c r="M117" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="118" spans="3:17">
+    <row r="118" spans="2:17">
       <c r="C118" s="20" t="s">
         <v>63</v>
       </c>
@@ -12002,22 +12071,22 @@
         <v>-13735</v>
       </c>
       <c r="I118" s="18">
-        <f t="shared" ref="I118:K119" si="23">H118</f>
+        <f t="shared" ref="I118:K119" si="20">H118</f>
         <v>-13735</v>
       </c>
       <c r="J118" s="18">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-13735</v>
       </c>
       <c r="K118" s="18">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-13735</v>
       </c>
       <c r="M118" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="119" spans="3:17">
+    <row r="119" spans="2:17">
       <c r="C119" s="70" t="s">
         <v>64</v>
       </c>
@@ -12039,22 +12108,22 @@
         <v>-73056</v>
       </c>
       <c r="I119" s="68">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-73056</v>
       </c>
       <c r="J119" s="68">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-73056</v>
       </c>
       <c r="K119" s="68">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>-73056</v>
       </c>
       <c r="M119" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="120" spans="3:17">
+    <row r="120" spans="2:17">
       <c r="C120" s="35" t="s">
         <v>28</v>
       </c>
@@ -12071,34 +12140,37 @@
         <v>70400</v>
       </c>
       <c r="G120" s="29">
-        <f ca="1">SUM(G116:G119)</f>
-        <v>35907.506097684833</v>
+        <f>SUM(G116:G119)</f>
+        <v>32172.975915329909</v>
       </c>
       <c r="H120" s="29">
-        <f ca="1">SUM(H116:H119)</f>
-        <v>5326.4073574395152</v>
+        <f>SUM(H116:H119)</f>
+        <v>-1810.1955582647206</v>
       </c>
       <c r="I120" s="29">
-        <f ca="1">SUM(I116:I119)</f>
-        <v>-21502.07229787598</v>
+        <f>SUM(I116:I119)</f>
+        <v>-31406.309965852517</v>
       </c>
       <c r="J120" s="29">
-        <f ca="1">SUM(J116:J119)</f>
-        <v>-44514.319742036285</v>
+        <f>SUM(J116:J119)</f>
+        <v>-56860.856133039437</v>
       </c>
       <c r="K120" s="29">
-        <f ca="1">SUM(K116:K119)</f>
-        <v>-63338.000568058094</v>
+        <f>SUM(K116:K119)</f>
+        <v>-77888.0658512378</v>
       </c>
       <c r="M120" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="121" spans="3:17">
+    <row r="121" spans="2:17">
       <c r="E121" s="34"/>
       <c r="F121" s="34"/>
     </row>
-    <row r="122" spans="3:17">
+    <row r="122" spans="2:17">
+      <c r="B122" t="s">
+        <v>316</v>
+      </c>
       <c r="C122" s="5" t="s">
         <v>131</v>
       </c>
@@ -12113,92 +12185,92 @@
       <c r="O122" s="65"/>
       <c r="P122" s="65"/>
     </row>
-    <row r="123" spans="3:17">
+    <row r="123" spans="2:17">
       <c r="C123" s="26" t="str">
-        <f t="shared" ref="C123:K123" si="24">C15</f>
+        <f t="shared" ref="C123:K123" si="21">C15</f>
         <v xml:space="preserve">Fiscal year  </v>
       </c>
       <c r="D123" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>2016</v>
       </c>
       <c r="E123" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>2017</v>
       </c>
       <c r="F123" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>2018</v>
       </c>
       <c r="G123" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>2019</v>
       </c>
       <c r="H123" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>2020</v>
       </c>
       <c r="I123" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>2021</v>
       </c>
       <c r="J123" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>2022</v>
       </c>
       <c r="K123" s="24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>2023</v>
       </c>
       <c r="O123" s="65"/>
       <c r="P123" s="65"/>
     </row>
-    <row r="124" spans="3:17">
+    <row r="124" spans="2:17">
       <c r="C124" s="7" t="str">
-        <f t="shared" ref="C124:K124" si="25">C16</f>
+        <f t="shared" ref="C124:K124" si="22">C16</f>
         <v>Fiscal year end date</v>
       </c>
       <c r="D124" s="25">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>42643</v>
       </c>
       <c r="E124" s="25">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>43008</v>
       </c>
       <c r="F124" s="25">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>43372</v>
       </c>
       <c r="G124" s="25">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>43738</v>
       </c>
       <c r="H124" s="25">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>44104</v>
       </c>
       <c r="I124" s="25">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>44469</v>
       </c>
       <c r="J124" s="25">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>44834</v>
       </c>
       <c r="K124" s="25">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>45199</v>
       </c>
       <c r="O124" s="65"/>
       <c r="P124" s="65"/>
     </row>
-    <row r="125" spans="3:17">
+    <row r="125" spans="2:17">
       <c r="C125" s="16"/>
       <c r="O125" s="65"/>
       <c r="P125" s="65"/>
     </row>
-    <row r="126" spans="3:17">
+    <row r="126" spans="2:17">
       <c r="C126" s="19" t="s">
         <v>39</v>
       </c>
@@ -12206,7 +12278,7 @@
       <c r="P126" s="65"/>
       <c r="Q126" s="65"/>
     </row>
-    <row r="127" spans="3:17">
+    <row r="127" spans="2:17">
       <c r="C127" s="20" t="s">
         <v>45</v>
       </c>
@@ -12215,20 +12287,20 @@
         <v>237100</v>
       </c>
       <c r="H127" s="18">
-        <f ca="1">G46</f>
-        <v>202199.73246575586</v>
+        <f>G46</f>
+        <v>198465.20228340095</v>
       </c>
       <c r="I127" s="18">
-        <f ca="1">H46</f>
-        <v>176523.72487352614</v>
+        <f>H46</f>
+        <v>169472.83261404157</v>
       </c>
       <c r="J127" s="18">
-        <f ca="1">I46</f>
-        <v>156076.92943323214</v>
+        <f>I46</f>
+        <v>146172.69176525564</v>
       </c>
       <c r="K127" s="18">
-        <f ca="1">J46</f>
-        <v>140273.77732642859</v>
+        <f>J46</f>
+        <v>127927.24093542548</v>
       </c>
       <c r="M127" t="s">
         <v>171</v>
@@ -12236,7 +12308,7 @@
       <c r="O127" s="65"/>
       <c r="P127" s="65"/>
     </row>
-    <row r="128" spans="3:17">
+    <row r="128" spans="2:17">
       <c r="C128" s="20" t="s">
         <v>69</v>
       </c>
@@ -12261,7 +12333,7 @@
       <c r="O128" s="65"/>
       <c r="P128" s="65"/>
     </row>
-    <row r="129" spans="3:19">
+    <row r="129" spans="2:19">
       <c r="C129" s="70" t="s">
         <v>40</v>
       </c>
@@ -12269,60 +12341,63 @@
       <c r="E129" s="67"/>
       <c r="F129" s="67"/>
       <c r="G129" s="68">
-        <f ca="1">SUM(G80,G83,G85,G87,G88)</f>
-        <v>-34936.267534244129</v>
+        <f>SUM(G80,G83,G85,G87,G88)</f>
+        <v>-38670.797716599038</v>
       </c>
       <c r="H129" s="68">
-        <f ca="1">SUM(H80,H83,H85,H87,H88)</f>
-        <v>-25676.007592229726</v>
+        <f>SUM(H80,H83,H85,H87,H88)</f>
+        <v>-28992.369669359381</v>
       </c>
       <c r="I129" s="68">
-        <f ca="1">SUM(I80,I83,I85,I87,I88)</f>
-        <v>-20446.795440293994</v>
+        <f>SUM(I80,I83,I85,I87,I88)</f>
+        <v>-23300.14084878593</v>
       </c>
       <c r="J129" s="68">
-        <f ca="1">SUM(J80,J83,J85,J87,J88)</f>
-        <v>-15803.152106803551</v>
+        <f>SUM(J80,J83,J85,J87,J88)</f>
+        <v>-18245.450829830166</v>
       </c>
       <c r="K129" s="68">
-        <f ca="1">SUM(K80,K83,K85,K87,K88)</f>
-        <v>-10801.321625207391</v>
+        <f>SUM(K80,K83,K85,K87,K88)</f>
+        <v>-13004.850517383966</v>
       </c>
       <c r="M129" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="130" spans="3:19">
+    <row r="130" spans="2:19">
       <c r="C130" s="35" t="s">
         <v>102</v>
       </c>
       <c r="G130" s="29">
-        <f ca="1">SUM(G127:G129)</f>
-        <v>152163.73246575586</v>
+        <f>SUM(G127:G129)</f>
+        <v>148429.20228340095</v>
       </c>
       <c r="H130" s="29">
-        <f ca="1">SUM(H127:H129)</f>
-        <v>126523.72487352614</v>
+        <f>SUM(H127:H129)</f>
+        <v>119472.83261404157</v>
       </c>
       <c r="I130" s="29">
-        <f ca="1">SUM(I127:I129)</f>
-        <v>106076.92943323214</v>
+        <f>SUM(I127:I129)</f>
+        <v>96172.691765255644</v>
       </c>
       <c r="J130" s="29">
-        <f ca="1">SUM(J127:J129)</f>
-        <v>90273.777326428593</v>
+        <f>SUM(J127:J129)</f>
+        <v>77927.240935425478</v>
       </c>
       <c r="K130" s="29">
-        <f ca="1">SUM(K127:K129)</f>
-        <v>79472.455701221203</v>
-      </c>
-    </row>
-    <row r="132" spans="3:19">
+        <f>SUM(K127:K129)</f>
+        <v>64922.390418041512</v>
+      </c>
+    </row>
+    <row r="132" spans="2:19">
+      <c r="B132" t="s">
+        <v>316</v>
+      </c>
       <c r="C132" s="16" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="133" spans="3:19">
+    <row r="133" spans="2:19">
       <c r="C133" s="20" t="s">
         <v>27</v>
       </c>
@@ -12331,54 +12406,54 @@
         <v>11964</v>
       </c>
       <c r="H133" s="18">
-        <f ca="1">G136</f>
+        <f>G136</f>
         <v>12000</v>
       </c>
       <c r="I133" s="18">
-        <f ca="1">H136</f>
+        <f>H136</f>
         <v>12000</v>
       </c>
       <c r="J133" s="18">
-        <f ca="1">I136</f>
+        <f>I136</f>
         <v>12000</v>
       </c>
       <c r="K133" s="18">
-        <f ca="1">J136</f>
+        <f>J136</f>
         <v>12000</v>
       </c>
       <c r="M133" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="134" spans="3:19">
+    <row r="134" spans="2:19">
       <c r="C134" s="31" t="s">
         <v>175</v>
       </c>
       <c r="G134" s="18">
-        <f ca="1">-MIN(G130,G133)</f>
+        <f>-MIN(G130,G133)</f>
         <v>-11964</v>
       </c>
       <c r="H134" s="18">
-        <f ca="1">-MIN(H130,H133)</f>
+        <f>-MIN(H130,H133)</f>
         <v>-12000</v>
       </c>
       <c r="I134" s="18">
-        <f ca="1">-MIN(I130,I133)</f>
+        <f>-MIN(I130,I133)</f>
         <v>-12000</v>
       </c>
       <c r="J134" s="18">
-        <f ca="1">-MIN(J130,J133)</f>
+        <f>-MIN(J130,J133)</f>
         <v>-12000</v>
       </c>
       <c r="K134" s="18">
-        <f ca="1">-MIN(K130,K133)</f>
+        <f>-MIN(K130,K133)</f>
         <v>-12000</v>
       </c>
       <c r="M134" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="135" spans="3:19">
+    <row r="135" spans="2:19">
       <c r="C135" s="69" t="s">
         <v>128</v>
       </c>
@@ -12404,7 +12479,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="136" spans="3:19">
+    <row r="136" spans="2:19">
       <c r="C136" s="20" t="s">
         <v>28</v>
       </c>
@@ -12421,27 +12496,27 @@
         <v>11964</v>
       </c>
       <c r="G136" s="109">
-        <f ca="1">SUM(G133:G135)</f>
+        <f>SUM(G133:G135)</f>
         <v>12000</v>
       </c>
       <c r="H136" s="109">
-        <f ca="1">SUM(H133:H135)</f>
+        <f>SUM(H133:H135)</f>
         <v>12000</v>
       </c>
       <c r="I136" s="109">
-        <f ca="1">SUM(I133:I135)</f>
+        <f>SUM(I133:I135)</f>
         <v>12000</v>
       </c>
       <c r="J136" s="109">
-        <f ca="1">SUM(J133:J135)</f>
+        <f>SUM(J133:J135)</f>
         <v>12000</v>
       </c>
       <c r="K136" s="109">
-        <f ca="1">SUM(K133:K135)</f>
+        <f>SUM(K133:K135)</f>
         <v>12000</v>
       </c>
     </row>
-    <row r="137" spans="3:19">
+    <row r="137" spans="2:19">
       <c r="C137" s="82" t="s">
         <v>119</v>
       </c>
@@ -12449,28 +12524,28 @@
       <c r="E137" s="87"/>
       <c r="F137" s="88"/>
       <c r="G137" s="83" t="str">
-        <f ca="1">IF(G136&lt;0,"Negative Debt","OK")</f>
+        <f>IF(G136&lt;0,"Negative Debt","OK")</f>
         <v>OK</v>
       </c>
       <c r="H137" s="83" t="str">
-        <f ca="1">IF(H136&lt;0,"Negative Debt","OK")</f>
+        <f>IF(H136&lt;0,"Negative Debt","OK")</f>
         <v>OK</v>
       </c>
       <c r="I137" s="83" t="str">
-        <f ca="1">IF(I136&lt;0,"Negative Debt","OK")</f>
+        <f>IF(I136&lt;0,"Negative Debt","OK")</f>
         <v>OK</v>
       </c>
       <c r="J137" s="83" t="str">
-        <f ca="1">IF(J136&lt;0,"Negative Debt","OK")</f>
+        <f>IF(J136&lt;0,"Negative Debt","OK")</f>
         <v>OK</v>
       </c>
       <c r="K137" s="84" t="str">
-        <f ca="1">IF(K136&lt;0,"Negative Debt","OK")</f>
+        <f>IF(K136&lt;0,"Negative Debt","OK")</f>
         <v>OK</v>
       </c>
       <c r="S137" s="34"/>
     </row>
-    <row r="138" spans="3:19">
+    <row r="138" spans="2:19">
       <c r="D138" s="18"/>
       <c r="E138" s="18"/>
       <c r="F138" s="85"/>
@@ -12481,7 +12556,10 @@
       <c r="K138" s="86"/>
       <c r="S138" s="34"/>
     </row>
-    <row r="139" spans="3:19">
+    <row r="139" spans="2:19">
+      <c r="B139" t="s">
+        <v>338</v>
+      </c>
       <c r="C139" s="5" t="s">
         <v>43</v>
       </c>
@@ -12495,86 +12573,86 @@
       <c r="K139" s="33"/>
       <c r="R139" s="66"/>
     </row>
-    <row r="140" spans="3:19">
+    <row r="140" spans="2:19">
       <c r="C140" s="26" t="str">
-        <f t="shared" ref="C140:K140" si="26">C15</f>
+        <f t="shared" ref="C140:K140" si="23">C15</f>
         <v xml:space="preserve">Fiscal year  </v>
       </c>
       <c r="D140" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>2016</v>
       </c>
       <c r="E140" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>2017</v>
       </c>
       <c r="F140" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>2018</v>
       </c>
       <c r="G140" s="24">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>2019</v>
       </c>
       <c r="H140" s="24">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>2020</v>
       </c>
       <c r="I140" s="24">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>2021</v>
       </c>
       <c r="J140" s="24">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>2022</v>
       </c>
       <c r="K140" s="24">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>2023</v>
       </c>
       <c r="R140" s="66"/>
       <c r="S140" s="34"/>
     </row>
-    <row r="141" spans="3:19">
+    <row r="141" spans="2:19">
       <c r="C141" s="7" t="str">
-        <f t="shared" ref="C141:K141" si="27">C16</f>
+        <f t="shared" ref="C141:K141" si="24">C16</f>
         <v>Fiscal year end date</v>
       </c>
       <c r="D141" s="25">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>42643</v>
       </c>
       <c r="E141" s="25">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>43008</v>
       </c>
       <c r="F141" s="25">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>43372</v>
       </c>
       <c r="G141" s="25">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>43738</v>
       </c>
       <c r="H141" s="25">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>44104</v>
       </c>
       <c r="I141" s="25">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>44469</v>
       </c>
       <c r="J141" s="25">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>44834</v>
       </c>
       <c r="K141" s="25">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>45199</v>
       </c>
       <c r="R141" s="66"/>
     </row>
-    <row r="142" spans="3:19">
+    <row r="142" spans="2:19">
       <c r="C142" s="20"/>
       <c r="D142" s="18"/>
       <c r="E142" s="18"/>
@@ -12586,7 +12664,7 @@
       <c r="K142" s="89"/>
       <c r="R142" s="66"/>
     </row>
-    <row r="143" spans="3:19">
+    <row r="143" spans="2:19">
       <c r="C143" s="28" t="s">
         <v>120</v>
       </c>
@@ -12603,41 +12681,44 @@
         <v>3240</v>
       </c>
       <c r="G143" s="18">
-        <f ca="1">G148+G153</f>
-        <v>3223.1468651501777</v>
+        <f>G148+G153</f>
+        <v>2961.9392651501776</v>
       </c>
       <c r="H143" s="18">
-        <f ca="1">H148+H153</f>
-        <v>3223.5392651501775</v>
+        <f>H148+H153</f>
+        <v>2961.9392651501776</v>
       </c>
       <c r="I143" s="18">
-        <f ca="1">I148+I153</f>
-        <v>3223.5392651501775</v>
+        <f>I148+I153</f>
+        <v>2961.9392651501776</v>
       </c>
       <c r="J143" s="18">
-        <f ca="1">J148+J153</f>
-        <v>3223.5392651501775</v>
+        <f>J148+J153</f>
+        <v>2961.9392651501776</v>
       </c>
       <c r="K143" s="18">
-        <f ca="1">K148+K153</f>
-        <v>3223.5392651501775</v>
+        <f>K148+K153</f>
+        <v>2961.9392651501776</v>
       </c>
       <c r="M143" t="s">
         <v>177</v>
       </c>
       <c r="R143" s="34"/>
     </row>
-    <row r="144" spans="3:19">
+    <row r="144" spans="2:19">
       <c r="C144" s="39"/>
       <c r="R144" s="34"/>
     </row>
-    <row r="145" spans="3:18">
+    <row r="145" spans="2:18">
+      <c r="B145" t="s">
+        <v>316</v>
+      </c>
       <c r="C145" s="61" t="s">
         <v>68</v>
       </c>
       <c r="R145" s="34"/>
     </row>
-    <row r="146" spans="3:18">
+    <row r="146" spans="2:18">
       <c r="C146" s="20" t="s">
         <v>111</v>
       </c>
@@ -12671,44 +12752,44 @@
         <v>132</v>
       </c>
     </row>
-    <row r="147" spans="3:18">
+    <row r="147" spans="2:18">
       <c r="C147" s="20" t="s">
         <v>112</v>
       </c>
       <c r="D147" s="68"/>
       <c r="E147" s="68">
-        <f t="shared" ref="E147:K147" si="28">E57</f>
+        <f t="shared" ref="E147:K147" si="25">E57</f>
         <v>11977</v>
       </c>
       <c r="F147" s="68">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>11964</v>
       </c>
       <c r="G147" s="18">
-        <f t="shared" ca="1" si="28"/>
+        <f t="shared" si="25"/>
         <v>12000</v>
       </c>
       <c r="H147" s="18">
-        <f t="shared" ca="1" si="28"/>
+        <f t="shared" si="25"/>
         <v>12000</v>
       </c>
       <c r="I147" s="18">
-        <f t="shared" ca="1" si="28"/>
+        <f t="shared" si="25"/>
         <v>12000</v>
       </c>
       <c r="J147" s="18">
-        <f t="shared" ca="1" si="28"/>
+        <f t="shared" si="25"/>
         <v>12000</v>
       </c>
       <c r="K147" s="18">
-        <f t="shared" ca="1" si="28"/>
+        <f t="shared" si="25"/>
         <v>12000</v>
       </c>
       <c r="M147" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="148" spans="3:18">
+    <row r="148" spans="2:18">
       <c r="C148" s="111" t="s">
         <v>41</v>
       </c>
@@ -12722,36 +12803,39 @@
         <v>260.95690000000002</v>
       </c>
       <c r="G148" s="112">
-        <f ca="1">IF($D$7=1,AVERAGE(F147:G147)*G146,0)</f>
-        <v>261.20760000000001</v>
+        <f>IF($D$7=1,AVERAGE(F147:G147)*G146,0)</f>
+        <v>0</v>
       </c>
       <c r="H148" s="112">
-        <f ca="1">IF($D$7=1,AVERAGE(G147:H147)*H146,0)</f>
-        <v>261.60000000000002</v>
+        <f>IF($D$7=1,AVERAGE(G147:H147)*H146,0)</f>
+        <v>0</v>
       </c>
       <c r="I148" s="112">
-        <f ca="1">IF($D$7=1,AVERAGE(H147:I147)*I146,0)</f>
-        <v>261.60000000000002</v>
+        <f>IF($D$7=1,AVERAGE(H147:I147)*I146,0)</f>
+        <v>0</v>
       </c>
       <c r="J148" s="112">
-        <f ca="1">IF($D$7=1,AVERAGE(I147:J147)*J146,0)</f>
-        <v>261.60000000000002</v>
+        <f>IF($D$7=1,AVERAGE(I147:J147)*J146,0)</f>
+        <v>0</v>
       </c>
       <c r="K148" s="112">
-        <f ca="1">IF($D$7=1,AVERAGE(J147:K147)*K146,0)</f>
-        <v>261.60000000000002</v>
+        <f>IF($D$7=1,AVERAGE(J147:K147)*K146,0)</f>
+        <v>0</v>
       </c>
       <c r="M148" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="149" spans="3:18">
+    <row r="149" spans="2:18">
       <c r="C149" s="49"/>
       <c r="D149" s="18"/>
       <c r="E149" s="18"/>
       <c r="F149" s="18"/>
     </row>
-    <row r="150" spans="3:18">
+    <row r="150" spans="2:18">
+      <c r="B150" t="s">
+        <v>316</v>
+      </c>
       <c r="C150" s="61" t="s">
         <v>67</v>
       </c>
@@ -12759,49 +12843,49 @@
       <c r="E150" s="18"/>
       <c r="F150" s="18"/>
     </row>
-    <row r="151" spans="3:18">
+    <row r="151" spans="2:18">
       <c r="C151" s="20" t="s">
         <v>112</v>
       </c>
       <c r="D151" s="18"/>
       <c r="E151" s="18">
-        <f t="shared" ref="E151:K151" si="29">E58</f>
+        <f t="shared" ref="E151:K151" si="26">E58</f>
         <v>103703</v>
       </c>
       <c r="F151" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>102519</v>
       </c>
       <c r="G151" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>102519</v>
       </c>
       <c r="H151" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>102519</v>
       </c>
       <c r="I151" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>102519</v>
       </c>
       <c r="J151" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>102519</v>
       </c>
       <c r="K151" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>102519</v>
       </c>
       <c r="M151" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="152" spans="3:18">
+    <row r="152" spans="2:18">
       <c r="C152" s="20" t="s">
         <v>111</v>
       </c>
       <c r="E152" s="60">
-        <f t="shared" ref="E152" si="30">E153/AVERAGE(D151:E151)</f>
+        <f t="shared" ref="E152" si="27">E153/AVERAGE(D151:E151)</f>
         <v>2.101458974185896E-2</v>
       </c>
       <c r="F152" s="60">
@@ -12833,7 +12917,7 @@
       </c>
       <c r="R152" s="66"/>
     </row>
-    <row r="153" spans="3:18">
+    <row r="153" spans="2:18">
       <c r="C153" s="35" t="s">
         <v>185</v>
       </c>
@@ -12870,17 +12954,17 @@
         <v>114</v>
       </c>
     </row>
-    <row r="154" spans="3:18">
+    <row r="154" spans="2:18">
       <c r="E154" s="18"/>
     </row>
-    <row r="155" spans="3:18">
+    <row r="155" spans="2:18">
       <c r="C155" s="39" t="s">
         <v>42</v>
       </c>
       <c r="E155" s="18"/>
       <c r="F155" s="18"/>
     </row>
-    <row r="156" spans="3:18" ht="15" customHeight="1">
+    <row r="156" spans="2:18" ht="15" customHeight="1">
       <c r="C156" s="20" t="s">
         <v>115</v>
       </c>
@@ -12917,7 +13001,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="157" spans="3:18" ht="15" customHeight="1">
+    <row r="157" spans="2:18" ht="15" customHeight="1">
       <c r="C157" s="20" t="s">
         <v>4</v>
       </c>
@@ -12934,30 +13018,30 @@
         <v>5686</v>
       </c>
       <c r="G157" s="15">
-        <f ca="1">IF($D$7=1,AVERAGE(F46,G46)*G156,0)</f>
-        <v>4744.4371106301642</v>
+        <f>IF($D$7=1,AVERAGE(F46,G46)*G156,0)</f>
+        <v>0</v>
       </c>
       <c r="H157" s="15">
-        <f ca="1">IF($D$7=1,AVERAGE(G46,H46)*H156,0)</f>
-        <v>4090.2133392642463</v>
+        <f>IF($D$7=1,AVERAGE(G46,H46)*H156,0)</f>
+        <v>0</v>
       </c>
       <c r="I157" s="15">
-        <f ca="1">IF($D$7=1,AVERAGE(H46,I46)*I156,0)</f>
-        <v>3592.0870665129901</v>
+        <f>IF($D$7=1,AVERAGE(H46,I46)*I156,0)</f>
+        <v>0</v>
       </c>
       <c r="J157" s="15">
-        <f ca="1">IF($D$7=1,AVERAGE(I46,J46)*J156,0)</f>
-        <v>3200.5876330043361</v>
+        <f>IF($D$7=1,AVERAGE(I46,J46)*J156,0)</f>
+        <v>0</v>
       </c>
       <c r="K157" s="15">
-        <f ca="1">IF($D$7=1,AVERAGE(J46,K46)*K156,0)</f>
-        <v>2913.259316698618</v>
+        <f>IF($D$7=1,AVERAGE(J46,K46)*K156,0)</f>
+        <v>0</v>
       </c>
       <c r="M157" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="158" spans="3:18">
+    <row r="158" spans="2:18">
       <c r="C158" s="41"/>
       <c r="D158" s="60"/>
       <c r="E158" s="60"/>
@@ -12965,7 +13049,10 @@
       <c r="G158" s="60"/>
       <c r="H158" s="60"/>
     </row>
-    <row r="159" spans="3:18">
+    <row r="159" spans="2:18">
+      <c r="B159" t="s">
+        <v>316</v>
+      </c>
       <c r="C159" s="5" t="s">
         <v>76</v>
       </c>
@@ -12978,10 +13065,10 @@
       <c r="J159" s="5"/>
       <c r="K159" s="5"/>
     </row>
-    <row r="160" spans="3:18">
+    <row r="160" spans="2:18">
       <c r="C160" s="16"/>
     </row>
-    <row r="161" spans="3:16" ht="15" thickBot="1">
+    <row r="161" spans="2:16" ht="15" thickBot="1">
       <c r="C161" s="44" t="s">
         <v>187</v>
       </c>
@@ -12992,7 +13079,7 @@
       <c r="H161" s="45"/>
       <c r="I161" s="45"/>
     </row>
-    <row r="162" spans="3:16">
+    <row r="162" spans="2:16">
       <c r="E162" s="169" t="s">
         <v>77</v>
       </c>
@@ -13001,72 +13088,161 @@
       <c r="H162" s="46"/>
       <c r="I162" s="46"/>
     </row>
-    <row r="163" spans="3:16" ht="15.75" customHeight="1" thickBot="1">
-      <c r="D163" s="118"/>
-      <c r="E163" s="160"/>
-      <c r="F163" s="160"/>
-      <c r="G163" s="160"/>
-      <c r="H163" s="160"/>
-      <c r="I163" s="160"/>
-    </row>
-    <row r="164" spans="3:16">
-      <c r="D164" s="161"/>
-      <c r="E164" s="162"/>
-      <c r="F164" s="162"/>
-      <c r="G164" s="162"/>
-      <c r="H164" s="162"/>
-      <c r="I164" s="162"/>
-    </row>
-    <row r="165" spans="3:16">
+    <row r="163" spans="2:16" ht="15.75" customHeight="1" thickBot="1">
+      <c r="D163" s="118">
+        <f>G29</f>
+        <v>48563.975915329909</v>
+      </c>
+      <c r="E163" s="160">
+        <v>-0.05</v>
+      </c>
+      <c r="F163" s="160">
+        <v>-2.5000000000000001E-2</v>
+      </c>
+      <c r="G163" s="160">
+        <v>0</v>
+      </c>
+      <c r="H163" s="160">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I163" s="160">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="164" spans="2:16">
+      <c r="D164" s="161">
+        <v>0.39</v>
+      </c>
+      <c r="E164" s="162">
+        <f t="dataTable" ref="E164:I169" dt2D="1" dtr="1" r1="G37" r2="G38"/>
+        <v>50550.716817629902</v>
+      </c>
+      <c r="F164" s="162">
+        <v>51955.594849879904</v>
+      </c>
+      <c r="G164" s="162">
+        <v>53360.472882129907</v>
+      </c>
+      <c r="H164" s="162">
+        <v>54765.350914379902</v>
+      </c>
+      <c r="I164" s="162">
+        <v>56170.228946629904</v>
+      </c>
+    </row>
+    <row r="165" spans="2:16">
       <c r="C165" s="168" t="s">
         <v>78</v>
       </c>
-      <c r="D165" s="161"/>
-      <c r="E165" s="162"/>
-      <c r="F165" s="162"/>
-      <c r="G165" s="162"/>
-      <c r="H165" s="162"/>
-      <c r="I165" s="162"/>
-    </row>
-    <row r="166" spans="3:16">
+      <c r="D165" s="161">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="E165" s="162">
+        <v>49499.823801379891</v>
+      </c>
+      <c r="F165" s="162">
+        <v>50877.046754254909</v>
+      </c>
+      <c r="G165" s="162">
+        <v>52254.269707129904</v>
+      </c>
+      <c r="H165" s="162">
+        <v>53631.492660004908</v>
+      </c>
+      <c r="I165" s="162">
+        <v>55008.715612879903</v>
+      </c>
+    </row>
+    <row r="166" spans="2:16">
       <c r="C166" s="168" t="s">
         <v>79</v>
       </c>
-      <c r="D166" s="161"/>
-      <c r="E166" s="162"/>
-      <c r="F166" s="162"/>
-      <c r="G166" s="162"/>
-      <c r="H166" s="162"/>
-      <c r="I166" s="162"/>
-    </row>
-    <row r="167" spans="3:16">
+      <c r="D166" s="161">
+        <v>0.38</v>
+      </c>
+      <c r="E166" s="162">
+        <v>48448.930785129902</v>
+      </c>
+      <c r="F166" s="162">
+        <v>49798.498658629898</v>
+      </c>
+      <c r="G166" s="162">
+        <v>51148.066532129909</v>
+      </c>
+      <c r="H166" s="162">
+        <v>52497.634405629906</v>
+      </c>
+      <c r="I166" s="162">
+        <v>53847.20227912991</v>
+      </c>
+    </row>
+    <row r="167" spans="2:16">
       <c r="C167" s="168" t="s">
         <v>80</v>
       </c>
-      <c r="D167" s="161"/>
-      <c r="E167" s="162"/>
-      <c r="F167" s="162"/>
-      <c r="G167" s="162"/>
-      <c r="H167" s="162"/>
-      <c r="I167" s="162"/>
-    </row>
-    <row r="168" spans="3:16">
-      <c r="D168" s="161"/>
-      <c r="E168" s="162"/>
-      <c r="F168" s="162"/>
-      <c r="G168" s="162"/>
-      <c r="H168" s="162"/>
-      <c r="I168" s="162"/>
-    </row>
-    <row r="169" spans="3:16">
-      <c r="D169" s="161"/>
-      <c r="E169" s="162"/>
-      <c r="F169" s="162"/>
-      <c r="G169" s="162"/>
-      <c r="H169" s="162"/>
-      <c r="I169" s="162"/>
-    </row>
-    <row r="171" spans="3:16">
+      <c r="D167" s="161">
+        <v>0.375</v>
+      </c>
+      <c r="E167" s="162">
+        <v>47398.037768879891</v>
+      </c>
+      <c r="F167" s="162">
+        <v>48719.950563004903</v>
+      </c>
+      <c r="G167" s="162">
+        <v>50041.8633571299</v>
+      </c>
+      <c r="H167" s="162">
+        <v>51363.776151254904</v>
+      </c>
+      <c r="I167" s="162">
+        <v>52685.688945379916</v>
+      </c>
+    </row>
+    <row r="168" spans="2:16">
+      <c r="D168" s="161">
+        <v>0.37</v>
+      </c>
+      <c r="E168" s="162">
+        <v>46347.144752629909</v>
+      </c>
+      <c r="F168" s="162">
+        <v>47641.402467379907</v>
+      </c>
+      <c r="G168" s="162">
+        <v>48935.660182129897</v>
+      </c>
+      <c r="H168" s="162">
+        <v>50229.917896879902</v>
+      </c>
+      <c r="I168" s="162">
+        <v>51524.175611629915</v>
+      </c>
+    </row>
+    <row r="169" spans="2:16">
+      <c r="D169" s="161">
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="E169" s="162">
+        <v>45296.251736379898</v>
+      </c>
+      <c r="F169" s="162">
+        <v>46562.854371754904</v>
+      </c>
+      <c r="G169" s="162">
+        <v>47829.457007129909</v>
+      </c>
+      <c r="H169" s="162">
+        <v>49096.059642504901</v>
+      </c>
+      <c r="I169" s="162">
+        <v>50362.662277879914</v>
+      </c>
+    </row>
+    <row r="171" spans="2:16">
+      <c r="B171" t="s">
+        <v>316</v>
+      </c>
       <c r="C171" s="5" t="s">
         <v>81</v>
       </c>
@@ -13079,8 +13255,8 @@
       <c r="J171" s="5"/>
       <c r="K171" s="5"/>
     </row>
-    <row r="172" spans="3:16" ht="15" thickBot="1"/>
-    <row r="173" spans="3:16" ht="15" thickBot="1">
+    <row r="172" spans="2:16" ht="15" thickBot="1"/>
+    <row r="173" spans="2:16" ht="15" thickBot="1">
       <c r="C173" t="s">
         <v>192</v>
       </c>
@@ -13096,23 +13272,23 @@
         <v>2019</v>
       </c>
       <c r="H173" s="24">
-        <f t="shared" ref="H173:K174" si="31">H15</f>
+        <f t="shared" ref="H173:K174" si="28">H15</f>
         <v>2020</v>
       </c>
       <c r="I173" s="24">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>2021</v>
       </c>
       <c r="J173" s="24">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>2022</v>
       </c>
       <c r="K173" s="24">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>2023</v>
       </c>
     </row>
-    <row r="174" spans="3:16">
+    <row r="174" spans="2:16">
       <c r="E174" s="127"/>
       <c r="F174" s="121" t="s">
         <v>189</v>
@@ -13122,88 +13298,283 @@
         <v>43738</v>
       </c>
       <c r="H174" s="25">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>44104</v>
       </c>
       <c r="I174" s="25">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>44469</v>
       </c>
       <c r="J174" s="25">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>44834</v>
       </c>
       <c r="K174" s="25">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>45199</v>
       </c>
     </row>
-    <row r="175" spans="3:16">
+    <row r="175" spans="2:16">
       <c r="C175" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="F175" s="157"/>
-      <c r="G175" s="158"/>
-      <c r="H175" s="158"/>
-      <c r="I175" s="158"/>
-      <c r="J175" s="158"/>
-      <c r="K175" s="158"/>
+      <c r="F175" s="157" t="str" cm="1">
+        <f t="array" ref="F175">_xlfn.LET(
+    _xlpm.n, (ROW(A1)-1)*4,
+    _xlpm.fRange, INDEX(F:F, 181 + _xlpm.n):INDEX(F:F, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
+        <v>-</v>
+      </c>
+      <c r="G175" s="158" cm="1">
+        <f t="array" ref="G175">_xlfn.LET(
+    _xlpm.n, (ROW(B1)-1)*4,
+    _xlpm.fRange, INDEX(G:G, 181 + _xlpm.n):INDEX(G:G, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
+        <v>-0.04</v>
+      </c>
+      <c r="H175" s="158" cm="1">
+        <f t="array" ref="H175">_xlfn.LET(
+    _xlpm.n, (ROW(C1)-1)*4,
+    _xlpm.fRange, INDEX(H:H, 181 + _xlpm.n):INDEX(H:H, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
+        <v>0.06</v>
+      </c>
+      <c r="I175" s="158" cm="1">
+        <f t="array" ref="I175">_xlfn.LET(
+    _xlpm.n, (ROW(D1)-1)*4,
+    _xlpm.fRange, INDEX(I:I, 181 + _xlpm.n):INDEX(I:I, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="J175" s="158" cm="1">
+        <f t="array" ref="J175">_xlfn.LET(
+    _xlpm.n, (ROW(E1)-1)*4,
+    _xlpm.fRange, INDEX(J:J, 181 + _xlpm.n):INDEX(J:J, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="K175" s="158" cm="1">
+        <f t="array" ref="K175">_xlfn.LET(
+    _xlpm.n, (ROW(F1)-1)*4,
+    _xlpm.fRange, INDEX(K:K, 181 + _xlpm.n):INDEX(K:K, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
+        <v>6.9000000000000006E-2</v>
+      </c>
       <c r="M175" s="150"/>
       <c r="O175" s="150"/>
       <c r="P175" s="150"/>
     </row>
-    <row r="176" spans="3:16">
+    <row r="176" spans="2:16">
       <c r="C176" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="F176" s="157"/>
-      <c r="G176" s="158"/>
-      <c r="H176" s="158"/>
-      <c r="I176" s="158"/>
-      <c r="J176" s="158"/>
-      <c r="K176" s="158"/>
+      <c r="F176" s="157" t="str" cm="1">
+        <f t="array" ref="F176">_xlfn.LET(
+    _xlpm.n, (ROW(A2)-1)*4,
+    _xlpm.fRange, INDEX(F:F, 181 + _xlpm.n):INDEX(F:F, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX(C:C, 181 + _xlpm.n):INDEX(C:C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
+        <v>-</v>
+      </c>
+      <c r="G176" s="158" cm="1">
+        <f t="array" ref="G176">_xlfn.LET(
+    _xlpm.n, (ROW(B2)-1)*4,
+    _xlpm.fRange, INDEX(G:G, 181 + _xlpm.n):INDEX(G:G, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
+        <v>0.378</v>
+      </c>
+      <c r="H176" s="158" cm="1">
+        <f t="array" ref="H176">_xlfn.LET(
+    _xlpm.n, (ROW(C2)-1)*4,
+    _xlpm.fRange, INDEX(H:H, 181 + _xlpm.n):INDEX(H:H, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
+        <v>0.38</v>
+      </c>
+      <c r="I176" s="158" cm="1">
+        <f t="array" ref="I176">_xlfn.LET(
+    _xlpm.n, (ROW(D2)-1)*4,
+    _xlpm.fRange, INDEX(I:I, 181 + _xlpm.n):INDEX(I:I, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="J176" s="158" cm="1">
+        <f t="array" ref="J176">_xlfn.LET(
+    _xlpm.n, (ROW(E2)-1)*4,
+    _xlpm.fRange, INDEX(J:J, 181 + _xlpm.n):INDEX(J:J, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="K176" s="158" cm="1">
+        <f t="array" ref="K176">_xlfn.LET(
+    _xlpm.n, (ROW(F2)-1)*4,
+    _xlpm.fRange, INDEX(K:K, 181 + _xlpm.n):INDEX(K:K, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
+        <v>0.38200000000000001</v>
+      </c>
       <c r="M176" s="150"/>
       <c r="O176" s="150"/>
       <c r="P176" s="150"/>
     </row>
-    <row r="177" spans="3:19">
+    <row r="177" spans="2:19">
       <c r="C177" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="F177" s="157"/>
-      <c r="G177" s="158"/>
-      <c r="H177" s="158"/>
-      <c r="I177" s="158"/>
-      <c r="J177" s="158"/>
-      <c r="K177" s="158"/>
+      <c r="F177" s="157" t="str" cm="1">
+        <f t="array" ref="F177">_xlfn.LET(
+    _xlpm.n, (ROW(A3)-1)*4,
+    _xlpm.fRange, INDEX(F:F, 181 + _xlpm.n):INDEX(F:F, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX(C:C, 181 + _xlpm.n):INDEX(C:C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
+        <v>-</v>
+      </c>
+      <c r="G177" s="158" cm="1">
+        <f t="array" ref="G177">_xlfn.LET(
+    _xlpm.n, (ROW(B3)-1)*4,
+    _xlpm.fRange, INDEX(G:G, 181 + _xlpm.n):INDEX(G:G, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
+        <v>6.2E-2</v>
+      </c>
+      <c r="H177" s="158" cm="1">
+        <f t="array" ref="H177">_xlfn.LET(
+    _xlpm.n, (ROW(C3)-1)*4,
+    _xlpm.fRange, INDEX(H:H, 181 + _xlpm.n):INDEX(H:H, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
+        <v>6.3E-2</v>
+      </c>
+      <c r="I177" s="158" cm="1">
+        <f t="array" ref="I177">_xlfn.LET(
+    _xlpm.n, (ROW(D3)-1)*4,
+    _xlpm.fRange, INDEX(I:I, 181 + _xlpm.n):INDEX(I:I, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
+        <v>6.3E-2</v>
+      </c>
+      <c r="J177" s="158" cm="1">
+        <f t="array" ref="J177">_xlfn.LET(
+    _xlpm.n, (ROW(E3)-1)*4,
+    _xlpm.fRange, INDEX(J:J, 181 + _xlpm.n):INDEX(J:J, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
+        <v>6.3E-2</v>
+      </c>
+      <c r="K177" s="158" cm="1">
+        <f t="array" ref="K177">_xlfn.LET(
+    _xlpm.n, (ROW(F3)-1)*4,
+    _xlpm.fRange, INDEX(K:K, 181 + _xlpm.n):INDEX(K:K, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
+        <v>6.3E-2</v>
+      </c>
       <c r="M177" s="150"/>
       <c r="O177" s="150"/>
       <c r="P177" s="150"/>
     </row>
-    <row r="178" spans="3:19">
+    <row r="178" spans="2:19">
       <c r="C178" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="F178" s="157"/>
-      <c r="G178" s="158"/>
-      <c r="H178" s="158"/>
-      <c r="I178" s="158"/>
-      <c r="J178" s="158"/>
-      <c r="K178" s="158"/>
+      <c r="F178" s="157" t="str" cm="1">
+        <f t="array" ref="F178">_xlfn.LET(
+    _xlpm.n, (ROW(A4)-1)*4,
+    _xlpm.fRange, INDEX(F:F, 181 + _xlpm.n):INDEX(F:F, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX(C:C, 181 + _xlpm.n):INDEX(C:C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
+        <v>-</v>
+      </c>
+      <c r="G178" s="158" cm="1">
+        <f t="array" ref="G178">_xlfn.LET(
+    _xlpm.n, (ROW(B4)-1)*4,
+    _xlpm.fRange, INDEX(G:G, 181 + _xlpm.n):INDEX(G:G, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="H178" s="158" cm="1">
+        <f t="array" ref="H178">_xlfn.LET(
+    _xlpm.n, (ROW(C4)-1)*4,
+    _xlpm.fRange, INDEX(H:H, 181 + _xlpm.n):INDEX(H:H, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="I178" s="158" cm="1">
+        <f t="array" ref="I178">_xlfn.LET(
+    _xlpm.n, (ROW(D4)-1)*4,
+    _xlpm.fRange, INDEX(I:I, 181 + _xlpm.n):INDEX(I:I, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="J178" s="158" cm="1">
+        <f t="array" ref="J178">_xlfn.LET(
+    _xlpm.n, (ROW(E4)-1)*4,
+    _xlpm.fRange, INDEX(J:J, 181 + _xlpm.n):INDEX(J:J, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="K178" s="158" cm="1">
+        <f t="array" ref="K178">_xlfn.LET(
+    _xlpm.n, (ROW(F4)-1)*4,
+    _xlpm.fRange, INDEX(K:K, 181 + _xlpm.n):INDEX(K:K, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
+        <v>6.9000000000000006E-2</v>
+      </c>
       <c r="M178" s="150"/>
       <c r="O178" s="150"/>
       <c r="P178" s="150"/>
     </row>
-    <row r="179" spans="3:19">
+    <row r="179" spans="2:19">
       <c r="F179" s="122"/>
     </row>
-    <row r="180" spans="3:19">
+    <row r="180" spans="2:19">
+      <c r="B180" t="s">
+        <v>316</v>
+      </c>
       <c r="C180" s="35" t="s">
         <v>1</v>
       </c>
       <c r="F180" s="122"/>
     </row>
-    <row r="181" spans="3:19">
+    <row r="181" spans="2:19">
       <c r="C181" s="49" t="s">
         <v>84</v>
       </c>
@@ -13231,12 +13602,12 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="182" spans="3:19">
+    <row r="182" spans="2:19">
       <c r="C182" s="49" t="s">
         <v>83</v>
       </c>
       <c r="F182" s="124" t="s">
-        <v>188</v>
+        <v>339</v>
       </c>
       <c r="G182" s="22">
         <v>-0.04</v>
@@ -13264,7 +13635,7 @@
       <c r="R182" s="22"/>
       <c r="S182" s="22"/>
     </row>
-    <row r="183" spans="3:19">
+    <row r="183" spans="2:19">
       <c r="C183" s="49" t="s">
         <v>85</v>
       </c>
@@ -13297,7 +13668,10 @@
       <c r="R183" s="22"/>
       <c r="S183" s="22"/>
     </row>
-    <row r="184" spans="3:19">
+    <row r="184" spans="2:19">
+      <c r="B184" t="s">
+        <v>316</v>
+      </c>
       <c r="C184" s="35" t="s">
         <v>230</v>
       </c>
@@ -13313,7 +13687,7 @@
       <c r="R184" s="22"/>
       <c r="S184" s="22"/>
     </row>
-    <row r="185" spans="3:19">
+    <row r="185" spans="2:19">
       <c r="C185" s="49" t="s">
         <v>84</v>
       </c>
@@ -13341,12 +13715,12 @@
         <v>0.39200000000000002</v>
       </c>
     </row>
-    <row r="186" spans="3:19">
+    <row r="186" spans="2:19">
       <c r="C186" s="49" t="s">
         <v>83</v>
       </c>
       <c r="F186" s="124" t="s">
-        <v>188</v>
+        <v>339</v>
       </c>
       <c r="G186" s="22">
         <v>0.378</v>
@@ -13369,7 +13743,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="187" spans="3:19">
+    <row r="187" spans="2:19">
       <c r="C187" s="49" t="s">
         <v>85</v>
       </c>
@@ -13397,7 +13771,10 @@
         <v>0.372</v>
       </c>
     </row>
-    <row r="188" spans="3:19">
+    <row r="188" spans="2:19">
+      <c r="B188" t="s">
+        <v>316</v>
+      </c>
       <c r="C188" s="35" t="s">
         <v>231</v>
       </c>
@@ -13408,7 +13785,7 @@
       <c r="J188" s="50"/>
       <c r="K188" s="50"/>
     </row>
-    <row r="189" spans="3:19">
+    <row r="189" spans="2:19">
       <c r="C189" s="49" t="s">
         <v>84</v>
       </c>
@@ -13436,12 +13813,12 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="190" spans="3:19">
+    <row r="190" spans="2:19">
       <c r="C190" s="49" t="s">
         <v>83</v>
       </c>
       <c r="F190" s="124" t="s">
-        <v>188</v>
+        <v>339</v>
       </c>
       <c r="G190" s="22">
         <v>6.2E-2</v>
@@ -13464,7 +13841,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="191" spans="3:19">
+    <row r="191" spans="2:19">
       <c r="C191" s="49" t="s">
         <v>85</v>
       </c>
@@ -13492,7 +13869,10 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="192" spans="3:19">
+    <row r="192" spans="2:19">
+      <c r="B192" t="s">
+        <v>316</v>
+      </c>
       <c r="C192" s="35" t="s">
         <v>233</v>
       </c>
@@ -13503,7 +13883,7 @@
       <c r="J192" s="50"/>
       <c r="K192" s="50"/>
     </row>
-    <row r="193" spans="3:13">
+    <row r="193" spans="2:13">
       <c r="C193" s="49" t="s">
         <v>84</v>
       </c>
@@ -13531,12 +13911,12 @@
         <v>5.9000000000000004E-2</v>
       </c>
     </row>
-    <row r="194" spans="3:13">
+    <row r="194" spans="2:13">
       <c r="C194" s="49" t="s">
         <v>83</v>
       </c>
       <c r="F194" s="124" t="s">
-        <v>188</v>
+        <v>339</v>
       </c>
       <c r="G194" s="22">
         <v>7.3999999999999996E-2</v>
@@ -13559,7 +13939,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="195" spans="3:13" ht="15" thickBot="1">
+    <row r="195" spans="2:13" ht="15" thickBot="1">
       <c r="C195" s="49" t="s">
         <v>85</v>
       </c>
@@ -13587,7 +13967,10 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="197" spans="3:13">
+    <row r="197" spans="2:13">
+      <c r="B197" t="s">
+        <v>316</v>
+      </c>
       <c r="C197" s="5" t="s">
         <v>213</v>
       </c>
@@ -13600,7 +13983,7 @@
       <c r="J197" s="5"/>
       <c r="K197" s="5"/>
     </row>
-    <row r="198" spans="3:13">
+    <row r="198" spans="2:13">
       <c r="C198" s="26" t="str">
         <f>C15</f>
         <v xml:space="preserve">Fiscal year  </v>
@@ -13610,35 +13993,35 @@
         <v>2016</v>
       </c>
       <c r="E198" s="23">
-        <f t="shared" ref="E198:K199" si="32">E15</f>
+        <f t="shared" ref="E198:K199" si="29">E15</f>
         <v>2017</v>
       </c>
       <c r="F198" s="23">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>2018</v>
       </c>
       <c r="G198" s="24">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>2019</v>
       </c>
       <c r="H198" s="24">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>2020</v>
       </c>
       <c r="I198" s="24">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>2021</v>
       </c>
       <c r="J198" s="24">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>2022</v>
       </c>
       <c r="K198" s="24">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>2023</v>
       </c>
     </row>
-    <row r="199" spans="3:13">
+    <row r="199" spans="2:13">
       <c r="C199" s="7" t="str">
         <f>C16</f>
         <v>Fiscal year end date</v>
@@ -13648,42 +14031,42 @@
         <v>42643</v>
       </c>
       <c r="E199" s="25">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>43008</v>
       </c>
       <c r="F199" s="25">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>43372</v>
       </c>
       <c r="G199" s="25">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>43738</v>
       </c>
       <c r="H199" s="25">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>44104</v>
       </c>
       <c r="I199" s="25">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>44469</v>
       </c>
       <c r="J199" s="25">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>44834</v>
       </c>
       <c r="K199" s="25">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>45199</v>
       </c>
     </row>
-    <row r="200" spans="3:13">
+    <row r="200" spans="2:13">
       <c r="G200" s="22"/>
       <c r="H200" s="22"/>
       <c r="I200" s="22"/>
       <c r="J200" s="21"/>
       <c r="K200" s="21"/>
     </row>
-    <row r="201" spans="3:13">
+    <row r="201" spans="2:13">
       <c r="C201" t="s">
         <v>2</v>
       </c>
@@ -13692,23 +14075,38 @@
         <v>45687</v>
       </c>
       <c r="E201" s="59">
-        <f t="shared" ref="E201:F201" si="33">E29</f>
+        <f t="shared" ref="E201:F201" si="30">E29</f>
         <v>48351</v>
       </c>
       <c r="F201" s="59">
-        <f t="shared" si="33"/>
+        <f t="shared" si="30"/>
         <v>59531</v>
       </c>
-      <c r="G201" s="235"/>
-      <c r="H201" s="235"/>
-      <c r="I201" s="235"/>
-      <c r="J201" s="235"/>
-      <c r="K201" s="235"/>
+      <c r="G201" s="235">
+        <f>G29</f>
+        <v>48563.975915329909</v>
+      </c>
+      <c r="H201" s="235">
+        <f t="shared" ref="H201:K201" si="31">H29</f>
+        <v>52807.82852640537</v>
+      </c>
+      <c r="I201" s="235">
+        <f t="shared" si="31"/>
+        <v>57194.885592412204</v>
+      </c>
+      <c r="J201" s="235">
+        <f t="shared" si="31"/>
+        <v>61336.45383281308</v>
+      </c>
+      <c r="K201" s="235">
+        <f t="shared" si="31"/>
+        <v>65763.79028180163</v>
+      </c>
       <c r="M201" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="202" spans="3:13">
+    <row r="202" spans="2:13">
       <c r="C202" t="s">
         <v>214</v>
       </c>
@@ -13721,47 +14119,80 @@
       <c r="F202" s="58">
         <v>4955.3770000000004</v>
       </c>
-      <c r="G202" s="235"/>
-      <c r="H202" s="235"/>
-      <c r="I202" s="235"/>
-      <c r="J202" s="235"/>
-      <c r="K202" s="235"/>
+      <c r="G202" s="59">
+        <f>F202+(-G208+G209)/G210</f>
+        <v>4577.9903333333341</v>
+      </c>
+      <c r="H202" s="59">
+        <f t="shared" ref="H202:K202" si="32">G202+(-H208+H209)/H210</f>
+        <v>4251.3139275362328</v>
+      </c>
+      <c r="I202" s="59">
+        <f t="shared" si="32"/>
+        <v>3968.822555538753</v>
+      </c>
+      <c r="J202" s="59">
+        <f t="shared" si="32"/>
+        <v>3724.6420125027594</v>
+      </c>
+      <c r="K202" s="59">
+        <f t="shared" si="32"/>
+        <v>3513.6721082249628</v>
+      </c>
       <c r="M202" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="203" spans="3:13">
+    <row r="203" spans="2:13">
       <c r="C203" s="16" t="s">
         <v>215</v>
       </c>
       <c r="D203" s="154">
-        <f t="shared" ref="D203:F203" si="34">D201/D202</f>
+        <f t="shared" ref="D203:F203" si="33">D201/D202</f>
         <v>8.3510333003096431</v>
       </c>
       <c r="E203" s="154">
+        <f t="shared" si="33"/>
+        <v>9.2675402061088974</v>
+      </c>
+      <c r="F203" s="154">
+        <f t="shared" si="33"/>
+        <v>12.0134149228202</v>
+      </c>
+      <c r="G203" s="236">
+        <f>G201/G202</f>
+        <v>10.608142957778904</v>
+      </c>
+      <c r="H203" s="236">
+        <f t="shared" ref="H203:K203" si="34">H201/H202</f>
+        <v>12.421531184597589</v>
+      </c>
+      <c r="I203" s="236">
         <f t="shared" si="34"/>
-        <v>9.2675402061088974</v>
-      </c>
-      <c r="F203" s="154">
+        <v>14.411046296991277</v>
+      </c>
+      <c r="J203" s="236">
         <f t="shared" si="34"/>
-        <v>12.0134149228202</v>
-      </c>
-      <c r="G203" s="236"/>
-      <c r="H203" s="236"/>
-      <c r="I203" s="236"/>
-      <c r="J203" s="236"/>
-      <c r="K203" s="236"/>
+        <v>16.467744719337009</v>
+      </c>
+      <c r="K203" s="236">
+        <f t="shared" si="34"/>
+        <v>18.716541628303556</v>
+      </c>
       <c r="M203" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="204" spans="3:13">
+    <row r="204" spans="2:13">
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
       <c r="F204" s="3"/>
       <c r="G204" s="18"/>
     </row>
-    <row r="205" spans="3:13">
+    <row r="205" spans="2:13">
+      <c r="B205" t="s">
+        <v>316</v>
+      </c>
       <c r="C205" t="s">
         <v>216</v>
       </c>
@@ -13774,16 +14205,31 @@
       <c r="F205" s="58">
         <v>5000.1090000000004</v>
       </c>
-      <c r="G205" s="235"/>
-      <c r="H205" s="235"/>
-      <c r="I205" s="235"/>
-      <c r="J205" s="235"/>
-      <c r="K205" s="235"/>
+      <c r="G205" s="235">
+        <f>(G202+F205)-F202</f>
+        <v>4622.722333333335</v>
+      </c>
+      <c r="H205" s="235">
+        <f t="shared" ref="H205:K205" si="35">(H202+G205)-G202</f>
+        <v>4296.0459275362346</v>
+      </c>
+      <c r="I205" s="235">
+        <f t="shared" si="35"/>
+        <v>4013.5545555387553</v>
+      </c>
+      <c r="J205" s="235">
+        <f t="shared" si="35"/>
+        <v>3769.3740125027612</v>
+      </c>
+      <c r="K205" s="235">
+        <f t="shared" si="35"/>
+        <v>3558.4041082249646</v>
+      </c>
       <c r="M205" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="206" spans="3:13">
+    <row r="206" spans="2:13">
       <c r="C206" s="16" t="s">
         <v>217</v>
       </c>
@@ -13792,67 +14238,124 @@
         <v>8.3063028961611227</v>
       </c>
       <c r="E206" s="154">
-        <f t="shared" ref="E206:F206" si="35">E201/E205</f>
+        <f t="shared" ref="E206:K206" si="36">E201/E205</f>
         <v>9.2067470826545037</v>
       </c>
       <c r="F206" s="154">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>11.905940450498179</v>
       </c>
-      <c r="G206" s="236"/>
-      <c r="H206" s="236"/>
-      <c r="I206" s="236"/>
-      <c r="J206" s="236"/>
-      <c r="K206" s="236"/>
+      <c r="G206" s="154">
+        <f t="shared" si="36"/>
+        <v>10.505492740748627</v>
+      </c>
+      <c r="H206" s="154">
+        <f t="shared" si="36"/>
+        <v>12.292193662997093</v>
+      </c>
+      <c r="I206" s="154">
+        <f t="shared" si="36"/>
+        <v>14.250431830678009</v>
+      </c>
+      <c r="J206" s="154">
+        <f t="shared" si="36"/>
+        <v>16.272318329081745</v>
+      </c>
+      <c r="K206" s="154">
+        <f t="shared" si="36"/>
+        <v>18.481259655077938</v>
+      </c>
       <c r="M206" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="207" spans="3:13">
+    <row r="207" spans="2:13">
       <c r="G207" s="152"/>
     </row>
-    <row r="208" spans="3:13">
+    <row r="208" spans="2:13">
       <c r="C208" t="s">
         <v>223</v>
       </c>
-      <c r="G208" s="235"/>
-      <c r="H208" s="235"/>
-      <c r="I208" s="235"/>
-      <c r="J208" s="235"/>
-      <c r="K208" s="235"/>
+      <c r="G208" s="235">
+        <f xml:space="preserve"> -G119</f>
+        <v>73056</v>
+      </c>
+      <c r="H208" s="235">
+        <f t="shared" ref="H208:K208" si="37" xml:space="preserve"> -H119</f>
+        <v>73056</v>
+      </c>
+      <c r="I208" s="235">
+        <f t="shared" si="37"/>
+        <v>73056</v>
+      </c>
+      <c r="J208" s="235">
+        <f t="shared" si="37"/>
+        <v>73056</v>
+      </c>
+      <c r="K208" s="235">
+        <f t="shared" si="37"/>
+        <v>73056</v>
+      </c>
       <c r="M208" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="209" spans="3:13">
+    <row r="209" spans="2:13">
       <c r="C209" t="s">
         <v>224</v>
       </c>
-      <c r="G209" s="235"/>
-      <c r="H209" s="235"/>
-      <c r="I209" s="235"/>
-      <c r="J209" s="235"/>
-      <c r="K209" s="235"/>
+      <c r="G209" s="235">
+        <f>G33</f>
+        <v>5126.3999999999996</v>
+      </c>
+      <c r="H209" s="235">
+        <f t="shared" ref="H209:K209" si="38">H33</f>
+        <v>5433.9839999999995</v>
+      </c>
+      <c r="I209" s="235">
+        <f t="shared" si="38"/>
+        <v>5808.9288959999994</v>
+      </c>
+      <c r="J209" s="235">
+        <f t="shared" si="38"/>
+        <v>6209.7449898239993</v>
+      </c>
+      <c r="K209" s="235">
+        <f t="shared" si="38"/>
+        <v>6638.2173941218552</v>
+      </c>
       <c r="M209" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="210" spans="3:13">
+    <row r="210" spans="2:13">
       <c r="C210" t="s">
         <v>219</v>
       </c>
       <c r="G210" s="155">
         <v>180</v>
       </c>
-      <c r="H210" s="237"/>
-      <c r="I210" s="237"/>
-      <c r="J210" s="237"/>
-      <c r="K210" s="237"/>
+      <c r="H210" s="237">
+        <f xml:space="preserve"> G210* (1 +H211)</f>
+        <v>206.99999999999997</v>
+      </c>
+      <c r="I210" s="237">
+        <f t="shared" ref="I210:K210" si="39" xml:space="preserve"> H210* (1 +I211)</f>
+        <v>238.04999999999995</v>
+      </c>
+      <c r="J210" s="237">
+        <f t="shared" si="39"/>
+        <v>273.75749999999994</v>
+      </c>
+      <c r="K210" s="237">
+        <f t="shared" si="39"/>
+        <v>314.82112499999988</v>
+      </c>
       <c r="M210" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="211" spans="3:13" ht="15" customHeight="1">
+    <row r="211" spans="2:13" ht="15" customHeight="1">
       <c r="C211" t="s">
         <v>218</v>
       </c>
@@ -13872,12 +14375,15 @@
         <v>299</v>
       </c>
     </row>
-    <row r="212" spans="3:13">
+    <row r="212" spans="2:13">
       <c r="M212" s="19" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="213" spans="3:13">
+    <row r="213" spans="2:13">
+      <c r="B213" t="s">
+        <v>316</v>
+      </c>
       <c r="C213" s="16" t="s">
         <v>294</v>
       </c>
@@ -13895,7 +14401,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="214" spans="3:13">
+    <row r="214" spans="2:13">
       <c r="C214" t="s">
         <v>295</v>
       </c>
@@ -13908,7 +14414,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="215" spans="3:13">
+    <row r="215" spans="2:13">
       <c r="C215" t="s">
         <v>296</v>
       </c>
@@ -13921,7 +14427,10 @@
         <v>305</v>
       </c>
     </row>
-    <row r="216" spans="3:13">
+    <row r="216" spans="2:13">
+      <c r="B216" t="s">
+        <v>316</v>
+      </c>
       <c r="C216" s="16" t="s">
         <v>297</v>
       </c>
@@ -13937,12 +14446,15 @@
         <v>306</v>
       </c>
     </row>
-    <row r="217" spans="3:13">
+    <row r="217" spans="2:13">
       <c r="M217" s="19" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="218" spans="3:13">
+    <row r="218" spans="2:13">
+      <c r="B218" t="s">
+        <v>316</v>
+      </c>
       <c r="C218" s="16" t="s">
         <v>2</v>
       </c>
@@ -13958,7 +14470,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="219" spans="3:13" ht="15" customHeight="1">
+    <row r="219" spans="2:13" ht="15" customHeight="1">
       <c r="C219" s="20" t="s">
         <v>298</v>
       </c>
@@ -14011,7 +14523,7 @@
   <sheetPr codeName="Sheet11">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="C1:T222"/>
+  <dimension ref="B1:T222"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="2" width="1.7265625" customWidth="1"/>
@@ -14025,8 +14537,11 @@
     <col min="18" max="19" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:19" ht="15" thickBot="1"/>
-    <row r="2" spans="3:19" ht="15" thickBot="1">
+    <row r="1" spans="2:19" ht="15" thickBot="1"/>
+    <row r="2" spans="2:19" ht="15" thickBot="1">
+      <c r="B2" t="s">
+        <v>316</v>
+      </c>
       <c r="C2" s="63" t="str">
         <f>"Financial Statement Model for "&amp;D5</f>
         <v>Financial Statement Model for Apple</v>
@@ -14040,7 +14555,7 @@
       <c r="J2" s="48"/>
       <c r="K2" s="48"/>
     </row>
-    <row r="3" spans="3:19">
+    <row r="3" spans="2:19">
       <c r="C3" s="2" t="s">
         <v>46</v>
       </c>
@@ -14050,7 +14565,7 @@
       <c r="G3" s="40"/>
       <c r="H3" s="40"/>
     </row>
-    <row r="5" spans="3:19">
+    <row r="5" spans="2:19">
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
@@ -14058,7 +14573,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="3:19">
+    <row r="6" spans="2:19">
       <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
@@ -14066,7 +14581,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="3:19">
+    <row r="7" spans="2:19">
       <c r="C7" t="s">
         <v>109</v>
       </c>
@@ -14074,7 +14589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="3:19">
+    <row r="8" spans="2:19">
       <c r="C8" t="s">
         <v>73</v>
       </c>
@@ -14082,7 +14597,7 @@
         <v>171.25</v>
       </c>
     </row>
-    <row r="9" spans="3:19">
+    <row r="9" spans="2:19">
       <c r="C9" t="s">
         <v>9</v>
       </c>
@@ -14090,7 +14605,7 @@
         <v>43500</v>
       </c>
     </row>
-    <row r="10" spans="3:19">
+    <row r="10" spans="2:19">
       <c r="C10" s="1" t="s">
         <v>8</v>
       </c>
@@ -14098,7 +14613,7 @@
         <v>43372</v>
       </c>
     </row>
-    <row r="11" spans="3:19" ht="15" customHeight="1">
+    <row r="11" spans="2:19" ht="15" customHeight="1">
       <c r="C11" t="s">
         <v>291</v>
       </c>
@@ -14106,7 +14621,7 @@
         <v>4745.3980000000001</v>
       </c>
     </row>
-    <row r="12" spans="3:19">
+    <row r="12" spans="2:19">
       <c r="C12" t="s">
         <v>82</v>
       </c>
@@ -14114,11 +14629,14 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="3:19">
+    <row r="13" spans="2:19">
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
     </row>
-    <row r="14" spans="3:19">
+    <row r="14" spans="2:19">
+      <c r="B14" t="s">
+        <v>316</v>
+      </c>
       <c r="C14" s="5" t="s">
         <v>19</v>
       </c>
@@ -14131,7 +14649,7 @@
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
     </row>
-    <row r="15" spans="3:19">
+    <row r="15" spans="2:19">
       <c r="C15" t="s">
         <v>10</v>
       </c>
@@ -14168,7 +14686,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="16" spans="3:19">
+    <row r="16" spans="2:19">
       <c r="C16" s="10" t="s">
         <v>7</v>
       </c>
@@ -14239,23 +14757,23 @@
         <v>265595</v>
       </c>
       <c r="G18" s="15">
-        <f ca="1">F18*(1+G37)</f>
+        <f>F18*(1+G37)</f>
         <v>254971.19999999998</v>
       </c>
       <c r="H18" s="15">
-        <f ca="1">G18*(1+H37)</f>
+        <f>G18*(1+H37)</f>
         <v>270269.47200000001</v>
       </c>
       <c r="I18" s="15">
-        <f ca="1">H18*(1+I37)</f>
+        <f>H18*(1+I37)</f>
         <v>288918.06556800002</v>
       </c>
       <c r="J18" s="15">
-        <f ca="1">I18*(1+J37)</f>
+        <f>I18*(1+J37)</f>
         <v>308853.41209219198</v>
       </c>
       <c r="K18" s="15">
-        <f ca="1">J18*(1+K37)</f>
+        <f>J18*(1+K37)</f>
         <v>330164.29752655321</v>
       </c>
       <c r="M18" t="s">
@@ -14276,23 +14794,23 @@
         <v>-163756</v>
       </c>
       <c r="G19" s="15">
-        <f ca="1">G20-G18</f>
+        <f>G20-G18</f>
         <v>-158592.08639999997</v>
       </c>
       <c r="H19" s="15">
-        <f ca="1">H20-H18</f>
+        <f>H20-H18</f>
         <v>-167296.80316800001</v>
       </c>
       <c r="I19" s="15">
-        <f ca="1">I20-I18</f>
+        <f>I20-I18</f>
         <v>-178551.36452102399</v>
       </c>
       <c r="J19" s="15">
-        <f ca="1">J20-J18</f>
+        <f>J20-J18</f>
         <v>-190871.40867297465</v>
       </c>
       <c r="K19" s="15">
-        <f ca="1">K20-K18</f>
+        <f>K20-K18</f>
         <v>-204041.53587140987</v>
       </c>
       <c r="M19" t="s">
@@ -14316,23 +14834,23 @@
         <v>101839</v>
       </c>
       <c r="G20" s="17">
-        <f ca="1">G18*G38</f>
+        <f>G18*G38</f>
         <v>96379.113599999997</v>
       </c>
       <c r="H20" s="17">
-        <f ca="1">H18*H38</f>
+        <f>H18*H38</f>
         <v>102972.66883200001</v>
       </c>
       <c r="I20" s="17">
-        <f ca="1">I18*I38</f>
+        <f>I18*I38</f>
         <v>110366.70104697601</v>
       </c>
       <c r="J20" s="17">
-        <f ca="1">J18*J38</f>
+        <f>J18*J38</f>
         <v>117982.00341921733</v>
       </c>
       <c r="K20" s="17">
-        <f ca="1">K18*K38</f>
+        <f>K18*K38</f>
         <v>126122.76165514333</v>
       </c>
       <c r="M20" s="54" t="s">
@@ -14353,23 +14871,23 @@
         <v>-14236</v>
       </c>
       <c r="G21" s="15">
-        <f ca="1">-G39*G18</f>
+        <f>-G39*G18</f>
         <v>-15808.214399999999</v>
       </c>
       <c r="H21" s="15">
-        <f ca="1">-H39*H18</f>
+        <f>-H39*H18</f>
         <v>-17026.976736000001</v>
       </c>
       <c r="I21" s="15">
-        <f ca="1">-I39*I18</f>
+        <f>-I39*I18</f>
         <v>-18201.838130784003</v>
       </c>
       <c r="J21" s="15">
-        <f ca="1">-J39*J18</f>
+        <f>-J39*J18</f>
         <v>-19457.764961808094</v>
       </c>
       <c r="K21" s="15">
-        <f ca="1">-K39*K18</f>
+        <f>-K39*K18</f>
         <v>-20800.350744172854</v>
       </c>
       <c r="M21" s="54" t="s">
@@ -14390,23 +14908,23 @@
         <v>-16705</v>
       </c>
       <c r="G22" s="15">
-        <f ca="1">-G18*G40</f>
+        <f>-G18*G40</f>
         <v>-18867.868799999997</v>
       </c>
       <c r="H22" s="15">
-        <f ca="1">-H18*H40</f>
+        <f>-H18*H40</f>
         <v>-18648.593568000004</v>
       </c>
       <c r="I22" s="15">
-        <f ca="1">-I18*I40</f>
+        <f>-I18*I40</f>
         <v>-19935.346524192002</v>
       </c>
       <c r="J22" s="15">
-        <f ca="1">-J18*J40</f>
+        <f>-J18*J40</f>
         <v>-21310.885434361247</v>
       </c>
       <c r="K22" s="15">
-        <f ca="1">-K18*K40</f>
+        <f>-K18*K40</f>
         <v>-22781.336529332173</v>
       </c>
       <c r="M22" s="54" t="s">
@@ -14430,23 +14948,23 @@
         <v>70898</v>
       </c>
       <c r="G23" s="17">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>61703.030400000003</v>
       </c>
       <c r="H23" s="17">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>67297.098528000002</v>
       </c>
       <c r="I23" s="17">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>72229.516392000005</v>
       </c>
       <c r="J23" s="17">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>77213.353023047996</v>
       </c>
       <c r="K23" s="17">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>82541.074381638304</v>
       </c>
       <c r="M23" s="16" t="s">
@@ -14468,23 +14986,23 @@
       </c>
       <c r="G24" s="18">
         <f ca="1">G157</f>
-        <v>4744.4371106301642</v>
+        <v>0</v>
       </c>
       <c r="H24" s="18">
         <f ca="1">H157</f>
-        <v>4090.2133392642463</v>
+        <v>0</v>
       </c>
       <c r="I24" s="18">
         <f ca="1">I157</f>
-        <v>3636.4123766928992</v>
+        <v>0</v>
       </c>
       <c r="J24" s="18">
         <f ca="1">J157</f>
-        <v>3232.6203873851432</v>
+        <v>0</v>
       </c>
       <c r="K24" s="18">
         <f ca="1">K157</f>
-        <v>2913.259316698618</v>
+        <v>0</v>
       </c>
       <c r="M24" t="s">
         <v>95</v>
@@ -14505,23 +15023,23 @@
       </c>
       <c r="G25" s="18">
         <f ca="1">-G143</f>
-        <v>-3223.1468651501777</v>
+        <v>-2961.9392651501776</v>
       </c>
       <c r="H25" s="18">
         <f ca="1">-H143</f>
-        <v>-3223.5392651501775</v>
+        <v>-2961.9392651501776</v>
       </c>
       <c r="I25" s="18">
         <f ca="1">-I143</f>
-        <v>-3223.5392651501775</v>
+        <v>-2961.9392651501776</v>
       </c>
       <c r="J25" s="18">
         <f ca="1">-J143</f>
-        <v>-3223.5392651501775</v>
+        <v>-2961.9392651501776</v>
       </c>
       <c r="K25" s="18">
         <f ca="1">-K143</f>
-        <v>-3223.5392651501775</v>
+        <v>-2961.9392651501776</v>
       </c>
       <c r="M25" t="s">
         <v>94</v>
@@ -14582,23 +15100,23 @@
       </c>
       <c r="G27" s="17">
         <f ca="1">SUM(G23:G26)</f>
-        <v>72575.808295480005</v>
+        <v>58300.091134849827</v>
       </c>
       <c r="H27" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>66460.107412614074</v>
+        <v>63894.159262849826</v>
       </c>
       <c r="I27" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>70968.973380104231</v>
+        <v>68826.577126849821</v>
       </c>
       <c r="J27" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>84769.798960125816</v>
+        <v>73810.413757897812</v>
       </c>
       <c r="K27" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>90329.356420253753</v>
+        <v>79138.13511648812</v>
       </c>
       <c r="M27" s="16" t="s">
         <v>96</v>
@@ -14620,23 +15138,23 @@
       </c>
       <c r="G28" s="15">
         <f ca="1">-G41*G27</f>
-        <v>-10484.81454779516</v>
+        <v>-9736.1152195199211</v>
       </c>
       <c r="H28" s="15">
         <f ca="1">-H41*H27</f>
-        <v>-11512.871342359393</v>
+        <v>-10862.00707468447</v>
       </c>
       <c r="I28" s="15">
         <f ca="1">-I41*I27</f>
-        <v>-12194.543848678317</v>
+        <v>-11631.691534437621</v>
       </c>
       <c r="J28" s="15">
         <f ca="1">-J41*J27</f>
-        <v>-12970.648835062466</v>
+        <v>-12473.959925084731</v>
       </c>
       <c r="K28" s="15">
         <f ca="1">-K41*K27</f>
-        <v>-13822.475259208561</v>
+        <v>-13374.344834686493</v>
       </c>
       <c r="M28" t="s">
         <v>92</v>
@@ -14660,23 +15178,23 @@
       </c>
       <c r="G29" s="17">
         <f ca="1">SUM(G27:G28)</f>
-        <v>62090.993747684843</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="H29" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>54947.236070254679</v>
+        <v>53032.152188165353</v>
       </c>
       <c r="I29" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>58774.429531425914</v>
+        <v>57194.885592412204</v>
       </c>
       <c r="J29" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>71799.150125063345</v>
+        <v>61336.45383281308</v>
       </c>
       <c r="K29" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>76506.881161045196</v>
+        <v>65763.79028180163</v>
       </c>
       <c r="M29" s="16" t="s">
         <v>93</v>
@@ -14707,23 +15225,23 @@
         <v>10903</v>
       </c>
       <c r="G31" s="18">
-        <f ca="1">G107</f>
+        <f>G107</f>
         <v>11085.020171261172</v>
       </c>
       <c r="H31" s="18">
-        <f ca="1">H107</f>
+        <f>H107</f>
         <v>11711.890744865921</v>
       </c>
       <c r="I31" s="18">
-        <f ca="1">I107</f>
+        <f>I107</f>
         <v>12226.380531123083</v>
       </c>
       <c r="J31" s="18">
-        <f ca="1">J107</f>
+        <f>J107</f>
         <v>13365.451007770575</v>
       </c>
       <c r="K31" s="18">
-        <f ca="1">K107</f>
+        <f>K107</f>
         <v>14603.503412486743</v>
       </c>
       <c r="M31" t="s">
@@ -14747,30 +15265,30 @@
         <v>81801</v>
       </c>
       <c r="G32" s="17">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>72788.050571261178</v>
       </c>
       <c r="H32" s="17">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>79008.989272865918</v>
       </c>
       <c r="I32" s="17">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>84455.896923123088</v>
       </c>
       <c r="J32" s="17">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>90578.804030818574</v>
       </c>
       <c r="K32" s="17">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>97144.577794125042</v>
       </c>
       <c r="M32" s="16" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="33" spans="3:20">
+    <row r="33" spans="2:20">
       <c r="C33" s="28" t="s">
         <v>74</v>
       </c>
@@ -14784,30 +15302,30 @@
         <v>5340</v>
       </c>
       <c r="G33" s="18">
-        <f ca="1">F33*(1+G37)</f>
+        <f>F33*(1+G37)</f>
         <v>5126.3999999999996</v>
       </c>
       <c r="H33" s="18">
-        <f ca="1">G33*(1+H37)</f>
+        <f>G33*(1+H37)</f>
         <v>5433.9839999999995</v>
       </c>
       <c r="I33" s="18">
-        <f ca="1">H33*(1+I37)</f>
+        <f>H33*(1+I37)</f>
         <v>5808.9288959999994</v>
       </c>
       <c r="J33" s="18">
-        <f ca="1">I33*(1+J37)</f>
+        <f>I33*(1+J37)</f>
         <v>6209.7449898239993</v>
       </c>
       <c r="K33" s="18">
-        <f ca="1">J33*(1+K37)</f>
+        <f>J33*(1+K37)</f>
         <v>6638.2173941218552</v>
       </c>
       <c r="M33" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="34" spans="3:20">
+    <row r="34" spans="2:20">
       <c r="C34" s="27" t="s">
         <v>72</v>
       </c>
@@ -14824,39 +15342,39 @@
         <v>87141</v>
       </c>
       <c r="G34" s="17">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>77914.450571261172</v>
       </c>
       <c r="H34" s="17">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>84442.973272865915</v>
       </c>
       <c r="I34" s="17">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>90264.825819123085</v>
       </c>
       <c r="J34" s="17">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>96788.549020642575</v>
       </c>
       <c r="K34" s="17">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>103782.79518824689</v>
       </c>
       <c r="M34" s="16" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="35" spans="3:20">
+    <row r="35" spans="2:20">
       <c r="C35" s="20"/>
       <c r="G35" s="38"/>
     </row>
-    <row r="36" spans="3:20">
+    <row r="36" spans="2:20">
       <c r="C36" s="19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="3:20">
+    <row r="37" spans="2:20">
       <c r="C37" s="20" t="s">
         <v>1</v>
       </c>
@@ -14870,23 +15388,23 @@
         <v>0.15861957650261305</v>
       </c>
       <c r="G37" s="21">
-        <f t="shared" ref="G37:K40" ca="1" si="5">G175</f>
+        <f t="shared" ref="G37:K40" si="5">G175</f>
         <v>-0.04</v>
       </c>
       <c r="H37" s="21">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>0.06</v>
       </c>
       <c r="I37" s="21">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="J37" s="21">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="K37" s="21">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="M37" t="s">
@@ -14899,7 +15417,7 @@
       <c r="S37" s="22"/>
       <c r="T37" s="22"/>
     </row>
-    <row r="38" spans="3:20">
+    <row r="38" spans="2:20">
       <c r="C38" s="20" t="s">
         <v>230</v>
       </c>
@@ -14916,23 +15434,23 @@
         <v>0.38343718820007905</v>
       </c>
       <c r="G38" s="21">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>0.378</v>
       </c>
       <c r="H38" s="21">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>0.38100000000000001</v>
       </c>
       <c r="I38" s="21">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>0.38200000000000001</v>
       </c>
       <c r="J38" s="21">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>0.38200000000000001</v>
       </c>
       <c r="K38" s="21">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>0.38200000000000001</v>
       </c>
       <c r="M38" t="s">
@@ -14945,7 +15463,7 @@
       <c r="S38" s="22"/>
       <c r="T38" s="22"/>
     </row>
-    <row r="39" spans="3:20">
+    <row r="39" spans="2:20">
       <c r="C39" s="20" t="s">
         <v>231</v>
       </c>
@@ -14962,23 +15480,23 @@
         <v>5.3600406634161032E-2</v>
       </c>
       <c r="G39" s="21">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>6.2E-2</v>
       </c>
       <c r="H39" s="21">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>6.3E-2</v>
       </c>
       <c r="I39" s="21">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>6.3E-2</v>
       </c>
       <c r="J39" s="21">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>6.3E-2</v>
       </c>
       <c r="K39" s="21">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>6.3E-2</v>
       </c>
       <c r="M39" t="s">
@@ -14991,7 +15509,7 @@
       <c r="S39" s="22"/>
       <c r="T39" s="22"/>
     </row>
-    <row r="40" spans="3:20">
+    <row r="40" spans="2:20">
       <c r="C40" s="20" t="s">
         <v>233</v>
       </c>
@@ -15008,23 +15526,23 @@
         <v>6.2896515371147807E-2</v>
       </c>
       <c r="G40" s="21">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>7.3999999999999996E-2</v>
       </c>
       <c r="H40" s="21">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="I40" s="21">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="J40" s="21">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="K40" s="21">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="M40" t="s">
@@ -15037,7 +15555,7 @@
       <c r="S40" s="22"/>
       <c r="T40" s="22"/>
     </row>
-    <row r="41" spans="3:20">
+    <row r="41" spans="2:20">
       <c r="C41" s="20" t="s">
         <v>0</v>
       </c>
@@ -15080,11 +15598,14 @@
       <c r="S41" s="22"/>
       <c r="T41" s="22"/>
     </row>
-    <row r="42" spans="3:20">
+    <row r="42" spans="2:20">
       <c r="C42" s="20"/>
       <c r="G42" s="38"/>
     </row>
-    <row r="43" spans="3:20">
+    <row r="43" spans="2:20">
+      <c r="B43" t="s">
+        <v>316</v>
+      </c>
       <c r="C43" s="5" t="s">
         <v>20</v>
       </c>
@@ -15097,7 +15618,7 @@
       <c r="J43" s="7"/>
       <c r="K43" s="7"/>
     </row>
-    <row r="44" spans="3:20">
+    <row r="44" spans="2:20">
       <c r="C44" s="26" t="str">
         <f>C15</f>
         <v xml:space="preserve">Fiscal year  </v>
@@ -15132,7 +15653,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="45" spans="3:20">
+    <row r="45" spans="2:20">
       <c r="C45" s="7" t="str">
         <f>C16</f>
         <v>Fiscal year end date</v>
@@ -15167,7 +15688,7 @@
         <v>45199</v>
       </c>
     </row>
-    <row r="46" spans="3:20">
+    <row r="46" spans="2:20">
       <c r="C46" t="s">
         <v>138</v>
       </c>
@@ -15182,29 +15703,29 @@
       </c>
       <c r="G46" s="18">
         <f ca="1">G91+F46</f>
-        <v>202199.73246575586</v>
+        <v>198465.20228340095</v>
       </c>
       <c r="H46" s="18">
         <f ca="1">H91+G46</f>
-        <v>180627.92026055476</v>
+        <v>169611.44561958191</v>
       </c>
       <c r="I46" s="18">
         <f ca="1">I91+H46</f>
-        <v>159042.92520923278</v>
+        <v>146397.01542701561</v>
       </c>
       <c r="J46" s="18">
         <f ca="1">J91+I46</f>
-        <v>144687.8938628305</v>
+        <v>128151.56459718544</v>
       </c>
       <c r="K46" s="18">
         <f ca="1">K91+J46</f>
-        <v>129472.4557012212</v>
+        <v>115146.71407980147</v>
       </c>
       <c r="M46" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="47" spans="3:20">
+    <row r="47" spans="2:20">
       <c r="C47" t="s">
         <v>54</v>
       </c>
@@ -15216,30 +15737,30 @@
         <v>23186</v>
       </c>
       <c r="G47" s="18">
-        <f ca="1">F47*(1+G37)</f>
+        <f>F47*(1+G37)</f>
         <v>22258.559999999998</v>
       </c>
       <c r="H47" s="18">
-        <f ca="1">G47*(1+H37)</f>
+        <f>G47*(1+H37)</f>
         <v>23594.0736</v>
       </c>
       <c r="I47" s="18">
-        <f ca="1">H47*(1+I37)</f>
+        <f>H47*(1+I37)</f>
         <v>25222.064678399998</v>
       </c>
       <c r="J47" s="18">
-        <f ca="1">I47*(1+J37)</f>
+        <f>I47*(1+J37)</f>
         <v>26962.387141209598</v>
       </c>
       <c r="K47" s="18">
-        <f ca="1">J47*(1+K37)</f>
+        <f>J47*(1+K37)</f>
         <v>28822.791853953058</v>
       </c>
       <c r="M47" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="48" spans="3:20">
+    <row r="48" spans="2:20">
       <c r="C48" t="s">
         <v>55</v>
       </c>
@@ -15251,23 +15772,23 @@
         <v>3956</v>
       </c>
       <c r="G48" s="18">
-        <f ca="1">F48*G19/F19</f>
+        <f>F48*G19/F19</f>
         <v>3831.2507254598299</v>
       </c>
       <c r="H48" s="18">
-        <f ca="1">G48*H19/G19</f>
+        <f>G48*H19/G19</f>
         <v>4041.5383456643303</v>
       </c>
       <c r="I48" s="18">
-        <f ca="1">H48*I19/H19</f>
+        <f>H48*I19/H19</f>
         <v>4313.4248396710409</v>
       </c>
       <c r="J48" s="18">
-        <f ca="1">I48*J19/I19</f>
+        <f>I48*J19/I19</f>
         <v>4611.0511536083422</v>
       </c>
       <c r="K48" s="18">
-        <f ca="1">J48*K19/J19</f>
+        <f>J48*K19/J19</f>
         <v>4929.2136832073174</v>
       </c>
       <c r="M48" t="s">
@@ -15288,23 +15809,23 @@
         <v>37896</v>
       </c>
       <c r="G49" s="18">
-        <f ca="1">F49*(1+G37)</f>
+        <f>F49*(1+G37)</f>
         <v>36380.159999999996</v>
       </c>
       <c r="H49" s="18">
-        <f ca="1">G49*(1+H37)</f>
+        <f>G49*(1+H37)</f>
         <v>38562.969599999997</v>
       </c>
       <c r="I49" s="18">
-        <f ca="1">H49*(1+I37)</f>
+        <f>H49*(1+I37)</f>
         <v>41223.814502399997</v>
       </c>
       <c r="J49" s="18">
-        <f ca="1">I49*(1+J37)</f>
+        <f>I49*(1+J37)</f>
         <v>44068.257703065596</v>
       </c>
       <c r="K49" s="18">
-        <f ca="1">J49*(1+K37)</f>
+        <f>J49*(1+K37)</f>
         <v>47108.967484577122</v>
       </c>
       <c r="M49" t="s">
@@ -15335,11 +15856,11 @@
         <v>51947.567835949827</v>
       </c>
       <c r="J50" s="18">
-        <f ca="1">J100</f>
+        <f>J100</f>
         <v>55218.714198720052</v>
       </c>
       <c r="K50" s="18">
-        <f ca="1">K100</f>
+        <f>K100</f>
         <v>58399.73337534142</v>
       </c>
       <c r="M50" t="s">
@@ -15358,23 +15879,23 @@
         <v>22283</v>
       </c>
       <c r="G51" s="18">
-        <f ca="1">F51*(1+G37)</f>
+        <f>F51*(1+G37)</f>
         <v>21391.68</v>
       </c>
       <c r="H51" s="18">
-        <f ca="1">G51*(1+H37)</f>
+        <f>G51*(1+H37)</f>
         <v>22675.180800000002</v>
       </c>
       <c r="I51" s="18">
-        <f ca="1">H51*(1+I37)</f>
+        <f>H51*(1+I37)</f>
         <v>24239.7682752</v>
       </c>
       <c r="J51" s="18">
-        <f ca="1">I51*(1+J37)</f>
+        <f>I51*(1+J37)</f>
         <v>25912.3122861888</v>
       </c>
       <c r="K51" s="18">
-        <f ca="1">J51*(1+K37)</f>
+        <f>J51*(1+K37)</f>
         <v>27700.261833935827</v>
       </c>
       <c r="M51" t="s">
@@ -15396,23 +15917,23 @@
       </c>
       <c r="G52" s="29">
         <f t="shared" ca="1" si="7"/>
-        <v>330867.67714668333</v>
+        <v>327369.71283759963</v>
       </c>
       <c r="H52" s="29">
         <f t="shared" ca="1" si="7"/>
-        <v>318490.86472855101</v>
+        <v>307096.38984911912</v>
       </c>
       <c r="I52" s="29">
         <f t="shared" ca="1" si="7"/>
-        <v>307814.56410790572</v>
+        <v>293343.65555863647</v>
       </c>
       <c r="J52" s="29">
         <f t="shared" ca="1" si="7"/>
-        <v>306077.00085757417</v>
+        <v>284924.28707997786</v>
       </c>
       <c r="K52" s="29">
         <f t="shared" ca="1" si="7"/>
-        <v>301368.33897551178</v>
+        <v>282107.68231081619</v>
       </c>
     </row>
     <row r="53" spans="3:13">
@@ -15438,23 +15959,23 @@
         <v>55888</v>
       </c>
       <c r="G54" s="18">
-        <f ca="1">F54*G19/F19</f>
+        <f>F54*G19/F19</f>
         <v>54125.616922269706</v>
       </c>
       <c r="H54" s="18">
-        <f ca="1">G54*H19/G19</f>
+        <f>G54*H19/G19</f>
         <v>57096.434545623881</v>
       </c>
       <c r="I54" s="18">
-        <f ca="1">H54*I19/H19</f>
+        <f>H54*I19/H19</f>
         <v>60937.484185928995</v>
       </c>
       <c r="J54" s="18">
-        <f ca="1">I54*J19/I19</f>
+        <f>I54*J19/I19</f>
         <v>65142.170594758099</v>
       </c>
       <c r="K54" s="18">
-        <f ca="1">J54*K19/J19</f>
+        <f>J54*K19/J19</f>
         <v>69636.980365796408</v>
       </c>
       <c r="M54" t="s">
@@ -15473,23 +15994,23 @@
         <v>32687</v>
       </c>
       <c r="G55" s="18">
-        <f ca="1">F55*(1+G37)</f>
+        <f>F55*(1+G37)</f>
         <v>31379.52</v>
       </c>
       <c r="H55" s="18">
-        <f ca="1">G55*(1+H37)</f>
+        <f>G55*(1+H37)</f>
         <v>33262.2912</v>
       </c>
       <c r="I55" s="18">
-        <f ca="1">H55*(1+I37)</f>
+        <f>H55*(1+I37)</f>
         <v>35557.389292799999</v>
       </c>
       <c r="J55" s="18">
-        <f ca="1">I55*(1+J37)</f>
+        <f>I55*(1+J37)</f>
         <v>38010.849154003197</v>
       </c>
       <c r="K55" s="18">
-        <f ca="1">J55*(1+K37)</f>
+        <f>J55*(1+K37)</f>
         <v>40633.597745629413</v>
       </c>
       <c r="M55" t="s">
@@ -15510,23 +16031,23 @@
         <v>10340</v>
       </c>
       <c r="G56" s="18">
-        <f ca="1">F56*(1+G37)</f>
+        <f>F56*(1+G37)</f>
         <v>9926.4</v>
       </c>
       <c r="H56" s="18">
-        <f ca="1">G56*(1+H37)</f>
+        <f>G56*(1+H37)</f>
         <v>10521.984</v>
       </c>
       <c r="I56" s="18">
-        <f ca="1">H56*(1+I37)</f>
+        <f>H56*(1+I37)</f>
         <v>11248.000896</v>
       </c>
       <c r="J56" s="18">
-        <f ca="1">I56*(1+J37)</f>
+        <f>I56*(1+J37)</f>
         <v>12024.112957824</v>
       </c>
       <c r="K56" s="18">
-        <f ca="1">J56*(1+K37)</f>
+        <f>J56*(1+K37)</f>
         <v>12853.776751913854</v>
       </c>
       <c r="M56" t="s">
@@ -15617,23 +16138,23 @@
         <v>45180</v>
       </c>
       <c r="G59" s="18">
-        <f ca="1">F59*(1+G37)</f>
+        <f>F59*(1+G37)</f>
         <v>43372.799999999996</v>
       </c>
       <c r="H59" s="18">
-        <f t="shared" ref="H59:K59" ca="1" si="9">G59*(1+H37)</f>
+        <f t="shared" ref="H59:K59" si="9">G59*(1+H37)</f>
         <v>45975.167999999998</v>
       </c>
       <c r="I59" s="18">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" si="9"/>
         <v>49147.454591999995</v>
       </c>
       <c r="J59" s="18">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" si="9"/>
         <v>52538.628958847992</v>
       </c>
       <c r="K59" s="18">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" si="9"/>
         <v>56163.794357008504</v>
       </c>
       <c r="M59" t="s">
@@ -15655,23 +16176,23 @@
       </c>
       <c r="G60" s="29">
         <f t="shared" ca="1" si="10"/>
-        <v>249981.27586934215</v>
+        <v>253323.33692226969</v>
       </c>
       <c r="H60" s="29">
         <f t="shared" ca="1" si="10"/>
-        <v>268205.34246798384</v>
+        <v>261374.87774562387</v>
       </c>
       <c r="I60" s="29">
         <f t="shared" ca="1" si="10"/>
-        <v>278704.41941918462</v>
+        <v>271409.32896672899</v>
       </c>
       <c r="J60" s="29">
         <f t="shared" ca="1" si="10"/>
-        <v>282896.21044537576</v>
+        <v>282234.7616654333</v>
       </c>
       <c r="K60" s="29">
         <f t="shared" ca="1" si="10"/>
-        <v>294514.23796610662</v>
+        <v>293807.14922034822</v>
       </c>
     </row>
     <row r="61" spans="3:13">
@@ -15697,23 +16218,23 @@
         <v>40201</v>
       </c>
       <c r="G62" s="18">
-        <f ca="1">F62+G33</f>
+        <f>F62+G33</f>
         <v>45327.4</v>
       </c>
       <c r="H62" s="18">
-        <f ca="1">G62+H33</f>
+        <f>G62+H33</f>
         <v>50761.383999999998</v>
       </c>
       <c r="I62" s="18">
-        <f ca="1">H62+I33</f>
+        <f>H62+I33</f>
         <v>56570.312895999996</v>
       </c>
       <c r="J62" s="18">
-        <f ca="1">I62+J33</f>
+        <f>I62+J33</f>
         <v>62780.057885823997</v>
       </c>
       <c r="K62" s="18">
-        <f ca="1">J62+K33</f>
+        <f>J62+K33</f>
         <v>69418.275279945854</v>
       </c>
       <c r="M62" t="s">
@@ -15734,23 +16255,23 @@
       </c>
       <c r="G63" s="18">
         <f ca="1">G120</f>
-        <v>35907.506097684833</v>
+        <v>32172.975915329909</v>
       </c>
       <c r="H63" s="18">
         <f ca="1">H120</f>
-        <v>5326.4073574395152</v>
+        <v>-1585.8718965047447</v>
       </c>
       <c r="I63" s="18">
         <f ca="1">I120</f>
-        <v>-21502.07229787598</v>
+        <v>-31181.986304092541</v>
       </c>
       <c r="J63" s="18">
         <f ca="1">J120</f>
-        <v>-44514.319742036285</v>
+        <v>-56636.532471279461</v>
       </c>
       <c r="K63" s="18">
         <f ca="1">K120</f>
-        <v>-63338.000568058094</v>
+        <v>-77663.742189477838</v>
       </c>
       <c r="M63" t="s">
         <v>107</v>
@@ -15791,7 +16312,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="65" spans="3:13">
+    <row r="65" spans="2:13">
       <c r="C65" s="27" t="s">
         <v>25</v>
       </c>
@@ -15806,31 +16327,31 @@
       </c>
       <c r="G65" s="29">
         <f t="shared" ca="1" si="11"/>
-        <v>77780.906097684841</v>
+        <v>74046.375915329903</v>
       </c>
       <c r="H65" s="29">
         <f t="shared" ca="1" si="11"/>
-        <v>52633.791357439513</v>
+        <v>45721.512103495254</v>
       </c>
       <c r="I65" s="29">
         <f t="shared" ca="1" si="11"/>
-        <v>31614.240598124015</v>
+        <v>21934.326591907455</v>
       </c>
       <c r="J65" s="29">
         <f t="shared" ca="1" si="11"/>
-        <v>14811.738143787712</v>
+        <v>2689.525414544536</v>
       </c>
       <c r="K65" s="29">
         <f t="shared" ca="1" si="11"/>
-        <v>2626.2747118877596</v>
-      </c>
-    </row>
-    <row r="66" spans="3:13">
+        <v>-11699.466909531984</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13">
       <c r="D66" s="18"/>
       <c r="E66" s="18"/>
       <c r="F66" s="18"/>
     </row>
-    <row r="67" spans="3:13">
+    <row r="67" spans="2:13">
       <c r="C67" s="12" t="s">
         <v>26</v>
       </c>
@@ -15857,14 +16378,14 @@
       </c>
       <c r="J67" s="30">
         <f t="shared" ca="1" si="12"/>
-        <v>8369.0519999999997</v>
+        <v>0</v>
       </c>
       <c r="K67" s="30">
         <f t="shared" ca="1" si="12"/>
-        <v>4934.915</v>
-      </c>
-    </row>
-    <row r="68" spans="3:13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="2:13">
       <c r="E68" s="18"/>
       <c r="F68" s="18"/>
       <c r="H68" s="18"/>
@@ -15872,7 +16393,10 @@
       <c r="J68" s="18"/>
       <c r="K68" s="18"/>
     </row>
-    <row r="69" spans="3:13">
+    <row r="69" spans="2:13">
+      <c r="B69" t="s">
+        <v>316</v>
+      </c>
       <c r="C69" s="5" t="s">
         <v>32</v>
       </c>
@@ -15885,7 +16409,7 @@
       <c r="J69" s="11"/>
       <c r="K69" s="11"/>
     </row>
-    <row r="70" spans="3:13">
+    <row r="70" spans="2:13">
       <c r="C70" s="26" t="str">
         <f>C15</f>
         <v xml:space="preserve">Fiscal year  </v>
@@ -15914,7 +16438,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="71" spans="3:13">
+    <row r="71" spans="2:13">
       <c r="C71" s="7" t="str">
         <f>C16</f>
         <v>Fiscal year end date</v>
@@ -15943,7 +16467,7 @@
         <v>45199</v>
       </c>
     </row>
-    <row r="73" spans="3:13">
+    <row r="73" spans="2:13">
       <c r="C73" t="s">
         <v>2</v>
       </c>
@@ -15952,27 +16476,27 @@
       <c r="F73" s="34"/>
       <c r="G73" s="18">
         <f ca="1">G29</f>
-        <v>62090.993747684843</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="H73" s="18">
         <f ca="1">H29</f>
-        <v>54947.236070254679</v>
+        <v>53032.152188165353</v>
       </c>
       <c r="I73" s="18">
         <f ca="1">I29</f>
-        <v>58774.429531425914</v>
+        <v>57194.885592412204</v>
       </c>
       <c r="J73" s="18">
         <f ca="1">J29</f>
-        <v>71799.150125063345</v>
+        <v>61336.45383281308</v>
       </c>
       <c r="K73" s="18">
         <f ca="1">K29</f>
-        <v>67967.319173978191</v>
+        <v>65763.79028180163</v>
       </c>
       <c r="M73" s="16"/>
     </row>
-    <row r="74" spans="3:13">
+    <row r="74" spans="2:13">
       <c r="C74" t="s">
         <v>33</v>
       </c>
@@ -15980,30 +16504,30 @@
       <c r="E74" s="34"/>
       <c r="F74" s="34"/>
       <c r="G74" s="18">
-        <f ca="1">G31</f>
+        <f>G31</f>
         <v>11085.020171261172</v>
       </c>
       <c r="H74" s="18">
-        <f ca="1">H31</f>
+        <f>H31</f>
         <v>11711.890744865921</v>
       </c>
       <c r="I74" s="18">
-        <f ca="1">I31</f>
+        <f>I31</f>
         <v>12226.380531123083</v>
       </c>
       <c r="J74" s="18">
-        <f ca="1">J31</f>
+        <f>J31</f>
         <v>13365.451007770575</v>
       </c>
       <c r="K74" s="18">
-        <f ca="1">K31</f>
+        <f>K31</f>
         <v>14603.503412486743</v>
       </c>
       <c r="M74" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="75" spans="3:13">
+    <row r="75" spans="2:13">
       <c r="C75" t="s">
         <v>74</v>
       </c>
@@ -16011,27 +16535,27 @@
       <c r="E75" s="34"/>
       <c r="F75" s="34"/>
       <c r="G75" s="18">
-        <f ca="1">G33</f>
+        <f>G33</f>
         <v>5126.3999999999996</v>
       </c>
       <c r="H75" s="18">
-        <f ca="1">H33</f>
+        <f>H33</f>
         <v>5433.9839999999995</v>
       </c>
       <c r="I75" s="18">
-        <f ca="1">I33</f>
+        <f>I33</f>
         <v>5808.9288959999994</v>
       </c>
       <c r="J75" s="18">
-        <f ca="1">J33</f>
+        <f>J33</f>
         <v>6209.7449898239993</v>
       </c>
       <c r="K75" s="18">
-        <f ca="1">K33</f>
+        <f>K33</f>
         <v>6638.2173941218552</v>
       </c>
     </row>
-    <row r="76" spans="3:13">
+    <row r="76" spans="2:13">
       <c r="C76" t="s">
         <v>65</v>
       </c>
@@ -16039,27 +16563,27 @@
       <c r="E76" s="18"/>
       <c r="F76" s="18"/>
       <c r="G76" s="18">
-        <f ca="1">-1*(SUM(G47:G49)-SUM(F47:F49))</f>
+        <f>-1*(SUM(G47:G49)-SUM(F47:F49))</f>
         <v>2568.0292745401748</v>
       </c>
       <c r="H76" s="18">
-        <f ca="1">-1*(SUM(H47:H49)-SUM(G47:G49))</f>
+        <f>-1*(SUM(H47:H49)-SUM(G47:G49))</f>
         <v>-3728.6108202044925</v>
       </c>
       <c r="I76" s="18">
-        <f ca="1">-1*(SUM(I47:I49)-SUM(H47:H49))</f>
+        <f>-1*(SUM(I47:I49)-SUM(H47:H49))</f>
         <v>-4560.7224748067092</v>
       </c>
       <c r="J76" s="18">
-        <f ca="1">-1*(SUM(J47:J49)-SUM(I47:I49))</f>
+        <f>-1*(SUM(J47:J49)-SUM(I47:I49))</f>
         <v>-4882.3919774125097</v>
       </c>
       <c r="K76" s="18">
-        <f ca="1">-1*(SUM(K47:K49)-SUM(J47:J49))</f>
+        <f>-1*(SUM(K47:K49)-SUM(J47:J49))</f>
         <v>-5219.277023853967</v>
       </c>
     </row>
-    <row r="77" spans="3:13">
+    <row r="77" spans="2:13">
       <c r="C77" t="s">
         <v>66</v>
       </c>
@@ -16067,103 +16591,103 @@
       <c r="E77" s="18"/>
       <c r="F77" s="18"/>
       <c r="G77" s="18">
-        <f ca="1">SUM(G54:G56)-SUM(F54:F56)</f>
+        <f>SUM(G54:G56)-SUM(F54:F56)</f>
         <v>-3483.4630777302955</v>
       </c>
       <c r="H77" s="18">
-        <f ca="1">SUM(H54:H56)-SUM(G54:G56)</f>
+        <f>SUM(H54:H56)-SUM(G54:G56)</f>
         <v>5449.1728233541653</v>
       </c>
       <c r="I77" s="18">
-        <f ca="1">SUM(I54:I56)-SUM(H54:H56)</f>
+        <f>SUM(I54:I56)-SUM(H54:H56)</f>
         <v>6862.1646291051147</v>
       </c>
       <c r="J77" s="18">
-        <f ca="1">SUM(J54:J56)-SUM(I54:I56)</f>
+        <f>SUM(J54:J56)-SUM(I54:I56)</f>
         <v>7434.2583318562974</v>
       </c>
       <c r="K77" s="18">
-        <f ca="1">SUM(K54:K56)-SUM(J54:J56)</f>
+        <f>SUM(K54:K56)-SUM(J54:J56)</f>
         <v>7947.2221567544038</v>
       </c>
     </row>
-    <row r="78" spans="3:13">
+    <row r="78" spans="2:13">
       <c r="C78" t="s">
         <v>56</v>
       </c>
       <c r="G78" s="18">
-        <f ca="1">-(G112)</f>
+        <f>-(G112)</f>
         <v>-647.56000000000131</v>
       </c>
       <c r="H78" s="18">
-        <f ca="1">-(H112)</f>
+        <f>-(H112)</f>
         <v>-2914.7136000000028</v>
       </c>
       <c r="I78" s="18">
-        <f ca="1">-(I112)</f>
+        <f>-(I112)</f>
         <v>-3308.3539583999991</v>
       </c>
       <c r="J78" s="18">
-        <f ca="1">-(J112)</f>
+        <f>-(J112)</f>
         <v>-3536.6303815296014</v>
       </c>
       <c r="K78" s="18">
-        <f ca="1">-(K112)</f>
+        <f>-(K112)</f>
         <v>-3780.6578778551411</v>
       </c>
       <c r="M78" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="79" spans="3:13">
+    <row r="79" spans="2:13">
       <c r="C79" t="s">
         <v>59</v>
       </c>
       <c r="G79" s="18">
-        <f ca="1">G59-F59</f>
+        <f>G59-F59</f>
         <v>-1807.2000000000044</v>
       </c>
       <c r="H79" s="18">
-        <f ca="1">H59-G59</f>
+        <f>H59-G59</f>
         <v>2602.3680000000022</v>
       </c>
       <c r="I79" s="18">
-        <f ca="1">I59-H59</f>
+        <f>I59-H59</f>
         <v>3172.2865919999967</v>
       </c>
       <c r="J79" s="18">
-        <f ca="1">J59-I59</f>
+        <f>J59-I59</f>
         <v>3391.1743668479976</v>
       </c>
       <c r="K79" s="18">
-        <f ca="1">K59-J59</f>
+        <f>K59-J59</f>
         <v>3625.1653981605123</v>
       </c>
       <c r="M79" s="16"/>
     </row>
-    <row r="80" spans="3:13">
+    <row r="80" spans="2:13">
       <c r="C80" s="16" t="s">
         <v>34</v>
       </c>
       <c r="G80" s="29">
         <f ca="1">SUM(G73:G79)</f>
-        <v>70378.329936099559</v>
+        <v>61405.202283400962</v>
       </c>
       <c r="H80" s="29">
         <f ca="1">SUM(H73:H79)</f>
-        <v>78868.187794798883</v>
+        <v>71586.243336180953</v>
       </c>
       <c r="I80" s="29">
         <f ca="1">SUM(I73:I79)</f>
-        <v>79025.004948678019</v>
+        <v>77395.569807433698</v>
       </c>
       <c r="J80" s="29">
         <f ca="1">SUM(J73:J79)</f>
-        <v>87208.479653597722</v>
+        <v>83318.060170169832</v>
       </c>
       <c r="K80" s="29">
         <f ca="1">SUM(K73:K79)</f>
-        <v>91598.138874323573</v>
+        <v>89577.963741616026</v>
       </c>
     </row>
     <row r="81" spans="3:13">
@@ -16190,11 +16714,11 @@
         <v>-13819</v>
       </c>
       <c r="J82" s="18">
-        <f ca="1">-(J98)</f>
+        <f>-(J98)</f>
         <v>-14772.510999999999</v>
       </c>
       <c r="K82" s="18">
-        <f ca="1">-(K98)</f>
+        <f>-(K98)</f>
         <v>-15791.814258999997</v>
       </c>
       <c r="M82" t="s">
@@ -16218,11 +16742,11 @@
         <v>-13819</v>
       </c>
       <c r="J83" s="29">
-        <f ca="1">IFERROR(J82,"NA")</f>
+        <f>IFERROR(J82,"NA")</f>
         <v>-14772.510999999999</v>
       </c>
       <c r="K83" s="29">
-        <f ca="1">IFERROR(K82,"NA")</f>
+        <f>IFERROR(K82,"NA")</f>
         <v>-15791.814258999997</v>
       </c>
     </row>
@@ -16380,23 +16904,23 @@
       </c>
       <c r="G91" s="29">
         <f ca="1">G80+G83+G89</f>
-        <v>-34900.267534244129</v>
+        <v>-38634.797716599038</v>
       </c>
       <c r="H91" s="29">
         <f ca="1">H80+H83+H89</f>
-        <v>-21571.812205201117</v>
+        <v>-28853.756663819047</v>
       </c>
       <c r="I91" s="29">
         <f ca="1">I80+I83+I89</f>
-        <v>-21584.995051321981</v>
+        <v>-23214.430192566302</v>
       </c>
       <c r="J91" s="29">
         <f ca="1">J80+J83+J89</f>
-        <v>-14355.031346402277</v>
+        <v>-18245.450829830166</v>
       </c>
       <c r="K91" s="29">
         <f ca="1">K80+K83+K89</f>
-        <v>-10801.321625207391</v>
+        <v>-13004.850517383966</v>
       </c>
     </row>
     <row r="93" spans="3:13">
@@ -16498,7 +17022,7 @@
       <c r="J96" s="76"/>
       <c r="K96" s="76"/>
     </row>
-    <row r="97" spans="3:17">
+    <row r="97" spans="2:17">
       <c r="C97" s="28" t="s">
         <v>27</v>
       </c>
@@ -16519,14 +17043,14 @@
         <v>51947.567835949827</v>
       </c>
       <c r="K97" s="18">
-        <f ca="1">J100</f>
+        <f>J100</f>
         <v>55218.714198720052</v>
       </c>
       <c r="M97" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="98" spans="3:17">
+    <row r="98" spans="2:17">
       <c r="C98" s="31" t="s">
         <v>30</v>
       </c>
@@ -16549,18 +17073,18 @@
         <v>13819</v>
       </c>
       <c r="J98" s="3">
-        <f ca="1">I98*(1+J37)</f>
+        <f>I98*(1+J37)</f>
         <v>14772.510999999999</v>
       </c>
       <c r="K98" s="3">
-        <f t="shared" ref="K98" ca="1" si="16">J98*(1+K37)</f>
+        <f t="shared" ref="K98" si="16">J98*(1+K37)</f>
         <v>15791.814258999997</v>
       </c>
       <c r="M98" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="99" spans="3:17">
+    <row r="99" spans="2:17">
       <c r="C99" s="69" t="s">
         <v>31</v>
       </c>
@@ -16586,18 +17110,18 @@
         <v>-10482.614047923083</v>
       </c>
       <c r="J99" s="68">
-        <f ca="1">-(J102*J98)</f>
+        <f>-(J102*J98)</f>
         <v>-11501.364637229775</v>
       </c>
       <c r="K99" s="68">
-        <f ca="1">-(K102*K98)</f>
+        <f>-(K102*K98)</f>
         <v>-12610.795082378629</v>
       </c>
       <c r="M99" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="100" spans="3:17">
+    <row r="100" spans="2:17">
       <c r="C100" s="35" t="s">
         <v>28</v>
       </c>
@@ -16623,24 +17147,24 @@
         <v>51947.567835949827</v>
       </c>
       <c r="J100" s="29">
-        <f ca="1">SUM(J97:J99)</f>
+        <f>SUM(J97:J99)</f>
         <v>55218.714198720052</v>
       </c>
       <c r="K100" s="29">
-        <f ca="1">SUM(K97:K99)</f>
+        <f>SUM(K97:K99)</f>
         <v>58399.73337534142</v>
       </c>
       <c r="M100" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="101" spans="3:17">
+    <row r="101" spans="2:17">
       <c r="C101" s="28"/>
       <c r="M101" s="19" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="102" spans="3:17">
+    <row r="102" spans="2:17">
       <c r="C102" s="28" t="s">
         <v>123</v>
       </c>
@@ -16683,7 +17207,7 @@
       <c r="P102" s="65"/>
       <c r="Q102" s="65"/>
     </row>
-    <row r="103" spans="3:17">
+    <row r="103" spans="2:17">
       <c r="C103" s="28"/>
       <c r="D103" s="4"/>
       <c r="E103" s="4"/>
@@ -16697,7 +17221,10 @@
       <c r="P103" s="65"/>
       <c r="Q103" s="65"/>
     </row>
-    <row r="104" spans="3:17">
+    <row r="104" spans="2:17">
+      <c r="B104" t="s">
+        <v>316</v>
+      </c>
       <c r="C104" s="90" t="s">
         <v>130</v>
       </c>
@@ -16713,7 +17240,7 @@
       <c r="P104" s="65"/>
       <c r="Q104" s="65"/>
     </row>
-    <row r="105" spans="3:17">
+    <row r="105" spans="2:17">
       <c r="C105" s="28" t="s">
         <v>155</v>
       </c>
@@ -16730,23 +17257,23 @@
         <v>1603</v>
       </c>
       <c r="G105" s="15">
-        <f ca="1">G106*G18</f>
+        <f>G106*G18</f>
         <v>1538.8799999999999</v>
       </c>
       <c r="H105" s="15">
-        <f ca="1">H106*H18</f>
+        <f>H106*H18</f>
         <v>1631.2128</v>
       </c>
       <c r="I105" s="15">
-        <f ca="1">I106*I18</f>
+        <f>I106*I18</f>
         <v>1743.7664832</v>
       </c>
       <c r="J105" s="15">
-        <f ca="1">J106*J18</f>
+        <f>J106*J18</f>
         <v>1864.0863705407999</v>
       </c>
       <c r="K105" s="15">
-        <f ca="1">K106*K18</f>
+        <f>K106*K18</f>
         <v>1992.708330108115</v>
       </c>
       <c r="M105" t="s">
@@ -16756,7 +17283,7 @@
       <c r="P105" s="65"/>
       <c r="Q105" s="65"/>
     </row>
-    <row r="106" spans="3:17">
+    <row r="106" spans="2:17">
       <c r="C106" s="20" t="s">
         <v>156</v>
       </c>
@@ -16796,7 +17323,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="107" spans="3:17">
+    <row r="107" spans="2:17">
       <c r="C107" s="27" t="s">
         <v>110</v>
       </c>
@@ -16813,30 +17340,30 @@
         <v>10903</v>
       </c>
       <c r="G107" s="17">
-        <f ca="1">-G99+G105</f>
+        <f>-G99+G105</f>
         <v>11085.020171261172</v>
       </c>
       <c r="H107" s="17">
-        <f ca="1">-H99+H105</f>
+        <f>-H99+H105</f>
         <v>11711.890744865921</v>
       </c>
       <c r="I107" s="17">
-        <f ca="1">-I99+I105</f>
+        <f>-I99+I105</f>
         <v>12226.380531123083</v>
       </c>
       <c r="J107" s="17">
-        <f ca="1">-J99+J105</f>
+        <f>-J99+J105</f>
         <v>13365.451007770575</v>
       </c>
       <c r="K107" s="17">
-        <f ca="1">-K99+K105</f>
+        <f>-K99+K105</f>
         <v>14603.503412486743</v>
       </c>
       <c r="M107" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="108" spans="3:17">
+    <row r="108" spans="2:17">
       <c r="C108" s="28"/>
       <c r="D108" s="18"/>
       <c r="E108" s="18"/>
@@ -16846,7 +17373,7 @@
       <c r="J108" s="18"/>
       <c r="K108" s="18"/>
     </row>
-    <row r="109" spans="3:17">
+    <row r="109" spans="2:17">
       <c r="C109" s="42" t="s">
         <v>129</v>
       </c>
@@ -16858,7 +17385,7 @@
       <c r="J109" s="18"/>
       <c r="K109" s="18"/>
     </row>
-    <row r="110" spans="3:17">
+    <row r="110" spans="2:17">
       <c r="C110" s="28" t="s">
         <v>27</v>
       </c>
@@ -16868,54 +17395,54 @@
         <v>22283</v>
       </c>
       <c r="H110" s="104">
-        <f ca="1">G113</f>
+        <f>G113</f>
         <v>21391.68</v>
       </c>
       <c r="I110" s="104">
-        <f ca="1">H113</f>
+        <f>H113</f>
         <v>22675.180800000002</v>
       </c>
       <c r="J110" s="104">
-        <f ca="1">I113</f>
+        <f>I113</f>
         <v>24239.7682752</v>
       </c>
       <c r="K110" s="104">
-        <f ca="1">J113</f>
+        <f>J113</f>
         <v>25912.3122861888</v>
       </c>
       <c r="M110" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="111" spans="3:17">
+    <row r="111" spans="2:17">
       <c r="C111" s="20" t="s">
         <v>124</v>
       </c>
       <c r="G111" s="18">
-        <f ca="1">-(G105)</f>
+        <f>-(G105)</f>
         <v>-1538.8799999999999</v>
       </c>
       <c r="H111" s="18">
-        <f ca="1">-(H105)</f>
+        <f>-(H105)</f>
         <v>-1631.2128</v>
       </c>
       <c r="I111" s="18">
-        <f ca="1">-(I105)</f>
+        <f>-(I105)</f>
         <v>-1743.7664832</v>
       </c>
       <c r="J111" s="18">
-        <f ca="1">-(J105)</f>
+        <f>-(J105)</f>
         <v>-1864.0863705407999</v>
       </c>
       <c r="K111" s="18">
-        <f ca="1">-(K105)</f>
+        <f>-(K105)</f>
         <v>-1992.708330108115</v>
       </c>
       <c r="M111" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="112" spans="3:17" ht="15" customHeight="1">
+    <row r="112" spans="2:17" ht="15" customHeight="1">
       <c r="C112" s="70" t="s">
         <v>125</v>
       </c>
@@ -16923,30 +17450,30 @@
       <c r="E112" s="67"/>
       <c r="F112" s="67"/>
       <c r="G112" s="94">
-        <f ca="1">G113-G111-G110</f>
+        <f>G113-G111-G110</f>
         <v>647.56000000000131</v>
       </c>
       <c r="H112" s="94">
-        <f ca="1">H113-H111-H110</f>
+        <f>H113-H111-H110</f>
         <v>2914.7136000000028</v>
       </c>
       <c r="I112" s="94">
-        <f ca="1">I113-I111-I110</f>
+        <f>I113-I111-I110</f>
         <v>3308.3539583999991</v>
       </c>
       <c r="J112" s="94">
-        <f ca="1">J113-J111-J110</f>
+        <f>J113-J111-J110</f>
         <v>3536.6303815296014</v>
       </c>
       <c r="K112" s="94">
-        <f ca="1">K113-K111-K110</f>
+        <f>K113-K111-K110</f>
         <v>3780.6578778551411</v>
       </c>
       <c r="M112" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="113" spans="3:17">
+    <row r="113" spans="2:17">
       <c r="C113" s="35" t="s">
         <v>28</v>
       </c>
@@ -16959,30 +17486,30 @@
         <v>22283</v>
       </c>
       <c r="G113" s="29">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" si="17"/>
         <v>21391.68</v>
       </c>
       <c r="H113" s="29">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" si="17"/>
         <v>22675.180800000002</v>
       </c>
       <c r="I113" s="29">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" si="17"/>
         <v>24239.7682752</v>
       </c>
       <c r="J113" s="29">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" si="17"/>
         <v>25912.3122861888</v>
       </c>
       <c r="K113" s="29">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" si="17"/>
         <v>27700.261833935827</v>
       </c>
       <c r="M113" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="114" spans="3:17">
+    <row r="114" spans="2:17">
       <c r="C114" s="20"/>
       <c r="E114" s="18"/>
       <c r="F114" s="18"/>
@@ -16991,7 +17518,7 @@
       <c r="J114" s="18"/>
       <c r="K114" s="18"/>
     </row>
-    <row r="115" spans="3:17">
+    <row r="115" spans="2:17">
       <c r="C115" s="43" t="s">
         <v>75</v>
       </c>
@@ -17004,7 +17531,7 @@
       <c r="J115" s="7"/>
       <c r="K115" s="7"/>
     </row>
-    <row r="116" spans="3:17">
+    <row r="116" spans="2:17">
       <c r="C116" s="28" t="s">
         <v>27</v>
       </c>
@@ -17014,25 +17541,25 @@
       </c>
       <c r="H116" s="18">
         <f ca="1">G120</f>
-        <v>35907.506097684833</v>
+        <v>32172.975915329909</v>
       </c>
       <c r="I116" s="18">
         <f ca="1">H120</f>
-        <v>5326.4073574395152</v>
+        <v>-1585.8718965047447</v>
       </c>
       <c r="J116" s="18">
         <f ca="1">I120</f>
-        <v>-21502.07229787598</v>
+        <v>-31181.986304092541</v>
       </c>
       <c r="K116" s="18">
         <f ca="1">J120</f>
-        <v>-44514.319742036285</v>
+        <v>-56636.532471279461</v>
       </c>
       <c r="M116" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="117" spans="3:17">
+    <row r="117" spans="2:17">
       <c r="C117" s="20" t="s">
         <v>62</v>
       </c>
@@ -17050,29 +17577,29 @@
       </c>
       <c r="G117" s="18">
         <f t="shared" ca="1" si="18"/>
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="H117" s="18">
         <f t="shared" ca="1" si="18"/>
-        <v>56209.901259754675</v>
+        <v>53032.152188165353</v>
       </c>
       <c r="I117" s="18">
         <f t="shared" ca="1" si="18"/>
-        <v>59962.520344684504</v>
+        <v>57194.885592412204</v>
       </c>
       <c r="J117" s="18">
         <f t="shared" ca="1" si="18"/>
-        <v>63778.752555839696</v>
+        <v>61336.45383281308</v>
       </c>
       <c r="K117" s="18">
         <f t="shared" ca="1" si="18"/>
-        <v>67967.319173978191</v>
+        <v>65763.79028180163</v>
       </c>
       <c r="M117" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="118" spans="3:17">
+    <row r="118" spans="2:17">
       <c r="C118" s="20" t="s">
         <v>63</v>
       </c>
@@ -17109,7 +17636,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="119" spans="3:17">
+    <row r="119" spans="2:17">
       <c r="C119" s="70" t="s">
         <v>64</v>
       </c>
@@ -17146,7 +17673,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="120" spans="3:17">
+    <row r="120" spans="2:17">
       <c r="C120" s="35" t="s">
         <v>28</v>
       </c>
@@ -17164,33 +17691,36 @@
       </c>
       <c r="G120" s="29">
         <f ca="1">SUM(G116:G119)</f>
-        <v>35907.506097684833</v>
+        <v>32172.975915329909</v>
       </c>
       <c r="H120" s="29">
         <f ca="1">SUM(H116:H119)</f>
-        <v>5326.4073574395152</v>
+        <v>-1585.8718965047447</v>
       </c>
       <c r="I120" s="29">
         <f ca="1">SUM(I116:I119)</f>
-        <v>-21502.07229787598</v>
+        <v>-31181.986304092541</v>
       </c>
       <c r="J120" s="29">
         <f ca="1">SUM(J116:J119)</f>
-        <v>-44514.319742036285</v>
+        <v>-56636.532471279461</v>
       </c>
       <c r="K120" s="29">
         <f ca="1">SUM(K116:K119)</f>
-        <v>-63338.000568058094</v>
+        <v>-77663.742189477838</v>
       </c>
       <c r="M120" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="121" spans="3:17">
+    <row r="121" spans="2:17">
       <c r="E121" s="34"/>
       <c r="F121" s="34"/>
     </row>
-    <row r="122" spans="3:17">
+    <row r="122" spans="2:17">
+      <c r="B122" t="s">
+        <v>316</v>
+      </c>
       <c r="C122" s="5" t="s">
         <v>131</v>
       </c>
@@ -17205,7 +17735,7 @@
       <c r="O122" s="65"/>
       <c r="P122" s="65"/>
     </row>
-    <row r="123" spans="3:17">
+    <row r="123" spans="2:17">
       <c r="C123" s="26" t="str">
         <f t="shared" ref="C123:K123" si="20">C15</f>
         <v xml:space="preserve">Fiscal year  </v>
@@ -17245,7 +17775,7 @@
       <c r="O123" s="65"/>
       <c r="P123" s="65"/>
     </row>
-    <row r="124" spans="3:17">
+    <row r="124" spans="2:17">
       <c r="C124" s="7" t="str">
         <f t="shared" ref="C124:K124" si="21">C16</f>
         <v>Fiscal year end date</v>
@@ -17285,12 +17815,12 @@
       <c r="O124" s="65"/>
       <c r="P124" s="65"/>
     </row>
-    <row r="125" spans="3:17">
+    <row r="125" spans="2:17">
       <c r="C125" s="16"/>
       <c r="O125" s="65"/>
       <c r="P125" s="65"/>
     </row>
-    <row r="126" spans="3:17">
+    <row r="126" spans="2:17">
       <c r="C126" s="19" t="s">
         <v>39</v>
       </c>
@@ -17298,7 +17828,7 @@
       <c r="P126" s="65"/>
       <c r="Q126" s="65"/>
     </row>
-    <row r="127" spans="3:17">
+    <row r="127" spans="2:17">
       <c r="C127" s="20" t="s">
         <v>45</v>
       </c>
@@ -17308,19 +17838,19 @@
       </c>
       <c r="H127" s="18">
         <f ca="1">G46</f>
-        <v>202199.73246575586</v>
+        <v>198465.20228340095</v>
       </c>
       <c r="I127" s="18">
         <f ca="1">H46</f>
-        <v>176523.72487352614</v>
+        <v>169611.44561958191</v>
       </c>
       <c r="J127" s="18">
         <f ca="1">I46</f>
-        <v>156076.92943323214</v>
+        <v>146397.01542701561</v>
       </c>
       <c r="K127" s="18">
         <f ca="1">J46</f>
-        <v>140273.77732642859</v>
+        <v>128151.56459718544</v>
       </c>
       <c r="M127" t="s">
         <v>171</v>
@@ -17328,7 +17858,7 @@
       <c r="O127" s="65"/>
       <c r="P127" s="65"/>
     </row>
-    <row r="128" spans="3:17">
+    <row r="128" spans="2:17">
       <c r="C128" s="20" t="s">
         <v>69</v>
       </c>
@@ -17353,7 +17883,7 @@
       <c r="O128" s="65"/>
       <c r="P128" s="65"/>
     </row>
-    <row r="129" spans="3:19">
+    <row r="129" spans="2:19">
       <c r="C129" s="70" t="s">
         <v>40</v>
       </c>
@@ -17362,59 +17892,59 @@
       <c r="F129" s="67"/>
       <c r="G129" s="68">
         <f ca="1">SUM(G80,G83,G85,G87,G88)</f>
-        <v>-29697.670063900441</v>
+        <v>-38670.797716599038</v>
       </c>
       <c r="H129" s="68">
         <f ca="1">SUM(H80,H83,H85,H87,H88)</f>
-        <v>-25676.007592229726</v>
+        <v>-28853.756663819047</v>
       </c>
       <c r="I129" s="68">
         <f ca="1">SUM(I80,I83,I85,I87,I88)</f>
-        <v>-20446.795440293994</v>
+        <v>-23214.430192566302</v>
       </c>
       <c r="J129" s="68">
         <f ca="1">SUM(J80,J83,J85,J87,J88)</f>
-        <v>-15803.152106803551</v>
+        <v>-18245.450829830166</v>
       </c>
       <c r="K129" s="68">
         <f ca="1">SUM(K80,K83,K85,K87,K88)</f>
-        <v>-10984.675384676419</v>
+        <v>-13004.850517383966</v>
       </c>
       <c r="M129" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="130" spans="3:19">
+    <row r="130" spans="2:19">
       <c r="C130" s="35" t="s">
         <v>102</v>
       </c>
       <c r="G130" s="29">
         <f ca="1">SUM(G127:G129)</f>
-        <v>157402.32993609956</v>
+        <v>148429.20228340095</v>
       </c>
       <c r="H130" s="29">
         <f ca="1">SUM(H127:H129)</f>
-        <v>126523.72487352614</v>
+        <v>119611.44561958191</v>
       </c>
       <c r="I130" s="29">
         <f ca="1">SUM(I127:I129)</f>
-        <v>106076.92943323214</v>
+        <v>96397.015427015605</v>
       </c>
       <c r="J130" s="29">
         <f ca="1">SUM(J127:J129)</f>
-        <v>90273.777326428593</v>
+        <v>78151.564597185439</v>
       </c>
       <c r="K130" s="29">
         <f ca="1">SUM(K127:K129)</f>
-        <v>79289.101941752175</v>
-      </c>
-    </row>
-    <row r="132" spans="3:19">
+        <v>65146.714079801473</v>
+      </c>
+    </row>
+    <row r="132" spans="2:19">
       <c r="C132" s="16" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="133" spans="3:19">
+    <row r="133" spans="2:19">
       <c r="C133" s="20" t="s">
         <v>27</v>
       </c>
@@ -17442,7 +17972,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="134" spans="3:19">
+    <row r="134" spans="2:19">
       <c r="C134" s="31" t="s">
         <v>175</v>
       </c>
@@ -17470,7 +18000,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="135" spans="3:19">
+    <row r="135" spans="2:19">
       <c r="C135" s="69" t="s">
         <v>128</v>
       </c>
@@ -17496,7 +18026,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="136" spans="3:19">
+    <row r="136" spans="2:19">
       <c r="C136" s="20" t="s">
         <v>28</v>
       </c>
@@ -17533,7 +18063,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="137" spans="3:19">
+    <row r="137" spans="2:19">
       <c r="C137" s="82" t="s">
         <v>119</v>
       </c>
@@ -17562,7 +18092,7 @@
       </c>
       <c r="S137" s="34"/>
     </row>
-    <row r="138" spans="3:19">
+    <row r="138" spans="2:19">
       <c r="D138" s="18"/>
       <c r="E138" s="18"/>
       <c r="F138" s="85"/>
@@ -17573,7 +18103,10 @@
       <c r="K138" s="86"/>
       <c r="S138" s="34"/>
     </row>
-    <row r="139" spans="3:19">
+    <row r="139" spans="2:19">
+      <c r="B139" t="s">
+        <v>316</v>
+      </c>
       <c r="C139" s="5" t="s">
         <v>43</v>
       </c>
@@ -17587,7 +18120,7 @@
       <c r="K139" s="33"/>
       <c r="R139" s="66"/>
     </row>
-    <row r="140" spans="3:19">
+    <row r="140" spans="2:19">
       <c r="C140" s="26" t="str">
         <f t="shared" ref="C140:K140" si="22">C15</f>
         <v xml:space="preserve">Fiscal year  </v>
@@ -17627,7 +18160,7 @@
       <c r="R140" s="66"/>
       <c r="S140" s="34"/>
     </row>
-    <row r="141" spans="3:19">
+    <row r="141" spans="2:19">
       <c r="C141" s="7" t="str">
         <f t="shared" ref="C141:K141" si="23">C16</f>
         <v>Fiscal year end date</v>
@@ -17666,7 +18199,7 @@
       </c>
       <c r="R141" s="66"/>
     </row>
-    <row r="142" spans="3:19">
+    <row r="142" spans="2:19">
       <c r="C142" s="20"/>
       <c r="D142" s="18"/>
       <c r="E142" s="18"/>
@@ -17678,7 +18211,7 @@
       <c r="K142" s="89"/>
       <c r="R142" s="66"/>
     </row>
-    <row r="143" spans="3:19">
+    <row r="143" spans="2:19">
       <c r="C143" s="28" t="s">
         <v>120</v>
       </c>
@@ -17696,40 +18229,40 @@
       </c>
       <c r="G143" s="18">
         <f ca="1">G148+G153</f>
-        <v>3223.1468651501777</v>
+        <v>2961.9392651501776</v>
       </c>
       <c r="H143" s="18">
         <f ca="1">H148+H153</f>
-        <v>3223.5392651501775</v>
+        <v>2961.9392651501776</v>
       </c>
       <c r="I143" s="18">
         <f ca="1">I148+I153</f>
-        <v>3223.5392651501775</v>
+        <v>2961.9392651501776</v>
       </c>
       <c r="J143" s="18">
         <f ca="1">J148+J153</f>
-        <v>3223.5392651501775</v>
+        <v>2961.9392651501776</v>
       </c>
       <c r="K143" s="18">
         <f ca="1">K148+K153</f>
-        <v>3223.5392651501775</v>
+        <v>2961.9392651501776</v>
       </c>
       <c r="M143" t="s">
         <v>177</v>
       </c>
       <c r="R143" s="34"/>
     </row>
-    <row r="144" spans="3:19">
+    <row r="144" spans="2:19">
       <c r="C144" s="39"/>
       <c r="R144" s="34"/>
     </row>
-    <row r="145" spans="3:18">
+    <row r="145" spans="2:18">
       <c r="C145" s="61" t="s">
         <v>68</v>
       </c>
       <c r="R145" s="34"/>
     </row>
-    <row r="146" spans="3:18">
+    <row r="146" spans="2:18">
       <c r="C146" s="20" t="s">
         <v>111</v>
       </c>
@@ -17763,7 +18296,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="147" spans="3:18">
+    <row r="147" spans="2:18">
       <c r="C147" s="20" t="s">
         <v>112</v>
       </c>
@@ -17800,7 +18333,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="148" spans="3:18">
+    <row r="148" spans="2:18">
       <c r="C148" s="111" t="s">
         <v>41</v>
       </c>
@@ -17815,35 +18348,35 @@
       </c>
       <c r="G148" s="112">
         <f ca="1">IF($D$7=1,AVERAGE(F147:G147)*G146,0)</f>
-        <v>261.20760000000001</v>
+        <v>0</v>
       </c>
       <c r="H148" s="112">
         <f ca="1">IF($D$7=1,AVERAGE(G147:H147)*H146,0)</f>
-        <v>261.60000000000002</v>
+        <v>0</v>
       </c>
       <c r="I148" s="112">
         <f ca="1">IF($D$7=1,AVERAGE(H147:I147)*I146,0)</f>
-        <v>261.60000000000002</v>
+        <v>0</v>
       </c>
       <c r="J148" s="112">
         <f ca="1">IF($D$7=1,AVERAGE(I147:J147)*J146,0)</f>
-        <v>261.60000000000002</v>
+        <v>0</v>
       </c>
       <c r="K148" s="112">
         <f ca="1">IF($D$7=1,AVERAGE(J147:K147)*K146,0)</f>
-        <v>261.60000000000002</v>
+        <v>0</v>
       </c>
       <c r="M148" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="149" spans="3:18">
+    <row r="149" spans="2:18">
       <c r="C149" s="49"/>
       <c r="D149" s="18"/>
       <c r="E149" s="18"/>
       <c r="F149" s="18"/>
     </row>
-    <row r="150" spans="3:18">
+    <row r="150" spans="2:18">
       <c r="C150" s="61" t="s">
         <v>67</v>
       </c>
@@ -17851,7 +18384,7 @@
       <c r="E150" s="18"/>
       <c r="F150" s="18"/>
     </row>
-    <row r="151" spans="3:18">
+    <row r="151" spans="2:18">
       <c r="C151" s="20" t="s">
         <v>112</v>
       </c>
@@ -17888,7 +18421,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="152" spans="3:18">
+    <row r="152" spans="2:18">
       <c r="C152" s="20" t="s">
         <v>111</v>
       </c>
@@ -17925,7 +18458,7 @@
       </c>
       <c r="R152" s="66"/>
     </row>
-    <row r="153" spans="3:18">
+    <row r="153" spans="2:18">
       <c r="C153" s="35" t="s">
         <v>185</v>
       </c>
@@ -17962,17 +18495,17 @@
         <v>114</v>
       </c>
     </row>
-    <row r="154" spans="3:18">
+    <row r="154" spans="2:18">
       <c r="E154" s="18"/>
     </row>
-    <row r="155" spans="3:18">
+    <row r="155" spans="2:18">
       <c r="C155" s="39" t="s">
         <v>42</v>
       </c>
       <c r="E155" s="18"/>
       <c r="F155" s="18"/>
     </row>
-    <row r="156" spans="3:18" ht="15" customHeight="1">
+    <row r="156" spans="2:18" ht="15" customHeight="1">
       <c r="C156" s="20" t="s">
         <v>115</v>
       </c>
@@ -18009,7 +18542,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="157" spans="3:18" ht="15" customHeight="1">
+    <row r="157" spans="2:18" ht="15" customHeight="1">
       <c r="C157" s="20" t="s">
         <v>4</v>
       </c>
@@ -18027,29 +18560,29 @@
       </c>
       <c r="G157" s="15">
         <f ca="1">IF($D$7=1,AVERAGE(F46,G46)*G156,0)</f>
-        <v>4744.4371106301642</v>
+        <v>0</v>
       </c>
       <c r="H157" s="15">
         <f ca="1">IF($D$7=1,AVERAGE(G46,H46)*H156,0)</f>
-        <v>4090.2133392642463</v>
+        <v>0</v>
       </c>
       <c r="I157" s="15">
         <f ca="1">IF($D$7=1,AVERAGE(H46,I46)*I156,0)</f>
-        <v>3636.4123766928992</v>
+        <v>0</v>
       </c>
       <c r="J157" s="15">
         <f ca="1">IF($D$7=1,AVERAGE(I46,J46)*J156,0)</f>
-        <v>3232.6203873851432</v>
+        <v>0</v>
       </c>
       <c r="K157" s="15">
         <f ca="1">IF($D$7=1,AVERAGE(J46,K46)*K156,0)</f>
-        <v>2913.259316698618</v>
+        <v>0</v>
       </c>
       <c r="M157" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="158" spans="3:18">
+    <row r="158" spans="2:18">
       <c r="C158" s="41"/>
       <c r="D158" s="60"/>
       <c r="E158" s="60"/>
@@ -18057,7 +18590,10 @@
       <c r="G158" s="60"/>
       <c r="H158" s="60"/>
     </row>
-    <row r="159" spans="3:18">
+    <row r="159" spans="2:18">
+      <c r="B159" t="s">
+        <v>316</v>
+      </c>
       <c r="C159" s="5" t="s">
         <v>76</v>
       </c>
@@ -18070,10 +18606,10 @@
       <c r="J159" s="5"/>
       <c r="K159" s="5"/>
     </row>
-    <row r="160" spans="3:18">
+    <row r="160" spans="2:18">
       <c r="C160" s="16"/>
     </row>
-    <row r="161" spans="3:16" ht="15" thickBot="1">
+    <row r="161" spans="2:16" ht="15" thickBot="1">
       <c r="C161" s="44" t="s">
         <v>187</v>
       </c>
@@ -18084,7 +18620,7 @@
       <c r="H161" s="45"/>
       <c r="I161" s="45"/>
     </row>
-    <row r="162" spans="3:16">
+    <row r="162" spans="2:16">
       <c r="D162" s="16"/>
       <c r="E162" s="169" t="s">
         <v>77</v>
@@ -18094,10 +18630,10 @@
       <c r="H162" s="46"/>
       <c r="I162" s="46"/>
     </row>
-    <row r="163" spans="3:16" ht="15.75" customHeight="1" thickBot="1">
+    <row r="163" spans="2:16" ht="15.75" customHeight="1" thickBot="1">
       <c r="D163" s="118">
         <f ca="1">G29</f>
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="E163" s="160">
         <v>-0.05</v>
@@ -18115,29 +18651,29 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="164" spans="3:16">
+    <row r="164" spans="2:16">
       <c r="C164" s="47"/>
       <c r="D164" s="161">
         <v>0.39</v>
       </c>
       <c r="E164" s="162">
         <f t="dataTable" ref="E164:I169" dt2D="1" dtr="1" r1="G37" r2="G38" ca="1"/>
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="F164" s="162">
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="G164" s="162">
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="H164" s="162">
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="I164" s="162">
-        <v>52298.506097684833</v>
-      </c>
-    </row>
-    <row r="165" spans="3:16">
+        <v>48563.975915329909</v>
+      </c>
+    </row>
+    <row r="165" spans="2:16">
       <c r="C165" s="168" t="s">
         <v>78</v>
       </c>
@@ -18145,22 +18681,22 @@
         <v>0.38500000000000001</v>
       </c>
       <c r="E165" s="162">
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="F165" s="162">
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="G165" s="162">
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="H165" s="162">
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="I165" s="162">
-        <v>52298.506097684833</v>
-      </c>
-    </row>
-    <row r="166" spans="3:16">
+        <v>48563.975915329909</v>
+      </c>
+    </row>
+    <row r="166" spans="2:16">
       <c r="C166" s="168" t="s">
         <v>79</v>
       </c>
@@ -18168,22 +18704,22 @@
         <v>0.38</v>
       </c>
       <c r="E166" s="162">
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="F166" s="162">
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="G166" s="162">
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="H166" s="162">
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="I166" s="162">
-        <v>52298.506097684833</v>
-      </c>
-    </row>
-    <row r="167" spans="3:16">
+        <v>48563.975915329909</v>
+      </c>
+    </row>
+    <row r="167" spans="2:16">
       <c r="C167" s="168" t="s">
         <v>80</v>
       </c>
@@ -18191,62 +18727,65 @@
         <v>0.375</v>
       </c>
       <c r="E167" s="162">
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="F167" s="162">
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="G167" s="162">
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="H167" s="162">
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="I167" s="162">
-        <v>52298.506097684833</v>
-      </c>
-    </row>
-    <row r="168" spans="3:16">
+        <v>48563.975915329909</v>
+      </c>
+    </row>
+    <row r="168" spans="2:16">
       <c r="D168" s="161">
         <v>0.37</v>
       </c>
       <c r="E168" s="162">
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="F168" s="162">
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="G168" s="162">
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="H168" s="162">
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="I168" s="162">
-        <v>52298.506097684833</v>
-      </c>
-    </row>
-    <row r="169" spans="3:16">
+        <v>48563.975915329909</v>
+      </c>
+    </row>
+    <row r="169" spans="2:16">
       <c r="D169" s="161">
         <v>0.36499999999999999</v>
       </c>
       <c r="E169" s="162">
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="F169" s="162">
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="G169" s="162">
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="H169" s="162">
-        <v>52298.506097684833</v>
+        <v>48563.975915329909</v>
       </c>
       <c r="I169" s="162">
-        <v>52298.506097684833</v>
-      </c>
-    </row>
-    <row r="171" spans="3:16">
+        <v>48563.975915329909</v>
+      </c>
+    </row>
+    <row r="171" spans="2:16">
+      <c r="B171" t="s">
+        <v>316</v>
+      </c>
       <c r="C171" s="5" t="s">
         <v>81</v>
       </c>
@@ -18259,12 +18798,12 @@
       <c r="J171" s="5"/>
       <c r="K171" s="5"/>
     </row>
-    <row r="172" spans="3:16" ht="15" thickBot="1"/>
-    <row r="173" spans="3:16" ht="15" thickBot="1">
+    <row r="172" spans="2:16" ht="15" thickBot="1"/>
+    <row r="173" spans="2:16" ht="15" thickBot="1">
       <c r="C173" t="s">
         <v>192</v>
       </c>
-      <c r="D173" s="128" t="str">
+      <c r="D173" s="293" t="str">
         <f>D12</f>
         <v>Base case</v>
       </c>
@@ -18292,7 +18831,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="174" spans="3:16">
+    <row r="174" spans="2:16">
       <c r="E174" s="127"/>
       <c r="F174" s="121" t="s">
         <v>189</v>
@@ -18318,32 +18857,62 @@
         <v>45199</v>
       </c>
     </row>
-    <row r="175" spans="3:16">
+    <row r="175" spans="2:16">
       <c r="C175" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="F175" s="157" t="str">
-        <f ca="1">OFFSET(F$180,MATCH($D$12,$C$181:$C$183,0)+MATCH($C175,$C$180:$C$195,0)-1,0)</f>
+      <c r="F175" s="157" t="str" cm="1">
+        <f t="array" ref="F175">_xlfn.LET(
+    _xlpm.n, (ROW(A1)-1)*4,
+    _xlpm.fRange, INDEX(F:F, 181 + _xlpm.n):INDEX(F:F, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
         <v>NM</v>
       </c>
-      <c r="G175" s="158">
-        <f ca="1">OFFSET(G$180,MATCH($D$12,$C$181:$C$183,0)+MATCH($C175,$C$180:$C$195,0)-1,0)</f>
+      <c r="G175" s="158" cm="1">
+        <f t="array" ref="G175">_xlfn.LET(
+    _xlpm.n, (ROW(B1)-1)*4,
+    _xlpm.fRange, INDEX(G:G, 181 + _xlpm.n):INDEX(G:G, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
         <v>-0.04</v>
       </c>
-      <c r="H175" s="158">
-        <f t="shared" ref="H175:K178" ca="1" si="28">OFFSET(H$180,MATCH($D$12,$C$181:$C$183,0)+MATCH($C175,$C$180:$C$195,0)-1,0)</f>
+      <c r="H175" s="158" cm="1">
+        <f t="array" ref="H175">_xlfn.LET(
+    _xlpm.n, (ROW(C1)-1)*4,
+    _xlpm.fRange, INDEX(H:H, 181 + _xlpm.n):INDEX(H:H, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
         <v>0.06</v>
       </c>
-      <c r="I175" s="158">
-        <f t="shared" ca="1" si="28"/>
+      <c r="I175" s="158" cm="1">
+        <f t="array" ref="I175">_xlfn.LET(
+    _xlpm.n, (ROW(D1)-1)*4,
+    _xlpm.fRange, INDEX(I:I, 181 + _xlpm.n):INDEX(I:I, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="J175" s="158">
-        <f t="shared" ca="1" si="28"/>
+      <c r="J175" s="158" cm="1">
+        <f t="array" ref="J175">_xlfn.LET(
+    _xlpm.n, (ROW(E1)-1)*4,
+    _xlpm.fRange, INDEX(J:J, 181 + _xlpm.n):INDEX(J:J, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="K175" s="158">
-        <f t="shared" ca="1" si="28"/>
+      <c r="K175" s="158" cm="1">
+        <f t="array" ref="K175">_xlfn.LET(
+    _xlpm.n, (ROW(F1)-1)*4,
+    _xlpm.fRange, INDEX(K:K, 181 + _xlpm.n):INDEX(K:K, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="M175" s="150"/>
@@ -18351,32 +18920,62 @@
       <c r="O175" s="150"/>
       <c r="P175" s="150"/>
     </row>
-    <row r="176" spans="3:16">
+    <row r="176" spans="2:16">
       <c r="C176" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="F176" s="157" t="str">
-        <f t="shared" ref="F176:G178" ca="1" si="29">OFFSET(F$180,MATCH($D$12,$C$181:$C$183,0)+MATCH($C176,$C$180:$C$195,0)-1,0)</f>
+      <c r="F176" s="157" t="str" cm="1">
+        <f t="array" ref="F176">_xlfn.LET(
+    _xlpm.n, (ROW(A2)-1)*4,
+    _xlpm.fRange, INDEX(F:F, 181 + _xlpm.n):INDEX(F:F, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX(C:C, 181 + _xlpm.n):INDEX(C:C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
         <v>NM</v>
       </c>
-      <c r="G176" s="158">
-        <f t="shared" ca="1" si="29"/>
+      <c r="G176" s="158" cm="1">
+        <f t="array" ref="G176">_xlfn.LET(
+    _xlpm.n, (ROW(B2)-1)*4,
+    _xlpm.fRange, INDEX(G:G, 181 + _xlpm.n):INDEX(G:G, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
         <v>0.378</v>
       </c>
-      <c r="H176" s="158">
-        <f t="shared" ca="1" si="28"/>
+      <c r="H176" s="158" cm="1">
+        <f t="array" ref="H176">_xlfn.LET(
+    _xlpm.n, (ROW(C2)-1)*4,
+    _xlpm.fRange, INDEX(H:H, 181 + _xlpm.n):INDEX(H:H, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
         <v>0.38100000000000001</v>
       </c>
-      <c r="I176" s="158">
-        <f t="shared" ca="1" si="28"/>
+      <c r="I176" s="158" cm="1">
+        <f t="array" ref="I176">_xlfn.LET(
+    _xlpm.n, (ROW(D2)-1)*4,
+    _xlpm.fRange, INDEX(I:I, 181 + _xlpm.n):INDEX(I:I, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
         <v>0.38200000000000001</v>
       </c>
-      <c r="J176" s="158">
-        <f t="shared" ca="1" si="28"/>
+      <c r="J176" s="158" cm="1">
+        <f t="array" ref="J176">_xlfn.LET(
+    _xlpm.n, (ROW(E2)-1)*4,
+    _xlpm.fRange, INDEX(J:J, 181 + _xlpm.n):INDEX(J:J, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
         <v>0.38200000000000001</v>
       </c>
-      <c r="K176" s="158">
-        <f t="shared" ca="1" si="28"/>
+      <c r="K176" s="158" cm="1">
+        <f t="array" ref="K176">_xlfn.LET(
+    _xlpm.n, (ROW(F2)-1)*4,
+    _xlpm.fRange, INDEX(K:K, 181 + _xlpm.n):INDEX(K:K, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
         <v>0.38200000000000001</v>
       </c>
       <c r="M176" s="150"/>
@@ -18388,28 +18987,58 @@
       <c r="C177" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="F177" s="157" t="str">
-        <f t="shared" ca="1" si="29"/>
+      <c r="F177" s="157" t="str" cm="1">
+        <f t="array" ref="F177">_xlfn.LET(
+    _xlpm.n, (ROW(A3)-1)*4,
+    _xlpm.fRange, INDEX(F:F, 181 + _xlpm.n):INDEX(F:F, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX(C:C, 181 + _xlpm.n):INDEX(C:C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
         <v>NM</v>
       </c>
-      <c r="G177" s="158">
-        <f t="shared" ca="1" si="29"/>
+      <c r="G177" s="158" cm="1">
+        <f t="array" ref="G177">_xlfn.LET(
+    _xlpm.n, (ROW(B3)-1)*4,
+    _xlpm.fRange, INDEX(G:G, 181 + _xlpm.n):INDEX(G:G, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
         <v>6.2E-2</v>
       </c>
-      <c r="H177" s="158">
-        <f t="shared" ca="1" si="28"/>
+      <c r="H177" s="158" cm="1">
+        <f t="array" ref="H177">_xlfn.LET(
+    _xlpm.n, (ROW(C3)-1)*4,
+    _xlpm.fRange, INDEX(H:H, 181 + _xlpm.n):INDEX(H:H, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
         <v>6.3E-2</v>
       </c>
-      <c r="I177" s="158">
-        <f t="shared" ca="1" si="28"/>
+      <c r="I177" s="158" cm="1">
+        <f t="array" ref="I177">_xlfn.LET(
+    _xlpm.n, (ROW(D3)-1)*4,
+    _xlpm.fRange, INDEX(I:I, 181 + _xlpm.n):INDEX(I:I, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
         <v>6.3E-2</v>
       </c>
-      <c r="J177" s="158">
-        <f t="shared" ca="1" si="28"/>
+      <c r="J177" s="158" cm="1">
+        <f t="array" ref="J177">_xlfn.LET(
+    _xlpm.n, (ROW(E3)-1)*4,
+    _xlpm.fRange, INDEX(J:J, 181 + _xlpm.n):INDEX(J:J, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
         <v>6.3E-2</v>
       </c>
-      <c r="K177" s="158">
-        <f t="shared" ca="1" si="28"/>
+      <c r="K177" s="158" cm="1">
+        <f t="array" ref="K177">_xlfn.LET(
+    _xlpm.n, (ROW(F3)-1)*4,
+    _xlpm.fRange, INDEX(K:K, 181 + _xlpm.n):INDEX(K:K, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
         <v>6.3E-2</v>
       </c>
       <c r="M177" s="150"/>
@@ -18421,28 +19050,58 @@
       <c r="C178" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="F178" s="157" t="str">
-        <f t="shared" ca="1" si="29"/>
+      <c r="F178" s="157" t="str" cm="1">
+        <f t="array" ref="F178">_xlfn.LET(
+    _xlpm.n, (ROW(A4)-1)*4,
+    _xlpm.fRange, INDEX(F:F, 181 + _xlpm.n):INDEX(F:F, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX(C:C, 181 + _xlpm.n):INDEX(C:C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
         <v>NM</v>
       </c>
-      <c r="G178" s="158">
-        <f t="shared" ca="1" si="29"/>
+      <c r="G178" s="158" cm="1">
+        <f t="array" ref="G178">_xlfn.LET(
+    _xlpm.n, (ROW(B4)-1)*4,
+    _xlpm.fRange, INDEX(G:G, 181 + _xlpm.n):INDEX(G:G, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="H178" s="158">
-        <f t="shared" ca="1" si="28"/>
+      <c r="H178" s="158" cm="1">
+        <f t="array" ref="H178">_xlfn.LET(
+    _xlpm.n, (ROW(C4)-1)*4,
+    _xlpm.fRange, INDEX(H:H, 181 + _xlpm.n):INDEX(H:H, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="I178" s="158">
-        <f t="shared" ca="1" si="28"/>
+      <c r="I178" s="158" cm="1">
+        <f t="array" ref="I178">_xlfn.LET(
+    _xlpm.n, (ROW(D4)-1)*4,
+    _xlpm.fRange, INDEX(I:I, 181 + _xlpm.n):INDEX(I:I, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="J178" s="158">
-        <f t="shared" ca="1" si="28"/>
+      <c r="J178" s="158" cm="1">
+        <f t="array" ref="J178">_xlfn.LET(
+    _xlpm.n, (ROW(E4)-1)*4,
+    _xlpm.fRange, INDEX(J:J, 181 + _xlpm.n):INDEX(J:J, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="K178" s="158">
-        <f t="shared" ca="1" si="28"/>
+      <c r="K178" s="158" cm="1">
+        <f t="array" ref="K178">_xlfn.LET(
+    _xlpm.n, (ROW(F4)-1)*4,
+    _xlpm.fRange, INDEX(K:K, 181 + _xlpm.n):INDEX(K:K, 183 + _xlpm.n),
+    _xlpm.cRange, INDEX($C:$C, 181 + _xlpm.n):INDEX($C:$C, 183 + _xlpm.n),
+    INDEX(_xlpm.fRange, _xlfn.XMATCH($D$173, _xlpm.cRange, 0))
+)</f>
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="M178" s="150"/>
@@ -18866,31 +19525,31 @@
         <v>2016</v>
       </c>
       <c r="E198" s="23">
-        <f t="shared" ref="E198:K198" si="30">E15</f>
+        <f t="shared" ref="E198:K198" si="28">E15</f>
         <v>2017</v>
       </c>
       <c r="F198" s="23">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>2018</v>
       </c>
       <c r="G198" s="24">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>2019</v>
       </c>
       <c r="H198" s="24">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>2020</v>
       </c>
       <c r="I198" s="24">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>2021</v>
       </c>
       <c r="J198" s="24">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>2022</v>
       </c>
       <c r="K198" s="24">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>2023</v>
       </c>
     </row>
@@ -18904,31 +19563,31 @@
         <v>42643</v>
       </c>
       <c r="E199" s="25">
-        <f t="shared" ref="E199:K199" si="31">E16</f>
+        <f t="shared" ref="E199:K199" si="29">E16</f>
         <v>43008</v>
       </c>
       <c r="F199" s="25">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>43372</v>
       </c>
       <c r="G199" s="25">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>43738</v>
       </c>
       <c r="H199" s="25">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>44104</v>
       </c>
       <c r="I199" s="25">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>44469</v>
       </c>
       <c r="J199" s="25">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>44834</v>
       </c>
       <c r="K199" s="25">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>45199</v>
       </c>
     </row>
@@ -18948,32 +19607,32 @@
         <v>45687</v>
       </c>
       <c r="E201" s="59">
-        <f t="shared" ref="E201:K201" si="32">E29</f>
+        <f t="shared" ref="E201:K201" si="30">E29</f>
         <v>48351</v>
       </c>
       <c r="F201" s="59">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>59531</v>
       </c>
       <c r="G201" s="59">
-        <f t="shared" ca="1" si="32"/>
-        <v>52298.506097684833</v>
+        <f t="shared" ca="1" si="30"/>
+        <v>48563.975915329909</v>
       </c>
       <c r="H201" s="59">
-        <f t="shared" ca="1" si="32"/>
-        <v>56209.901259754675</v>
+        <f t="shared" ca="1" si="30"/>
+        <v>53032.152188165353</v>
       </c>
       <c r="I201" s="59">
-        <f t="shared" ca="1" si="32"/>
-        <v>59962.520344684504</v>
+        <f t="shared" ca="1" si="30"/>
+        <v>57194.885592412204</v>
       </c>
       <c r="J201" s="59">
-        <f t="shared" ca="1" si="32"/>
-        <v>63778.752555839696</v>
+        <f t="shared" ca="1" si="30"/>
+        <v>61336.45383281308</v>
       </c>
       <c r="K201" s="59">
-        <f t="shared" ca="1" si="32"/>
-        <v>76506.881161045196</v>
+        <f t="shared" ca="1" si="30"/>
+        <v>65763.79028180163</v>
       </c>
       <c r="M201" t="s">
         <v>222</v>
@@ -18993,23 +19652,23 @@
         <v>4955.3770000000004</v>
       </c>
       <c r="G202" s="59">
-        <f ca="1">F202+(-G208+G209)/G210</f>
+        <f>F202+(-G208+G209)/G210</f>
         <v>4577.9903333333341</v>
       </c>
       <c r="H202" s="59">
-        <f t="shared" ref="H202:K202" ca="1" si="33">G202+(-H208+H209)/H210</f>
+        <f t="shared" ref="H202:K202" si="31">G202+(-H208+H209)/H210</f>
         <v>4251.3139275362328</v>
       </c>
       <c r="I202" s="59">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" si="31"/>
         <v>3968.822555538753</v>
       </c>
       <c r="J202" s="59">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" si="31"/>
         <v>3724.6420125027594</v>
       </c>
       <c r="K202" s="59">
-        <f t="shared" ca="1" si="33"/>
+        <f t="shared" si="31"/>
         <v>3513.6721082249628</v>
       </c>
       <c r="M202" t="s">
@@ -19021,36 +19680,36 @@
         <v>215</v>
       </c>
       <c r="D203" s="154">
-        <f t="shared" ref="D203:K203" si="34">D201/D202</f>
+        <f t="shared" ref="D203:K203" si="32">D201/D202</f>
         <v>8.3510333003096431</v>
       </c>
       <c r="E203" s="154">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>9.2675402061088974</v>
       </c>
       <c r="F203" s="154">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>12.0134149228202</v>
       </c>
       <c r="G203" s="154">
-        <f t="shared" ca="1" si="34"/>
-        <v>11.419090578686729</v>
+        <f t="shared" ca="1" si="32"/>
+        <v>10.608142957778904</v>
       </c>
       <c r="H203" s="154">
-        <f t="shared" ca="1" si="34"/>
-        <v>13.210256466883937</v>
+        <f t="shared" ca="1" si="32"/>
+        <v>12.474296909637797</v>
       </c>
       <c r="I203" s="154">
-        <f t="shared" ca="1" si="34"/>
-        <v>15.088021236782133</v>
+        <f t="shared" ca="1" si="32"/>
+        <v>14.411046296991277</v>
       </c>
       <c r="J203" s="154">
-        <f t="shared" ca="1" si="34"/>
-        <v>17.091823622909363</v>
+        <f t="shared" ca="1" si="32"/>
+        <v>16.467744719337009</v>
       </c>
       <c r="K203" s="154">
-        <f t="shared" ca="1" si="34"/>
-        <v>19.29796771630301</v>
+        <f t="shared" ca="1" si="32"/>
+        <v>18.716541628303556</v>
       </c>
       <c r="M203" t="s">
         <v>225</v>
@@ -19076,23 +19735,23 @@
         <v>5000.1090000000004</v>
       </c>
       <c r="G205" s="59">
-        <f ca="1">G202+F205-F202</f>
+        <f>G202+F205-F202</f>
         <v>4622.722333333335</v>
       </c>
       <c r="H205" s="59">
-        <f t="shared" ref="H205:K205" ca="1" si="35">H202+G205-G202</f>
+        <f t="shared" ref="H205:K205" si="33">H202+G205-G202</f>
         <v>4296.0459275362346</v>
       </c>
       <c r="I205" s="59">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" si="33"/>
         <v>4013.5545555387553</v>
       </c>
       <c r="J205" s="59">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" si="33"/>
         <v>3769.3740125027612</v>
       </c>
       <c r="K205" s="59">
-        <f t="shared" ca="1" si="35"/>
+        <f t="shared" si="33"/>
         <v>3558.4041082249646</v>
       </c>
       <c r="M205" t="s">
@@ -19108,32 +19767,32 @@
         <v>8.3063028961611227</v>
       </c>
       <c r="E206" s="154">
-        <f t="shared" ref="E206:F206" si="36">E201/E205</f>
+        <f t="shared" ref="E206:F206" si="34">E201/E205</f>
         <v>9.2067470826545037</v>
       </c>
       <c r="F206" s="154">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>11.905940450498179</v>
       </c>
       <c r="G206" s="154">
-        <f t="shared" ref="G206" ca="1" si="37">G201/G205</f>
-        <v>11.308639261045046</v>
+        <f t="shared" ref="G206" ca="1" si="35">G201/G205</f>
+        <v>10.505492740748627</v>
       </c>
       <c r="H206" s="154">
-        <f t="shared" ref="H206" ca="1" si="38">H201/H205</f>
-        <v>13.072824997325833</v>
+        <f t="shared" ref="H206" ca="1" si="36">H201/H205</f>
+        <v>12.34440997202725</v>
       </c>
       <c r="I206" s="154">
-        <f t="shared" ref="I206" ca="1" si="39">I201/I205</f>
-        <v>14.920085916043046</v>
+        <f t="shared" ref="I206" ca="1" si="37">I201/I205</f>
+        <v>14.250431830678009</v>
       </c>
       <c r="J206" s="154">
-        <f t="shared" ref="J206" ca="1" si="40">J201/J205</f>
-        <v>16.889361434027901</v>
+        <f t="shared" ref="J206" ca="1" si="38">J201/J205</f>
+        <v>16.272318329081745</v>
       </c>
       <c r="K206" s="154">
-        <f t="shared" ref="K206" ca="1" si="41">K201/K205</f>
-        <v>21.450172879587438</v>
+        <f t="shared" ref="K206" ca="1" si="39">K201/K205</f>
+        <v>18.481259655077938</v>
       </c>
       <c r="M206" t="s">
         <v>227</v>
@@ -19175,23 +19834,23 @@
         <v>224</v>
       </c>
       <c r="G209" s="239">
-        <f ca="1">G33</f>
+        <f>G33</f>
         <v>5126.3999999999996</v>
       </c>
       <c r="H209" s="239">
-        <f ca="1">H33</f>
+        <f>H33</f>
         <v>5433.9839999999995</v>
       </c>
       <c r="I209" s="239">
-        <f ca="1">I33</f>
+        <f>I33</f>
         <v>5808.9288959999994</v>
       </c>
       <c r="J209" s="239">
-        <f ca="1">J33</f>
+        <f>J33</f>
         <v>6209.7449898239993</v>
       </c>
       <c r="K209" s="239">
-        <f ca="1">K33</f>
+        <f>K33</f>
         <v>6638.2173941218552</v>
       </c>
       <c r="M209" t="s">
@@ -19272,19 +19931,19 @@
         <v>4745.3980000000001</v>
       </c>
       <c r="H213" s="101">
-        <f ca="1">G215</f>
+        <f>G215</f>
         <v>4368.0113333333338</v>
       </c>
       <c r="I213" s="101">
-        <f t="shared" ref="I213:K213" ca="1" si="42">H215</f>
+        <f t="shared" ref="I213:K213" si="40">H215</f>
         <v>4041.3349275362325</v>
       </c>
       <c r="J213" s="101">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" si="40"/>
         <v>3758.8435555387528</v>
       </c>
       <c r="K213" s="101">
-        <f t="shared" ca="1" si="42"/>
+        <f t="shared" si="40"/>
         <v>3514.6630125027591</v>
       </c>
       <c r="M213" t="s">
@@ -19296,23 +19955,23 @@
         <v>295</v>
       </c>
       <c r="G214" s="59">
-        <f ca="1">(-G208+G209)/G210</f>
+        <f>(-G208+G209)/G210</f>
         <v>-377.38666666666671</v>
       </c>
       <c r="H214" s="59">
-        <f t="shared" ref="H214:K214" ca="1" si="43">(-H208+H209)/H210</f>
+        <f t="shared" ref="H214:K214" si="41">(-H208+H209)/H210</f>
         <v>-326.67640579710149</v>
       </c>
       <c r="I214" s="59">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" si="41"/>
         <v>-282.49137199747958</v>
       </c>
       <c r="J214" s="59">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" si="41"/>
         <v>-244.18054303599359</v>
       </c>
       <c r="K214" s="59">
-        <f t="shared" ca="1" si="43"/>
+        <f t="shared" si="41"/>
         <v>-210.96990427779639</v>
       </c>
       <c r="M214" t="s">
@@ -19324,23 +19983,23 @@
         <v>296</v>
       </c>
       <c r="G215" s="59">
-        <f ca="1">SUM(G213:G214)</f>
+        <f>SUM(G213:G214)</f>
         <v>4368.0113333333338</v>
       </c>
       <c r="H215" s="59">
-        <f t="shared" ref="H215:K215" ca="1" si="44">SUM(H213:H214)</f>
+        <f t="shared" ref="H215:K215" si="42">SUM(H213:H214)</f>
         <v>4041.3349275362325</v>
       </c>
       <c r="I215" s="59">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" si="42"/>
         <v>3758.8435555387528</v>
       </c>
       <c r="J215" s="59">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" si="42"/>
         <v>3514.6630125027591</v>
       </c>
       <c r="K215" s="59">
-        <f t="shared" ca="1" si="44"/>
+        <f t="shared" si="42"/>
         <v>3303.6931082249625</v>
       </c>
       <c r="M215" t="s">
@@ -19355,23 +20014,23 @@
       <c r="E216" s="16"/>
       <c r="F216" s="16"/>
       <c r="G216" s="101">
-        <f ca="1">AVERAGE(G215,G213)</f>
+        <f>AVERAGE(G215,G213)</f>
         <v>4556.7046666666665</v>
       </c>
       <c r="H216" s="101">
-        <f t="shared" ref="H216:K216" ca="1" si="45">AVERAGE(H215,H213)</f>
+        <f t="shared" ref="H216:K216" si="43">AVERAGE(H215,H213)</f>
         <v>4204.6731304347832</v>
       </c>
       <c r="I216" s="101">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" si="43"/>
         <v>3900.0892415374929</v>
       </c>
       <c r="J216" s="101">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" si="43"/>
         <v>3636.7532840207559</v>
       </c>
       <c r="K216" s="101">
-        <f t="shared" ca="1" si="45"/>
+        <f t="shared" si="43"/>
         <v>3409.1780603638608</v>
       </c>
       <c r="M216" t="s">
@@ -19401,32 +20060,32 @@
         <v>45687</v>
       </c>
       <c r="E218" s="101">
-        <f t="shared" ref="E218:K218" si="46">E29</f>
+        <f t="shared" ref="E218:K218" si="44">E29</f>
         <v>48351</v>
       </c>
       <c r="F218" s="101">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>59531</v>
       </c>
       <c r="G218" s="101">
-        <f t="shared" ca="1" si="46"/>
-        <v>52298.506097684833</v>
+        <f t="shared" ca="1" si="44"/>
+        <v>48563.975915329909</v>
       </c>
       <c r="H218" s="101">
-        <f t="shared" ca="1" si="46"/>
-        <v>56209.901259754675</v>
+        <f t="shared" ca="1" si="44"/>
+        <v>53032.152188165353</v>
       </c>
       <c r="I218" s="101">
-        <f t="shared" ca="1" si="46"/>
-        <v>59962.520344684504</v>
+        <f t="shared" ca="1" si="44"/>
+        <v>57194.885592412204</v>
       </c>
       <c r="J218" s="101">
-        <f t="shared" ca="1" si="46"/>
-        <v>63778.752555839696</v>
+        <f t="shared" ca="1" si="44"/>
+        <v>61336.45383281308</v>
       </c>
       <c r="K218" s="101">
-        <f t="shared" ca="1" si="46"/>
-        <v>67967.319173978191</v>
+        <f t="shared" ca="1" si="44"/>
+        <v>65763.79028180163</v>
       </c>
       <c r="M218" t="s">
         <v>308</v>
@@ -19441,28 +20100,28 @@
         <v>5.830980366406191E-2</v>
       </c>
       <c r="F219" s="184">
-        <f t="shared" ref="F219:K219" si="47">F218/E218-1</f>
+        <f t="shared" ref="F219:K219" si="45">F218/E218-1</f>
         <v>0.23122582780087275</v>
       </c>
       <c r="G219" s="184">
-        <f t="shared" ca="1" si="47"/>
-        <v>-0.12149122141934732</v>
+        <f t="shared" ca="1" si="45"/>
+        <v>-0.18422375039340999</v>
       </c>
       <c r="H219" s="184">
-        <f t="shared" ca="1" si="47"/>
-        <v>7.4789806706218487E-2</v>
+        <f t="shared" ca="1" si="45"/>
+        <v>9.2005981565957518E-2</v>
       </c>
       <c r="I219" s="184">
-        <f t="shared" ca="1" si="47"/>
-        <v>6.6760819727976317E-2</v>
+        <f t="shared" ca="1" si="45"/>
+        <v>7.8494521389154581E-2</v>
       </c>
       <c r="J219" s="184">
-        <f t="shared" ca="1" si="47"/>
-        <v>6.364362587193173E-2</v>
+        <f t="shared" ca="1" si="45"/>
+        <v>7.2411513678249495E-2</v>
       </c>
       <c r="K219" s="184">
-        <f t="shared" ca="1" si="47"/>
-        <v>6.5673385732518241E-2</v>
+        <f t="shared" ca="1" si="45"/>
+        <v>7.2181160995324234E-2</v>
       </c>
       <c r="M219" t="s">
         <v>309</v>
@@ -19487,7 +20146,7 @@
       <formula>#REF!=$C192</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7" xr:uid="{B45F508E-62FE-4C13-BDC4-DAF07368D71A}">
       <formula1>"0,1"</formula1>
     </dataValidation>
@@ -53370,11 +54029,11 @@
       <c r="F23" s="3">
         <v>5686</v>
       </c>
-      <c r="G23" s="304"/>
-      <c r="H23" s="304"/>
-      <c r="I23" s="304"/>
-      <c r="J23" s="304"/>
-      <c r="K23" s="304"/>
+      <c r="G23" s="303"/>
+      <c r="H23" s="303"/>
+      <c r="I23" s="303"/>
+      <c r="J23" s="303"/>
+      <c r="K23" s="303"/>
       <c r="M23" t="s">
         <v>95</v>
       </c>
@@ -53392,11 +54051,11 @@
       <c r="F24" s="3">
         <v>-3240</v>
       </c>
-      <c r="G24" s="304"/>
-      <c r="H24" s="304"/>
-      <c r="I24" s="304"/>
-      <c r="J24" s="304"/>
-      <c r="K24" s="304"/>
+      <c r="G24" s="303"/>
+      <c r="H24" s="303"/>
+      <c r="I24" s="303"/>
+      <c r="J24" s="303"/>
+      <c r="K24" s="303"/>
       <c r="M24" t="s">
         <v>94</v>
       </c>
@@ -54181,23 +54840,23 @@
       <c r="F49" s="3">
         <v>41304</v>
       </c>
-      <c r="G49" s="304">
+      <c r="G49" s="303">
         <f>G99</f>
         <v>44900.8704</v>
       </c>
-      <c r="H49" s="304">
+      <c r="H49" s="303">
         <f t="shared" ref="H49:K49" si="20">H99</f>
         <v>48442.606847999996</v>
       </c>
-      <c r="I49" s="304">
+      <c r="I49" s="303">
         <f t="shared" si="20"/>
         <v>51939.081648767991</v>
       </c>
-      <c r="J49" s="304">
+      <c r="J49" s="303">
         <f t="shared" si="20"/>
         <v>55367.186487757041</v>
       </c>
-      <c r="K49" s="304">
+      <c r="K49" s="303">
         <f t="shared" si="20"/>
         <v>58700.839593715194</v>
       </c>
@@ -54398,23 +55057,23 @@
       <c r="F56" s="3">
         <v>11964</v>
       </c>
-      <c r="G56" s="304">
+      <c r="G56" s="303">
         <f>$F$56</f>
         <v>11964</v>
       </c>
-      <c r="H56" s="304">
+      <c r="H56" s="303">
         <f t="shared" ref="H56:K56" si="26">$F$56</f>
         <v>11964</v>
       </c>
-      <c r="I56" s="304">
+      <c r="I56" s="303">
         <f t="shared" si="26"/>
         <v>11964</v>
       </c>
-      <c r="J56" s="304">
+      <c r="J56" s="303">
         <f t="shared" si="26"/>
         <v>11964</v>
       </c>
-      <c r="K56" s="304">
+      <c r="K56" s="303">
         <f t="shared" si="26"/>
         <v>11964</v>
       </c>
@@ -54580,23 +55239,23 @@
       <c r="F62" s="3">
         <v>70400</v>
       </c>
-      <c r="G62" s="304">
+      <c r="G62" s="303">
         <f>G119</f>
         <v>34640.271323199995</v>
       </c>
-      <c r="H62" s="304">
+      <c r="H62" s="303">
         <f t="shared" ref="H62:K62" si="31">H119</f>
         <v>3339.8331014399882</v>
       </c>
-      <c r="I62" s="304">
+      <c r="I62" s="303">
         <f t="shared" si="31"/>
         <v>-23794.909776808025</v>
       </c>
-      <c r="J62" s="304">
+      <c r="J62" s="303">
         <f t="shared" si="31"/>
         <v>-46788.084414655139</v>
       </c>
-      <c r="K62" s="304">
+      <c r="K62" s="303">
         <f t="shared" si="31"/>
         <v>-65353.922603513725</v>
       </c>
@@ -56047,75 +56706,75 @@
       <c r="F120" s="34"/>
     </row>
     <row r="121" spans="2:13">
-      <c r="C121" s="301" t="s">
+      <c r="C121" s="20" t="s">
         <v>335</v>
       </c>
-      <c r="D121" s="302">
+      <c r="D121" s="301">
         <f t="shared" ref="D121:E121" si="72">D117/D116</f>
         <v>-0.26677172937597127</v>
       </c>
-      <c r="E121" s="302">
+      <c r="E121" s="301">
         <f t="shared" si="72"/>
         <v>-0.2647928688134682</v>
       </c>
-      <c r="F121" s="302">
+      <c r="F121" s="301">
         <f>F117/F116</f>
         <v>-0.23072012900841579</v>
       </c>
-      <c r="G121" s="303">
+      <c r="G121" s="302">
         <f>$F$121</f>
         <v>-0.23072012900841579</v>
       </c>
-      <c r="H121" s="303">
+      <c r="H121" s="302">
         <f t="shared" ref="H121:K121" si="73">$F$121</f>
         <v>-0.23072012900841579</v>
       </c>
-      <c r="I121" s="303">
+      <c r="I121" s="302">
         <f t="shared" si="73"/>
         <v>-0.23072012900841579</v>
       </c>
-      <c r="J121" s="303">
+      <c r="J121" s="302">
         <f t="shared" si="73"/>
         <v>-0.23072012900841579</v>
       </c>
-      <c r="K121" s="303">
+      <c r="K121" s="302">
         <f t="shared" si="73"/>
         <v>-0.23072012900841579</v>
       </c>
     </row>
     <row r="122" spans="2:13">
-      <c r="C122" s="301" t="s">
+      <c r="C122" s="20" t="s">
         <v>336</v>
       </c>
-      <c r="D122" s="302">
+      <c r="D122" s="301">
         <f t="shared" ref="D122:E122" si="74">D118/D116</f>
         <v>-0.63475386871538952</v>
       </c>
-      <c r="E122" s="302">
+      <c r="E122" s="301">
         <f t="shared" si="74"/>
         <v>-0.68252983392277311</v>
       </c>
-      <c r="F122" s="302">
+      <c r="F122" s="301">
         <f>F118/F116</f>
         <v>-1.2271925551393392</v>
       </c>
-      <c r="G122" s="302">
+      <c r="G122" s="301">
         <f t="shared" ref="G122:K122" si="75">G118/G116</f>
         <v>-1.4315927882201724</v>
       </c>
-      <c r="H122" s="302">
+      <c r="H122" s="301">
         <f t="shared" si="75"/>
         <v>-1.3165482139459632</v>
       </c>
-      <c r="I122" s="302">
+      <c r="I122" s="301">
         <f t="shared" si="75"/>
         <v>-1.2246158831403147</v>
       </c>
-      <c r="J122" s="302">
+      <c r="J122" s="301">
         <f t="shared" si="75"/>
         <v>-1.1451174014990704</v>
       </c>
-      <c r="K122" s="302">
+      <c r="K122" s="301">
         <f t="shared" si="75"/>
         <v>-1.0708072807834614</v>
       </c>
@@ -65386,7 +66045,7 @@
   <sheetPr codeName="Sheet7">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="C1:T157"/>
+  <dimension ref="B1:T157"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="2" width="1.7265625" customWidth="1"/>
@@ -65399,8 +66058,11 @@
     <col min="18" max="19" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:19" ht="15" thickBot="1"/>
-    <row r="2" spans="3:19" ht="15" thickBot="1">
+    <row r="1" spans="2:19" ht="15" thickBot="1"/>
+    <row r="2" spans="2:19" ht="15" thickBot="1">
+      <c r="B2" t="s">
+        <v>316</v>
+      </c>
       <c r="C2" s="63" t="str">
         <f>"Financial Statement Model for "&amp;D5</f>
         <v>Financial Statement Model for Apple</v>
@@ -65414,7 +66076,7 @@
       <c r="J2" s="48"/>
       <c r="K2" s="48"/>
     </row>
-    <row r="3" spans="3:19">
+    <row r="3" spans="2:19">
       <c r="C3" s="2" t="s">
         <v>46</v>
       </c>
@@ -65424,7 +66086,7 @@
       <c r="G3" s="40"/>
       <c r="H3" s="40"/>
     </row>
-    <row r="5" spans="3:19">
+    <row r="5" spans="2:19">
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
@@ -65432,7 +66094,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="3:19">
+    <row r="6" spans="2:19">
       <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
@@ -65440,7 +66102,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="3:19">
+    <row r="7" spans="2:19">
       <c r="C7" t="s">
         <v>109</v>
       </c>
@@ -65448,7 +66110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="3:19">
+    <row r="8" spans="2:19">
       <c r="C8" t="s">
         <v>73</v>
       </c>
@@ -65456,7 +66118,7 @@
         <v>171.25</v>
       </c>
     </row>
-    <row r="9" spans="3:19">
+    <row r="9" spans="2:19">
       <c r="C9" t="s">
         <v>9</v>
       </c>
@@ -65464,7 +66126,7 @@
         <v>43500</v>
       </c>
     </row>
-    <row r="10" spans="3:19">
+    <row r="10" spans="2:19">
       <c r="C10" s="1" t="s">
         <v>8</v>
       </c>
@@ -65472,7 +66134,7 @@
         <v>43372</v>
       </c>
     </row>
-    <row r="11" spans="3:19" ht="15" customHeight="1">
+    <row r="11" spans="2:19" ht="15" customHeight="1">
       <c r="C11" t="s">
         <v>291</v>
       </c>
@@ -65480,7 +66142,10 @@
         <v>4745.3980000000001</v>
       </c>
     </row>
-    <row r="13" spans="3:19">
+    <row r="13" spans="2:19">
+      <c r="B13" t="s">
+        <v>316</v>
+      </c>
       <c r="C13" s="5" t="s">
         <v>19</v>
       </c>
@@ -65493,7 +66158,7 @@
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
     </row>
-    <row r="14" spans="3:19">
+    <row r="14" spans="2:19">
       <c r="C14" t="s">
         <v>10</v>
       </c>
@@ -65530,7 +66195,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="15" spans="3:19">
+    <row r="15" spans="2:19">
       <c r="C15" s="10" t="s">
         <v>7</v>
       </c>
@@ -65576,7 +66241,7 @@
       <c r="R15" s="64"/>
       <c r="S15" s="64"/>
     </row>
-    <row r="16" spans="3:19">
+    <row r="16" spans="2:19">
       <c r="C16" s="12"/>
       <c r="D16" s="13"/>
       <c r="E16" s="14"/>
@@ -66169,7 +66834,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="33" spans="3:20">
+    <row r="33" spans="2:20">
       <c r="C33" s="27" t="s">
         <v>72</v>
       </c>
@@ -66209,16 +66874,16 @@
         <v>98</v>
       </c>
     </row>
-    <row r="34" spans="3:20">
+    <row r="34" spans="2:20">
       <c r="C34" s="20"/>
       <c r="G34" s="38"/>
     </row>
-    <row r="35" spans="3:20">
+    <row r="35" spans="2:20">
       <c r="C35" s="19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="3:20">
+    <row r="36" spans="2:20">
       <c r="C36" s="20" t="s">
         <v>1</v>
       </c>
@@ -66258,7 +66923,7 @@
       <c r="S36" s="22"/>
       <c r="T36" s="22"/>
     </row>
-    <row r="37" spans="3:20">
+    <row r="37" spans="2:20">
       <c r="C37" s="20" t="s">
         <v>230</v>
       </c>
@@ -66301,7 +66966,7 @@
       <c r="S37" s="22"/>
       <c r="T37" s="22"/>
     </row>
-    <row r="38" spans="3:20">
+    <row r="38" spans="2:20">
       <c r="C38" s="20" t="s">
         <v>231</v>
       </c>
@@ -66344,7 +67009,7 @@
       <c r="S38" s="22"/>
       <c r="T38" s="22"/>
     </row>
-    <row r="39" spans="3:20">
+    <row r="39" spans="2:20">
       <c r="C39" s="20" t="s">
         <v>233</v>
       </c>
@@ -66387,7 +67052,7 @@
       <c r="S39" s="22"/>
       <c r="T39" s="22"/>
     </row>
-    <row r="40" spans="3:20">
+    <row r="40" spans="2:20">
       <c r="C40" s="20" t="s">
         <v>0</v>
       </c>
@@ -66430,11 +67095,14 @@
       <c r="S40" s="22"/>
       <c r="T40" s="22"/>
     </row>
-    <row r="41" spans="3:20">
+    <row r="41" spans="2:20">
       <c r="C41" s="20"/>
       <c r="G41" s="38"/>
     </row>
-    <row r="42" spans="3:20">
+    <row r="42" spans="2:20">
+      <c r="B42" t="s">
+        <v>316</v>
+      </c>
       <c r="C42" s="5" t="s">
         <v>20</v>
       </c>
@@ -66447,7 +67115,7 @@
       <c r="J42" s="7"/>
       <c r="K42" s="7"/>
     </row>
-    <row r="43" spans="3:20">
+    <row r="43" spans="2:20">
       <c r="C43" s="26" t="str">
         <f>C14</f>
         <v xml:space="preserve">Fiscal year  </v>
@@ -66482,7 +67150,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="44" spans="3:20">
+    <row r="44" spans="2:20">
       <c r="C44" s="7" t="str">
         <f>C15</f>
         <v>Fiscal year end date</v>
@@ -66517,7 +67185,7 @@
         <v>45199</v>
       </c>
     </row>
-    <row r="45" spans="3:20">
+    <row r="45" spans="2:20">
       <c r="C45" t="s">
         <v>138</v>
       </c>
@@ -66554,7 +67222,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="46" spans="3:20">
+    <row r="46" spans="2:20">
       <c r="C46" t="s">
         <v>54</v>
       </c>
@@ -66589,7 +67257,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="47" spans="3:20">
+    <row r="47" spans="2:20">
       <c r="C47" t="s">
         <v>55</v>
       </c>
@@ -66624,7 +67292,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="48" spans="3:20">
+    <row r="48" spans="2:20">
       <c r="C48" t="s">
         <v>108</v>
       </c>
@@ -66661,7 +67329,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="49" spans="3:13">
+    <row r="49" spans="2:13">
       <c r="C49" t="s">
         <v>21</v>
       </c>
@@ -66696,7 +67364,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="50" spans="3:13">
+    <row r="50" spans="2:13">
       <c r="C50" t="s">
         <v>56</v>
       </c>
@@ -66731,7 +67399,10 @@
         <v>103</v>
       </c>
     </row>
-    <row r="51" spans="3:13">
+    <row r="51" spans="2:13">
+      <c r="B51" t="s">
+        <v>316</v>
+      </c>
       <c r="C51" s="27" t="s">
         <v>22</v>
       </c>
@@ -66765,7 +67436,7 @@
         <v>296433.42393223592</v>
       </c>
     </row>
-    <row r="52" spans="3:13">
+    <row r="52" spans="2:13">
       <c r="C52" s="28"/>
       <c r="D52" s="18"/>
       <c r="E52" s="18"/>
@@ -66776,7 +67447,7 @@
       <c r="J52" s="18"/>
       <c r="K52" s="18"/>
     </row>
-    <row r="53" spans="3:13">
+    <row r="53" spans="2:13">
       <c r="C53" s="28" t="s">
         <v>57</v>
       </c>
@@ -66811,7 +67482,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="54" spans="3:13">
+    <row r="54" spans="2:13">
       <c r="C54" s="28" t="s">
         <v>117</v>
       </c>
@@ -66846,7 +67517,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="55" spans="3:13">
+    <row r="55" spans="2:13">
       <c r="C55" s="28" t="s">
         <v>58</v>
       </c>
@@ -66883,7 +67554,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="56" spans="3:13">
+    <row r="56" spans="2:13">
       <c r="C56" s="28" t="s">
         <v>60</v>
       </c>
@@ -66918,7 +67589,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="57" spans="3:13">
+    <row r="57" spans="2:13">
       <c r="C57" s="28" t="s">
         <v>122</v>
       </c>
@@ -66955,7 +67626,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="3:13" ht="15.75" customHeight="1">
+    <row r="58" spans="2:13" ht="15.75" customHeight="1">
       <c r="C58" s="28" t="s">
         <v>59</v>
       </c>
@@ -66990,7 +67661,10 @@
         <v>103</v>
       </c>
     </row>
-    <row r="59" spans="3:13">
+    <row r="59" spans="2:13">
+      <c r="B59" t="s">
+        <v>316</v>
+      </c>
       <c r="C59" s="27" t="s">
         <v>24</v>
       </c>
@@ -67024,7 +67698,7 @@
         <v>293807.14922034822</v>
       </c>
     </row>
-    <row r="60" spans="3:13">
+    <row r="60" spans="2:13">
       <c r="C60" s="27"/>
       <c r="D60" s="17"/>
       <c r="E60" s="17"/>
@@ -67035,7 +67709,7 @@
       <c r="J60" s="18"/>
       <c r="K60" s="18"/>
     </row>
-    <row r="61" spans="3:13">
+    <row r="61" spans="2:13">
       <c r="C61" s="28" t="s">
         <v>61</v>
       </c>
@@ -67070,7 +67744,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="62" spans="3:13" ht="15.75" customHeight="1">
+    <row r="62" spans="2:13" ht="15.75" customHeight="1">
       <c r="C62" s="28" t="s">
         <v>44</v>
       </c>
@@ -67106,7 +67780,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="63" spans="3:13" ht="15.75" customHeight="1">
+    <row r="63" spans="2:13" ht="15.75" customHeight="1">
       <c r="C63" s="28" t="s">
         <v>121</v>
       </c>
@@ -67141,7 +67815,10 @@
         <v>100</v>
       </c>
     </row>
-    <row r="64" spans="3:13">
+    <row r="64" spans="2:13">
+      <c r="B64" t="s">
+        <v>316</v>
+      </c>
       <c r="C64" s="27" t="s">
         <v>25</v>
       </c>
@@ -67523,7 +68200,7 @@
       <c r="J80" s="18"/>
       <c r="K80" s="18"/>
     </row>
-    <row r="81" spans="3:13">
+    <row r="81" spans="2:13">
       <c r="C81" t="s">
         <v>35</v>
       </c>
@@ -67551,7 +68228,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="82" spans="3:13">
+    <row r="82" spans="2:13">
       <c r="C82" s="16" t="s">
         <v>36</v>
       </c>
@@ -67576,14 +68253,14 @@
         <v>-15791.814258999997</v>
       </c>
     </row>
-    <row r="83" spans="3:13">
+    <row r="83" spans="2:13">
       <c r="G83" s="18"/>
       <c r="H83" s="18"/>
       <c r="I83" s="18"/>
       <c r="J83" s="18"/>
       <c r="K83" s="18"/>
     </row>
-    <row r="84" spans="3:13">
+    <row r="84" spans="2:13">
       <c r="C84" t="s">
         <v>67</v>
       </c>
@@ -67608,7 +68285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="3:13">
+    <row r="85" spans="2:13">
       <c r="C85" t="s">
         <v>23</v>
       </c>
@@ -67636,7 +68313,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="86" spans="3:13">
+    <row r="86" spans="2:13">
       <c r="C86" t="s">
         <v>70</v>
       </c>
@@ -67664,7 +68341,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="87" spans="3:13">
+    <row r="87" spans="2:13">
       <c r="C87" t="s">
         <v>71</v>
       </c>
@@ -67692,7 +68369,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="88" spans="3:13">
+    <row r="88" spans="2:13">
       <c r="C88" s="16" t="s">
         <v>37</v>
       </c>
@@ -67717,14 +68394,14 @@
         <v>-86791</v>
       </c>
     </row>
-    <row r="89" spans="3:13">
+    <row r="89" spans="2:13">
       <c r="G89" s="18"/>
       <c r="H89" s="18"/>
       <c r="I89" s="18"/>
       <c r="J89" s="18"/>
       <c r="K89" s="18"/>
     </row>
-    <row r="90" spans="3:13">
+    <row r="90" spans="2:13">
       <c r="C90" s="16" t="s">
         <v>38</v>
       </c>
@@ -67749,7 +68426,10 @@
         <v>-10801.321625207391</v>
       </c>
     </row>
-    <row r="92" spans="3:13">
+    <row r="92" spans="2:13">
+      <c r="B92" t="s">
+        <v>316</v>
+      </c>
       <c r="C92" s="5" t="s">
         <v>29</v>
       </c>
@@ -67762,7 +68442,7 @@
       <c r="J92" s="7"/>
       <c r="K92" s="7"/>
     </row>
-    <row r="93" spans="3:13">
+    <row r="93" spans="2:13">
       <c r="C93" s="26" t="str">
         <f t="shared" ref="C93:K93" si="17">C14</f>
         <v xml:space="preserve">Fiscal year  </v>
@@ -67800,7 +68480,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="94" spans="3:13">
+    <row r="94" spans="2:13">
       <c r="C94" s="7" t="str">
         <f t="shared" ref="C94:K94" si="18">C15</f>
         <v>Fiscal year end date</v>
@@ -67838,7 +68518,7 @@
         <v>45199</v>
       </c>
     </row>
-    <row r="95" spans="3:13">
+    <row r="95" spans="2:13">
       <c r="C95" s="16"/>
       <c r="G95" s="76" t="s">
         <v>116</v>
@@ -67848,7 +68528,7 @@
       <c r="J95" s="76"/>
       <c r="K95" s="76"/>
     </row>
-    <row r="96" spans="3:13">
+    <row r="96" spans="2:13">
       <c r="C96" s="28" t="s">
         <v>27</v>
       </c>
@@ -67876,7 +68556,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="97" spans="3:17">
+    <row r="97" spans="2:17">
       <c r="C97" s="31" t="s">
         <v>30</v>
       </c>
@@ -67910,7 +68590,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="98" spans="3:17">
+    <row r="98" spans="2:17">
       <c r="C98" s="69" t="s">
         <v>31</v>
       </c>
@@ -67947,7 +68627,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="99" spans="3:17">
+    <row r="99" spans="2:17">
       <c r="C99" s="35" t="s">
         <v>28</v>
       </c>
@@ -67984,13 +68664,13 @@
         <v>164</v>
       </c>
     </row>
-    <row r="100" spans="3:17">
+    <row r="100" spans="2:17">
       <c r="C100" s="28"/>
       <c r="M100" s="19" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="101" spans="3:17">
+    <row r="101" spans="2:17">
       <c r="C101" s="28" t="s">
         <v>123</v>
       </c>
@@ -68033,7 +68713,7 @@
       <c r="P101" s="65"/>
       <c r="Q101" s="65"/>
     </row>
-    <row r="102" spans="3:17">
+    <row r="102" spans="2:17">
       <c r="C102" s="28"/>
       <c r="D102" s="4"/>
       <c r="E102" s="4"/>
@@ -68047,7 +68727,10 @@
       <c r="P102" s="65"/>
       <c r="Q102" s="65"/>
     </row>
-    <row r="103" spans="3:17">
+    <row r="103" spans="2:17">
+      <c r="B103" t="s">
+        <v>316</v>
+      </c>
       <c r="C103" s="90" t="s">
         <v>130</v>
       </c>
@@ -68063,7 +68746,7 @@
       <c r="P103" s="65"/>
       <c r="Q103" s="65"/>
     </row>
-    <row r="104" spans="3:17">
+    <row r="104" spans="2:17">
       <c r="C104" s="28" t="s">
         <v>155</v>
       </c>
@@ -68106,7 +68789,7 @@
       <c r="P104" s="65"/>
       <c r="Q104" s="65"/>
     </row>
-    <row r="105" spans="3:17">
+    <row r="105" spans="2:17">
       <c r="C105" s="20" t="s">
         <v>156</v>
       </c>
@@ -68146,7 +68829,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="106" spans="3:17">
+    <row r="106" spans="2:17">
       <c r="C106" s="27" t="s">
         <v>110</v>
       </c>
@@ -68186,7 +68869,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="107" spans="3:17">
+    <row r="107" spans="2:17">
       <c r="C107" s="28"/>
       <c r="D107" s="18"/>
       <c r="E107" s="18"/>
@@ -68196,7 +68879,10 @@
       <c r="J107" s="18"/>
       <c r="K107" s="18"/>
     </row>
-    <row r="108" spans="3:17">
+    <row r="108" spans="2:17">
+      <c r="B108" t="s">
+        <v>316</v>
+      </c>
       <c r="C108" s="42" t="s">
         <v>129</v>
       </c>
@@ -68208,7 +68894,7 @@
       <c r="J108" s="18"/>
       <c r="K108" s="18"/>
     </row>
-    <row r="109" spans="3:17">
+    <row r="109" spans="2:17">
       <c r="C109" s="28" t="s">
         <v>27</v>
       </c>
@@ -68237,7 +68923,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="110" spans="3:17">
+    <row r="110" spans="2:17">
       <c r="C110" s="20" t="s">
         <v>124</v>
       </c>
@@ -68265,7 +68951,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="111" spans="3:17" ht="15" customHeight="1">
+    <row r="111" spans="2:17" ht="15" customHeight="1">
       <c r="C111" s="70" t="s">
         <v>125</v>
       </c>
@@ -68296,7 +68982,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="112" spans="3:17">
+    <row r="112" spans="2:17">
       <c r="C112" s="35" t="s">
         <v>28</v>
       </c>
@@ -68332,7 +69018,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="113" spans="3:17">
+    <row r="113" spans="2:17">
       <c r="C113" s="20"/>
       <c r="E113" s="18"/>
       <c r="F113" s="18"/>
@@ -68341,7 +69027,10 @@
       <c r="J113" s="18"/>
       <c r="K113" s="18"/>
     </row>
-    <row r="114" spans="3:17">
+    <row r="114" spans="2:17">
+      <c r="B114" t="s">
+        <v>316</v>
+      </c>
       <c r="C114" s="43" t="s">
         <v>75</v>
       </c>
@@ -68354,7 +69043,7 @@
       <c r="J114" s="7"/>
       <c r="K114" s="7"/>
     </row>
-    <row r="115" spans="3:17">
+    <row r="115" spans="2:17">
       <c r="C115" s="28" t="s">
         <v>27</v>
       </c>
@@ -68382,7 +69071,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="116" spans="3:17">
+    <row r="116" spans="2:17">
       <c r="C116" s="20" t="s">
         <v>62</v>
       </c>
@@ -68422,7 +69111,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="117" spans="3:17">
+    <row r="117" spans="2:17">
       <c r="C117" s="20" t="s">
         <v>63</v>
       </c>
@@ -68459,7 +69148,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="118" spans="3:17">
+    <row r="118" spans="2:17">
       <c r="C118" s="70" t="s">
         <v>64</v>
       </c>
@@ -68496,7 +69185,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="119" spans="3:17">
+    <row r="119" spans="2:17">
       <c r="C119" s="35" t="s">
         <v>28</v>
       </c>
@@ -68536,11 +69225,14 @@
         <v>163</v>
       </c>
     </row>
-    <row r="120" spans="3:17">
+    <row r="120" spans="2:17">
       <c r="E120" s="34"/>
       <c r="F120" s="34"/>
     </row>
-    <row r="121" spans="3:17">
+    <row r="121" spans="2:17">
+      <c r="B121" t="s">
+        <v>316</v>
+      </c>
       <c r="C121" s="5" t="s">
         <v>131</v>
       </c>
@@ -68555,7 +69247,7 @@
       <c r="O121" s="65"/>
       <c r="P121" s="65"/>
     </row>
-    <row r="122" spans="3:17">
+    <row r="122" spans="2:17">
       <c r="C122" s="26" t="str">
         <f t="shared" ref="C122:K122" si="23">C14</f>
         <v xml:space="preserve">Fiscal year  </v>
@@ -68595,7 +69287,7 @@
       <c r="O122" s="65"/>
       <c r="P122" s="65"/>
     </row>
-    <row r="123" spans="3:17">
+    <row r="123" spans="2:17">
       <c r="C123" s="7" t="str">
         <f t="shared" ref="C123:K123" si="24">C15</f>
         <v>Fiscal year end date</v>
@@ -68635,12 +69327,12 @@
       <c r="O123" s="65"/>
       <c r="P123" s="65"/>
     </row>
-    <row r="124" spans="3:17">
+    <row r="124" spans="2:17">
       <c r="C124" s="16"/>
       <c r="O124" s="65"/>
       <c r="P124" s="65"/>
     </row>
-    <row r="125" spans="3:17">
+    <row r="125" spans="2:17">
       <c r="C125" s="19" t="s">
         <v>39</v>
       </c>
@@ -68648,7 +69340,7 @@
       <c r="P125" s="65"/>
       <c r="Q125" s="65"/>
     </row>
-    <row r="126" spans="3:17">
+    <row r="126" spans="2:17">
       <c r="C126" s="20" t="s">
         <v>45</v>
       </c>
@@ -68678,7 +69370,7 @@
       <c r="O126" s="65"/>
       <c r="P126" s="65"/>
     </row>
-    <row r="127" spans="3:17">
+    <row r="127" spans="2:17">
       <c r="C127" s="20" t="s">
         <v>69</v>
       </c>
@@ -68703,7 +69395,7 @@
       <c r="O127" s="65"/>
       <c r="P127" s="65"/>
     </row>
-    <row r="128" spans="3:17">
+    <row r="128" spans="2:17">
       <c r="C128" s="70" t="s">
         <v>40</v>
       </c>
@@ -68734,7 +69426,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="129" spans="3:19">
+    <row r="129" spans="2:19">
       <c r="C129" s="35" t="s">
         <v>102</v>
       </c>
@@ -68759,12 +69451,15 @@
         <v>79472.455701221203</v>
       </c>
     </row>
-    <row r="131" spans="3:19">
+    <row r="131" spans="2:19">
+      <c r="B131" t="s">
+        <v>316</v>
+      </c>
       <c r="C131" s="16" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="132" spans="3:19">
+    <row r="132" spans="2:19">
       <c r="C132" s="20" t="s">
         <v>27</v>
       </c>
@@ -68792,7 +69487,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="133" spans="3:19">
+    <row r="133" spans="2:19">
       <c r="C133" s="31" t="s">
         <v>175</v>
       </c>
@@ -68820,7 +69515,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="134" spans="3:19">
+    <row r="134" spans="2:19">
       <c r="C134" s="69" t="s">
         <v>128</v>
       </c>
@@ -68846,7 +69541,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="135" spans="3:19">
+    <row r="135" spans="2:19">
       <c r="C135" s="20" t="s">
         <v>28</v>
       </c>
@@ -68883,7 +69578,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="136" spans="3:19">
+    <row r="136" spans="2:19">
       <c r="C136" s="82" t="s">
         <v>119</v>
       </c>
@@ -68912,7 +69607,7 @@
       </c>
       <c r="S136" s="34"/>
     </row>
-    <row r="137" spans="3:19">
+    <row r="137" spans="2:19">
       <c r="D137" s="18"/>
       <c r="E137" s="18"/>
       <c r="F137" s="85"/>
@@ -68923,7 +69618,10 @@
       <c r="K137" s="86"/>
       <c r="S137" s="34"/>
     </row>
-    <row r="138" spans="3:19">
+    <row r="138" spans="2:19">
+      <c r="B138" t="s">
+        <v>316</v>
+      </c>
       <c r="C138" s="5" t="s">
         <v>43</v>
       </c>
@@ -68937,7 +69635,7 @@
       <c r="K138" s="33"/>
       <c r="R138" s="66"/>
     </row>
-    <row r="139" spans="3:19">
+    <row r="139" spans="2:19">
       <c r="C139" s="26" t="str">
         <f t="shared" ref="C139:K139" si="25">C14</f>
         <v xml:space="preserve">Fiscal year  </v>
@@ -68977,7 +69675,7 @@
       <c r="R139" s="66"/>
       <c r="S139" s="34"/>
     </row>
-    <row r="140" spans="3:19">
+    <row r="140" spans="2:19">
       <c r="C140" s="7" t="str">
         <f t="shared" ref="C140:K140" si="26">C15</f>
         <v>Fiscal year end date</v>
@@ -69016,7 +69714,7 @@
       </c>
       <c r="R140" s="66"/>
     </row>
-    <row r="141" spans="3:19">
+    <row r="141" spans="2:19">
       <c r="C141" s="20"/>
       <c r="D141" s="18"/>
       <c r="E141" s="18"/>
@@ -69028,7 +69726,7 @@
       <c r="K141" s="89"/>
       <c r="R141" s="66"/>
     </row>
-    <row r="142" spans="3:19">
+    <row r="142" spans="2:19">
       <c r="C142" s="28" t="s">
         <v>120</v>
       </c>
@@ -69069,17 +69767,20 @@
       </c>
       <c r="R142" s="34"/>
     </row>
-    <row r="143" spans="3:19">
+    <row r="143" spans="2:19">
       <c r="C143" s="39"/>
       <c r="R143" s="34"/>
     </row>
-    <row r="144" spans="3:19">
+    <row r="144" spans="2:19">
+      <c r="B144" t="s">
+        <v>316</v>
+      </c>
       <c r="C144" s="61" t="s">
         <v>68</v>
       </c>
       <c r="R144" s="34"/>
     </row>
-    <row r="145" spans="3:18">
+    <row r="145" spans="2:18">
       <c r="C145" s="20" t="s">
         <v>111</v>
       </c>
@@ -69113,7 +69814,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="146" spans="3:18">
+    <row r="146" spans="2:18">
       <c r="C146" s="20" t="s">
         <v>112</v>
       </c>
@@ -69150,7 +69851,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="147" spans="3:18">
+    <row r="147" spans="2:18">
       <c r="C147" s="111" t="s">
         <v>41</v>
       </c>
@@ -69187,13 +69888,16 @@
         <v>179</v>
       </c>
     </row>
-    <row r="148" spans="3:18">
+    <row r="148" spans="2:18">
       <c r="C148" s="49"/>
       <c r="D148" s="18"/>
       <c r="E148" s="18"/>
       <c r="F148" s="18"/>
     </row>
-    <row r="149" spans="3:18">
+    <row r="149" spans="2:18">
+      <c r="B149" t="s">
+        <v>316</v>
+      </c>
       <c r="C149" s="61" t="s">
         <v>67</v>
       </c>
@@ -69201,7 +69905,7 @@
       <c r="E149" s="18"/>
       <c r="F149" s="18"/>
     </row>
-    <row r="150" spans="3:18">
+    <row r="150" spans="2:18">
       <c r="C150" s="20" t="s">
         <v>112</v>
       </c>
@@ -69238,7 +69942,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="151" spans="3:18">
+    <row r="151" spans="2:18">
       <c r="C151" s="20" t="s">
         <v>111</v>
       </c>
@@ -69275,7 +69979,7 @@
       </c>
       <c r="R151" s="66"/>
     </row>
-    <row r="152" spans="3:18">
+    <row r="152" spans="2:18">
       <c r="C152" s="35" t="s">
         <v>185</v>
       </c>
@@ -69312,17 +70016,17 @@
         <v>114</v>
       </c>
     </row>
-    <row r="153" spans="3:18">
+    <row r="153" spans="2:18">
       <c r="E153" s="18"/>
     </row>
-    <row r="154" spans="3:18">
+    <row r="154" spans="2:18">
       <c r="C154" s="39" t="s">
         <v>42</v>
       </c>
       <c r="E154" s="18"/>
       <c r="F154" s="18"/>
     </row>
-    <row r="155" spans="3:18" ht="15" customHeight="1">
+    <row r="155" spans="2:18" ht="15" customHeight="1">
       <c r="C155" s="20" t="s">
         <v>115</v>
       </c>
@@ -69359,7 +70063,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="156" spans="3:18" ht="15" customHeight="1">
+    <row r="156" spans="2:18" ht="15" customHeight="1">
       <c r="C156" s="20" t="s">
         <v>4</v>
       </c>
@@ -69399,7 +70103,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="157" spans="3:18">
+    <row r="157" spans="2:18">
       <c r="C157" s="41"/>
       <c r="D157" s="60"/>
       <c r="E157" s="60"/>
